--- a/database/event/2036/event_2036_evp_summary.xlsx
+++ b/database/event/2036/event_2036_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3893</v>
+        <v>9.0284</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1746</v>
+        <v>5.5688</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9677</v>
+        <v>3.153</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3893</v>
+        <v>9.0284</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8642</v>
+        <v>2.5033</v>
       </c>
       <c r="G2" t="n">
         <v>6.525</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8642</v>
+        <v>2.5033</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8729</v>
+        <v>2.5244</v>
       </c>
       <c r="J2" t="n">
         <v>6.8989</v>
@@ -529,7 +529,7 @@
         <v>207</v>
       </c>
       <c r="M2" t="n">
-        <v>8.771800000000001</v>
+        <v>9.423300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4046</v>
+        <v>6.7167</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9504</v>
+        <v>4.1429</v>
       </c>
       <c r="D3" t="n">
-        <v>2.166</v>
+        <v>2.232</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4046</v>
+        <v>6.7167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4701</v>
+        <v>3.2799</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9345</v>
+        <v>3.4367</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4701</v>
+        <v>3.2799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4723</v>
+        <v>3.2799</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9345</v>
+        <v>3.4367</v>
       </c>
       <c r="K3" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L3" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4068</v>
+        <v>6.7166</v>
       </c>
       <c r="N3" t="n">
-        <v>347</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9624</v>
+        <v>6.4029</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6776</v>
+        <v>3.9493</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9873</v>
+        <v>2.107</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9624</v>
+        <v>6.4029</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5257</v>
+        <v>0.4684</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4367</v>
+        <v>5.9345</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5257</v>
+        <v>0.4684</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5257</v>
+        <v>0.4723</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4367</v>
+        <v>5.9345</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="L4" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="M4" t="n">
-        <v>5.962400000000001</v>
+        <v>6.4068</v>
       </c>
       <c r="N4" t="n">
-        <v>284</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4497</v>
+        <v>5.6807</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3614</v>
+        <v>3.5039</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7802</v>
+        <v>1.8193</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4497</v>
+        <v>5.6807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.784</v>
+        <v>1.015</v>
       </c>
       <c r="G5" t="n">
         <v>4.6658</v>
       </c>
       <c r="H5" t="n">
-        <v>0.784</v>
+        <v>1.015</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7876</v>
+        <v>1.0235</v>
       </c>
       <c r="J5" t="n">
         <v>4.6658</v>
@@ -667,7 +667,7 @@
         <v>207</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4534</v>
+        <v>5.6893</v>
       </c>
       <c r="N5" t="n">
         <v>347</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1349</v>
+        <v>4.6303</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5504</v>
+        <v>2.856</v>
       </c>
       <c r="D6" t="n">
-        <v>1.249</v>
+        <v>1.4008</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1349</v>
+        <v>4.6303</v>
       </c>
       <c r="F6" t="n">
-        <v>4.528</v>
+        <v>3.6123</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3931</v>
+        <v>1.018</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6567</v>
+        <v>3.6123</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5849</v>
+        <v>3.6427</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3931</v>
+        <v>1.018</v>
       </c>
       <c r="K6" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="L6" t="n">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="M6" t="n">
-        <v>4.191800000000001</v>
+        <v>4.6607</v>
       </c>
       <c r="N6" t="n">
-        <v>192</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5975</v>
+        <v>4.4509</v>
       </c>
       <c r="C7" t="n">
-        <v>2.219</v>
+        <v>2.7453</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0319</v>
+        <v>1.3293</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5975</v>
+        <v>4.4509</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3445</v>
+        <v>4.844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.253</v>
+        <v>-0.3931</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3445</v>
+        <v>6.9282</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7108</v>
+        <v>5.6155</v>
       </c>
       <c r="J7" t="n">
-        <v>0.253</v>
+        <v>-0.3931</v>
       </c>
       <c r="K7" t="n">
         <v>119</v>
@@ -759,7 +759,7 @@
         <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9638</v>
+        <v>5.2224</v>
       </c>
       <c r="N7" t="n">
         <v>192</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4453</v>
+        <v>4.4395</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1251</v>
+        <v>2.7383</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9705</v>
+        <v>1.3248</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4453</v>
+        <v>4.4395</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4273</v>
+        <v>4.4395</v>
       </c>
       <c r="G8" t="n">
-        <v>1.018</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4273</v>
+        <v>4.6581</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4385</v>
+        <v>4.6581</v>
       </c>
       <c r="J8" t="n">
-        <v>1.018</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L8" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4565</v>
+        <v>4.6581</v>
       </c>
       <c r="N8" t="n">
-        <v>347</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.284</v>
+        <v>4.3993</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0256</v>
+        <v>2.7135</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9053</v>
+        <v>1.3088</v>
       </c>
       <c r="E9" t="n">
-        <v>3.284</v>
+        <v>4.3993</v>
       </c>
       <c r="F9" t="n">
-        <v>3.395</v>
+        <v>4.1463</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.111</v>
+        <v>0.253</v>
       </c>
       <c r="H9" t="n">
-        <v>3.395</v>
+        <v>4.1463</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7518</v>
+        <v>3.3607</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.111</v>
+        <v>0.253</v>
       </c>
       <c r="K9" t="n">
         <v>119</v>
@@ -851,7 +851,7 @@
         <v>73</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6408</v>
+        <v>3.6137</v>
       </c>
       <c r="N9" t="n">
         <v>192</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2778</v>
+        <v>3.8436</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0218</v>
+        <v>2.3707</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9028</v>
+        <v>1.0874</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2778</v>
+        <v>3.8436</v>
       </c>
       <c r="F10" t="n">
-        <v>4.448</v>
+        <v>3.9546</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1702</v>
+        <v>-0.111</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3349</v>
+        <v>3.9546</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3241</v>
+        <v>3.2053</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1702</v>
+        <v>-0.111</v>
       </c>
       <c r="K10" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="L10" t="n">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1539</v>
+        <v>3.0943</v>
       </c>
       <c r="N10" t="n">
-        <v>294</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1</v>
+        <v>3.6485</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9121</v>
+        <v>2.2504</v>
       </c>
       <c r="D11" t="n">
-        <v>0.831</v>
+        <v>1.0097</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1</v>
+        <v>3.6485</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7646</v>
+        <v>4.8187</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3354</v>
+        <v>-1.1702</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7646</v>
+        <v>6.8262</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4303</v>
+        <v>5.5329</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3354</v>
+        <v>-1.1702</v>
       </c>
       <c r="K11" t="n">
         <v>136</v>
@@ -943,7 +943,7 @@
         <v>158</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7657</v>
+        <v>4.3627</v>
       </c>
       <c r="N11" t="n">
         <v>294</v>
@@ -952,173 +952,173 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.07</v>
+        <v>3.3875</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8936</v>
+        <v>2.0894</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8188</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.07</v>
+        <v>3.3875</v>
       </c>
       <c r="F12" t="n">
-        <v>3.07</v>
+        <v>2.0521</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.3354</v>
       </c>
       <c r="H12" t="n">
-        <v>3.07</v>
+        <v>2.0521</v>
       </c>
       <c r="I12" t="n">
-        <v>3.07</v>
+        <v>1.6633</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.3354</v>
       </c>
       <c r="K12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M12" t="n">
-        <v>3.07</v>
+        <v>2.9987</v>
       </c>
       <c r="N12" t="n">
-        <v>135</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5175</v>
+        <v>3.1896</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5528</v>
+        <v>1.9674</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5957</v>
+        <v>0.8268</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5175</v>
+        <v>3.1896</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1158</v>
+        <v>3.1896</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4017</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1158</v>
+        <v>3.1896</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1158</v>
+        <v>3.1896</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4017</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="L13" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5175</v>
+        <v>3.1896</v>
       </c>
       <c r="N13" t="n">
-        <v>284</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4367</v>
+        <v>3.0388</v>
       </c>
       <c r="C14" t="n">
-        <v>1.503</v>
+        <v>1.8743</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7667</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4367</v>
+        <v>3.0388</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4367</v>
+        <v>2.6371</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.4017</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4367</v>
+        <v>2.6371</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4367</v>
+        <v>2.6371</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.4017</v>
       </c>
       <c r="K14" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4367</v>
+        <v>3.0388</v>
       </c>
       <c r="N14" t="n">
-        <v>134</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3837</v>
+        <v>2.9655</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4703</v>
+        <v>1.8291</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5416</v>
+        <v>0.7375</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3837</v>
+        <v>2.9655</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8801</v>
+        <v>3.8437</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5036</v>
+        <v>-0.8782</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8801</v>
+        <v>3.8437</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8801</v>
+        <v>3.8437</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5036</v>
+        <v>-0.8782</v>
       </c>
       <c r="K15" t="n">
         <v>140</v>
@@ -1127,7 +1127,7 @@
         <v>89</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3837</v>
+        <v>2.9655</v>
       </c>
       <c r="N15" t="n">
         <v>229</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3909</v>
+        <v>1.7464</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4896</v>
+        <v>0.6841</v>
       </c>
       <c r="E16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="F16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="I16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.255</v>
+        <v>2.8314</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1182,860 +1182,860 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2429</v>
+        <v>2.5806</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3834</v>
+        <v>1.5917</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4847</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2429</v>
+        <v>2.5806</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8271</v>
+        <v>1.077</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4158</v>
+        <v>1.5036</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8271</v>
+        <v>1.077</v>
       </c>
       <c r="I17" t="n">
-        <v>1.481</v>
+        <v>1.077</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4158</v>
+        <v>1.5036</v>
       </c>
       <c r="K17" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L17" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8968</v>
+        <v>2.5806</v>
       </c>
       <c r="N17" t="n">
-        <v>294</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8914</v>
+        <v>2.5727</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1666</v>
+        <v>1.5869</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3427</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8914</v>
+        <v>2.5727</v>
       </c>
       <c r="F18" t="n">
-        <v>1.699</v>
+        <v>2.5727</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1924</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.699</v>
+        <v>2.5727</v>
       </c>
       <c r="I18" t="n">
-        <v>1.699</v>
+        <v>2.5727</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1924</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L18" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8914</v>
+        <v>2.5727</v>
       </c>
       <c r="N18" t="n">
-        <v>229</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.76</v>
+        <v>2.2853</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0856</v>
+        <v>1.4096</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2896</v>
+        <v>0.4666</v>
       </c>
       <c r="E19" t="n">
-        <v>1.76</v>
+        <v>2.2853</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8317</v>
+        <v>1.8695</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0717</v>
+        <v>0.4158</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8317</v>
+        <v>1.8695</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4846</v>
+        <v>1.5153</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0717</v>
+        <v>0.4158</v>
       </c>
       <c r="K19" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4129</v>
+        <v>1.9311</v>
       </c>
       <c r="N19" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7527</v>
+        <v>2.0916</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0811</v>
+        <v>1.2901</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2867</v>
+        <v>0.3894</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7527</v>
+        <v>2.0916</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7527</v>
+        <v>1.8992</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1924</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7527</v>
+        <v>1.8992</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7527</v>
+        <v>1.8992</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1924</v>
       </c>
       <c r="K20" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7527</v>
+        <v>2.0916</v>
       </c>
       <c r="N20" t="n">
-        <v>133</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.344</v>
+        <v>1.8907</v>
       </c>
       <c r="C21" t="n">
-        <v>0.829</v>
+        <v>1.1662</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1216</v>
+        <v>0.3093</v>
       </c>
       <c r="E21" t="n">
-        <v>1.344</v>
+        <v>1.8907</v>
       </c>
       <c r="F21" t="n">
-        <v>1.344</v>
+        <v>1.9624</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.0717</v>
       </c>
       <c r="H21" t="n">
-        <v>1.344</v>
+        <v>1.9624</v>
       </c>
       <c r="I21" t="n">
-        <v>1.344</v>
+        <v>1.5906</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.0717</v>
       </c>
       <c r="K21" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M21" t="n">
-        <v>1.344</v>
+        <v>1.5189</v>
       </c>
       <c r="N21" t="n">
-        <v>135</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>v1c7oR</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2778</v>
+        <v>1.8076</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7882</v>
+        <v>1.1149</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0948</v>
+        <v>0.2762</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2778</v>
+        <v>1.8076</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2778</v>
+        <v>2.8076</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2778</v>
+        <v>2.8076</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2778</v>
+        <v>2.8076</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K22" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2778</v>
+        <v>1.8076</v>
       </c>
       <c r="N22" t="n">
-        <v>137</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>v1c7oR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2761</v>
+        <v>1.5813</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7871</v>
+        <v>0.9754</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1861</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2761</v>
+        <v>1.5813</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1543</v>
+        <v>1.5813</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8782</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1543</v>
+        <v>1.5813</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1543</v>
+        <v>1.5813</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8782</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L23" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2761</v>
+        <v>1.5813</v>
       </c>
       <c r="N23" t="n">
-        <v>229</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7236</v>
+        <v>0.9667</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0526</v>
+        <v>0.1805</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1732</v>
+        <v>1.5673</v>
       </c>
       <c r="N24" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1346</v>
+        <v>1.5357</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6998</v>
+        <v>0.9472</v>
       </c>
       <c r="D25" t="n">
-        <v>0.037</v>
+        <v>0.1679</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1346</v>
+        <v>1.5357</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8091</v>
+        <v>1.5357</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3255</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8091</v>
+        <v>1.5357</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6558</v>
+        <v>1.5357</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3255</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L25" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9813000000000001</v>
+        <v>1.5357</v>
       </c>
       <c r="N25" t="n">
-        <v>294</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9487</v>
+        <v>1.5129</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.9332</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0381</v>
+        <v>0.1588</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9487</v>
+        <v>1.5129</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5591</v>
+        <v>1.1874</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.3255</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5591</v>
+        <v>1.1874</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2637</v>
+        <v>0.9624</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.3255</v>
       </c>
       <c r="K26" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="L26" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6533</v>
+        <v>1.2879</v>
       </c>
       <c r="N26" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.1732</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5431</v>
+        <v>0.7236</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.0235</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.1732</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3023</v>
+        <v>1.1732</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1828</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3023</v>
+        <v>1.1732</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3023</v>
+        <v>1.1732</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1828</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L27" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8805000000000001</v>
+        <v>1.1732</v>
       </c>
       <c r="N27" t="n">
-        <v>284</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8686</v>
+        <v>1.1686</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.7208</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.0217</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8686</v>
+        <v>1.1686</v>
       </c>
       <c r="F28" t="n">
-        <v>1.8686</v>
+        <v>1.779</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8686</v>
+        <v>1.779</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8686</v>
+        <v>1.4419</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8686</v>
+        <v>0.8314999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8505</v>
+        <v>1.1134</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5246</v>
+        <v>0.6868</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8505</v>
+        <v>1.1134</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8505</v>
+        <v>1.8655</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.7521</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8505</v>
+        <v>1.8655</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8505</v>
+        <v>1.8655</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.7521</v>
       </c>
       <c r="K29" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8505</v>
+        <v>1.1134</v>
       </c>
       <c r="N29" t="n">
-        <v>133</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7958</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4909</v>
+        <v>0.5431</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0999</v>
+        <v>-0.0931</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7958</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1751</v>
+        <v>-0.3023</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9709</v>
+        <v>1.1828</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1751</v>
+        <v>-0.3023</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1759</v>
+        <v>-0.3023</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9709</v>
+        <v>1.1828</v>
       </c>
       <c r="K30" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L30" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.8805000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>347</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7242</v>
+        <v>0.8109</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4467</v>
+        <v>0.5002</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1288</v>
+        <v>-0.1208</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7242</v>
+        <v>0.8109</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7242</v>
+        <v>-0.16</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.9709</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7242</v>
+        <v>-0.16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7242</v>
+        <v>-0.1613</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.9709</v>
       </c>
       <c r="K31" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7242</v>
+        <v>0.8096</v>
       </c>
       <c r="N31" t="n">
-        <v>149</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5261</v>
+        <v>0.7987</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3245</v>
+        <v>0.4926</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2088</v>
+        <v>-0.1257</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5261</v>
+        <v>0.7987</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5261</v>
+        <v>1.9667</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.168</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5261</v>
+        <v>1.9667</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5261</v>
+        <v>1.9667</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1.168</v>
       </c>
       <c r="K32" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5261</v>
+        <v>0.7987</v>
       </c>
       <c r="N32" t="n">
-        <v>149</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3339</v>
+        <v>0.7464</v>
       </c>
       <c r="C33" t="n">
-        <v>0.206</v>
+        <v>0.4604</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2865</v>
+        <v>-0.1465</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3339</v>
+        <v>0.7464</v>
       </c>
       <c r="F33" t="n">
-        <v>1.086</v>
+        <v>0.7464</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7521</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.086</v>
+        <v>0.7464</v>
       </c>
       <c r="I33" t="n">
-        <v>1.086</v>
+        <v>0.7464</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7521</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="L33" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3339000000000001</v>
+        <v>0.7464</v>
       </c>
       <c r="N33" t="n">
-        <v>284</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1224</v>
+        <v>0.3378</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3412</v>
+        <v>-0.2257</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1984</v>
+        <v>0.5476</v>
       </c>
       <c r="N34" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1087</v>
+        <v>0.3245</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3502</v>
+        <v>-0.2343</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1762</v>
+        <v>0.5261</v>
       </c>
       <c r="N35" t="n">
         <v>149</v>
@@ -2056,35 +2056,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1436</v>
+        <v>0.4428</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0886</v>
+        <v>0.2731</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3634</v>
+        <v>-0.2675</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1436</v>
+        <v>0.4428</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8286</v>
+        <v>1.4428</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8286</v>
+        <v>1.4428</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8286</v>
+        <v>1.4428</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K36" t="n">
         <v>131</v>
@@ -2093,7 +2093,7 @@
         <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1435999999999999</v>
+        <v>0.4428000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>176</v>
@@ -2102,323 +2102,323 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0847</v>
+        <v>0.2394</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3659</v>
+        <v>-0.2893</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1373</v>
+        <v>0.3881</v>
       </c>
       <c r="N37" t="n">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0606</v>
+        <v>0.2504</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0374</v>
+        <v>0.1544</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3969</v>
+        <v>-0.3442</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0606</v>
+        <v>0.2504</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0606</v>
+        <v>0.4625</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.2121</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0606</v>
+        <v>0.4625</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0606</v>
+        <v>0.4625</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.2121</v>
       </c>
       <c r="K38" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0606</v>
+        <v>0.2504</v>
       </c>
       <c r="N38" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0393</v>
+        <v>0.1984</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0242</v>
+        <v>0.1224</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4055</v>
+        <v>-0.3649</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0393</v>
+        <v>0.1984</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2514</v>
+        <v>0.1984</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2121</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2514</v>
+        <v>0.1984</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2514</v>
+        <v>0.1984</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2121</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L39" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0393</v>
+        <v>0.1984</v>
       </c>
       <c r="N39" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0022</v>
+        <v>0.1466</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0014</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4205</v>
+        <v>-0.3855</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0022</v>
+        <v>0.1466</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1702</v>
+        <v>0.8316</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.168</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1702</v>
+        <v>0.8316</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1702</v>
+        <v>0.8316</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.168</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L40" t="n">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.00219999999999998</v>
+        <v>0.1466</v>
       </c>
       <c r="N40" t="n">
-        <v>284</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0368</v>
+        <v>0.0374</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4454</v>
+        <v>-0.4198</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0596</v>
+        <v>0.0606</v>
       </c>
       <c r="N41" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0843</v>
+        <v>-0.0368</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4766</v>
+        <v>-0.4677</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1367</v>
+        <v>-0.0596</v>
       </c>
       <c r="N42" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0953</v>
+        <v>-0.0843</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4838</v>
+        <v>-0.4984</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="N43" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.2333</v>
+        <v>-0.1494</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5404</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3782</v>
+        <v>-0.2422</v>
       </c>
       <c r="N44" t="n">
         <v>135</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2501</v>
+        <v>-0.2055</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5767</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4055</v>
+        <v>-0.3332</v>
       </c>
       <c r="N45" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2674</v>
+        <v>-0.2311</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5965</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4335</v>
+        <v>-0.3747</v>
       </c>
       <c r="N46" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5708</v>
+        <v>-0.3756</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3521</v>
+        <v>-0.2317</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.652</v>
+        <v>-0.5935</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5708</v>
+        <v>-0.3756</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2431</v>
+        <v>-0.0479</v>
       </c>
       <c r="G47" t="n">
         <v>-0.3277</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.2431</v>
+        <v>-0.0479</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2431</v>
+        <v>-0.0479</v>
       </c>
       <c r="J47" t="n">
         <v>-0.3277</v>
@@ -2599,7 +2599,7 @@
         <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.5708</v>
+        <v>-0.3756</v>
       </c>
       <c r="N47" t="n">
         <v>176</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3987</v>
+        <v>-0.2552</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6825</v>
+        <v>-0.6087</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6464</v>
+        <v>-0.4137</v>
       </c>
       <c r="N48" t="n">
         <v>135</v>
@@ -2654,47 +2654,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.5065</v>
+        <v>-0.2674</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7531</v>
+        <v>-0.6166</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="N49" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50">
@@ -2710,7 +2710,7 @@
         <v>-0.5295</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7681</v>
+        <v>-0.7859</v>
       </c>
       <c r="E50" t="n">
         <v>-0.8584000000000001</v>
@@ -2756,7 +2756,7 @@
         <v>-0.5686</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7938</v>
+        <v>-0.8112</v>
       </c>
       <c r="E51" t="n">
         <v>-0.9219000000000001</v>
@@ -2802,7 +2802,7 @@
         <v>-0.6847</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8698</v>
+        <v>-0.8862</v>
       </c>
       <c r="E52" t="n">
         <v>-1.1101</v>
@@ -2838,139 +2838,139 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.1773</v>
+        <v>-1.1284</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.7262</v>
+        <v>-0.696</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.897</v>
+        <v>-0.8935</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1773</v>
+        <v>-1.1284</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.1773</v>
+        <v>-0.1284</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.1773</v>
+        <v>-0.1284</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.1773</v>
+        <v>-0.1284</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K53" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.1773</v>
+        <v>-1.1284</v>
       </c>
       <c r="N53" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machinegun</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.9306</v>
+        <v>-0.7262</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0308</v>
+        <v>-0.9129</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.5087</v>
+        <v>-1.1773</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Machinegun</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="C55" t="n">
-        <v>-1.0347</v>
+        <v>-0.9306</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.099</v>
+        <v>-1.045</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="J55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="L55" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.6775</v>
+        <v>-1.5087</v>
       </c>
       <c r="N55" t="n">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.7403</v>
+        <v>-1.7387</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.0734</v>
+        <v>-1.0724</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1244</v>
+        <v>-1.1366</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.7403</v>
+        <v>-1.7387</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.5754</v>
+        <v>-1.5738</v>
       </c>
       <c r="G56" t="n">
         <v>-0.1649</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.5754</v>
+        <v>-1.5738</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.2769</v>
+        <v>-1.2756</v>
       </c>
       <c r="J56" t="n">
         <v>-0.1649</v>
@@ -3013,7 +3013,7 @@
         <v>158</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.4418</v>
+        <v>-1.4405</v>
       </c>
       <c r="N56" t="n">
         <v>294</v>
@@ -3032,7 +3032,7 @@
         <v>-1.2688</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.2523</v>
+        <v>-1.2634</v>
       </c>
       <c r="E57" t="n">
         <v>-2.057</v>
@@ -3078,7 +3078,7 @@
         <v>-1.6801</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.5217</v>
+        <v>-1.5291</v>
       </c>
       <c r="E58" t="n">
         <v>-2.7238</v>
@@ -3124,7 +3124,7 @@
         <v>-1.7778</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.5857</v>
+        <v>-1.5922</v>
       </c>
       <c r="E59" t="n">
         <v>-2.8822</v>
@@ -3170,7 +3170,7 @@
         <v>-1.8698</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.646</v>
+        <v>-1.6516</v>
       </c>
       <c r="E60" t="n">
         <v>-3.0314</v>
@@ -3216,7 +3216,7 @@
         <v>-1.9605</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.7054</v>
+        <v>-1.7102</v>
       </c>
       <c r="E61" t="n">
         <v>-3.1785</v>

--- a/database/event/2036/event_2036_evp_summary.xlsx
+++ b/database/event/2036/event_2036_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0284</v>
+        <v>8.390499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5688</v>
+        <v>5.1753</v>
       </c>
       <c r="D2" t="n">
-        <v>3.153</v>
+        <v>3.1499</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0284</v>
+        <v>8.390499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5033</v>
+        <v>2.4857</v>
       </c>
       <c r="G2" t="n">
-        <v>6.525</v>
+        <v>5.9048</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5033</v>
+        <v>2.4857</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5244</v>
+        <v>2.5879</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8989</v>
+        <v>5.9048</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>207</v>
       </c>
       <c r="M2" t="n">
-        <v>9.423300000000001</v>
+        <v>8.492699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7167</v>
+        <v>6.0711</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1429</v>
+        <v>3.7447</v>
       </c>
       <c r="D3" t="n">
-        <v>2.232</v>
+        <v>2.1028</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7167</v>
+        <v>6.0711</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2799</v>
+        <v>0.761</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4367</v>
+        <v>5.3101</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2799</v>
+        <v>0.761</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2799</v>
+        <v>0.7923</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4367</v>
+        <v>5.3101</v>
       </c>
       <c r="K3" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="L3" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7166</v>
+        <v>6.1024</v>
       </c>
       <c r="N3" t="n">
-        <v>284</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4029</v>
+        <v>5.8437</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9493</v>
+        <v>3.6044</v>
       </c>
       <c r="D4" t="n">
-        <v>2.107</v>
+        <v>2.0001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4029</v>
+        <v>5.8437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4684</v>
+        <v>2.9892</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9345</v>
+        <v>2.8545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4684</v>
+        <v>3.204</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4723</v>
+        <v>3.204</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9345</v>
+        <v>2.8545</v>
       </c>
       <c r="K4" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L4" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4068</v>
+        <v>6.0585</v>
       </c>
       <c r="N4" t="n">
-        <v>347</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6807</v>
+        <v>5.5446</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5039</v>
+        <v>3.4199</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8193</v>
+        <v>1.8651</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6807</v>
+        <v>5.5446</v>
       </c>
       <c r="F5" t="n">
-        <v>1.015</v>
+        <v>1.1046</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6658</v>
+        <v>4.4401</v>
       </c>
       <c r="H5" t="n">
-        <v>1.015</v>
+        <v>1.1046</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0235</v>
+        <v>1.15</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6658</v>
+        <v>4.4401</v>
       </c>
       <c r="K5" t="n">
         <v>140</v>
@@ -667,7 +667,7 @@
         <v>207</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6893</v>
+        <v>5.5901</v>
       </c>
       <c r="N5" t="n">
         <v>347</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6303</v>
+        <v>4.2945</v>
       </c>
       <c r="C6" t="n">
-        <v>2.856</v>
+        <v>2.6489</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4008</v>
+        <v>1.3007</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6303</v>
+        <v>4.2945</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6123</v>
+        <v>4.4518</v>
       </c>
       <c r="G6" t="n">
-        <v>1.018</v>
+        <v>-0.1573</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6123</v>
+        <v>10.2462</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6427</v>
+        <v>5.3275</v>
       </c>
       <c r="J6" t="n">
-        <v>1.018</v>
+        <v>-0.1573</v>
       </c>
       <c r="K6" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="L6" t="n">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6607</v>
+        <v>5.170199999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>347</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4509</v>
+        <v>4.0764</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7453</v>
+        <v>2.5143</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3293</v>
+        <v>1.2023</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4509</v>
+        <v>4.0764</v>
       </c>
       <c r="F7" t="n">
-        <v>4.844</v>
+        <v>3.0543</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3931</v>
+        <v>1.0221</v>
       </c>
       <c r="H7" t="n">
-        <v>6.9282</v>
+        <v>3.347</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6155</v>
+        <v>3.4846</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3931</v>
+        <v>1.0221</v>
       </c>
       <c r="K7" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2224</v>
+        <v>4.5067</v>
       </c>
       <c r="N7" t="n">
-        <v>192</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4395</v>
+        <v>3.6956</v>
       </c>
       <c r="C8" t="n">
-        <v>2.7383</v>
+        <v>2.2795</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3248</v>
+        <v>1.0304</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4395</v>
+        <v>3.6956</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4395</v>
+        <v>3.6956</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6581</v>
+        <v>4.7551</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6581</v>
+        <v>4.7551</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6581</v>
+        <v>4.7551</v>
       </c>
       <c r="N8" t="n">
         <v>135</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3993</v>
+        <v>3.6678</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7135</v>
+        <v>2.2623</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3088</v>
+        <v>1.0178</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3993</v>
+        <v>3.6678</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1463</v>
+        <v>3.3689</v>
       </c>
       <c r="G9" t="n">
-        <v>0.253</v>
+        <v>0.2989</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1463</v>
+        <v>6.3836</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3607</v>
+        <v>3.3192</v>
       </c>
       <c r="J9" t="n">
-        <v>0.253</v>
+        <v>0.2989</v>
       </c>
       <c r="K9" t="n">
         <v>119</v>
@@ -851,7 +851,7 @@
         <v>73</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6137</v>
+        <v>3.6181</v>
       </c>
       <c r="N9" t="n">
         <v>192</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8436</v>
+        <v>3.651</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3707</v>
+        <v>2.252</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0874</v>
+        <v>1.0102</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8436</v>
+        <v>3.651</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9546</v>
+        <v>2.554</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.111</v>
+        <v>1.097</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9546</v>
+        <v>3.5124</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2053</v>
+        <v>1.8263</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.111</v>
+        <v>1.097</v>
       </c>
       <c r="K10" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="L10" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0943</v>
+        <v>2.9233</v>
       </c>
       <c r="N10" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6485</v>
+        <v>3.4397</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2504</v>
+        <v>2.1216</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0097</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6485</v>
+        <v>3.4397</v>
       </c>
       <c r="F11" t="n">
-        <v>4.8187</v>
+        <v>4.3212</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1702</v>
+        <v>-0.8815</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8262</v>
+        <v>9.738799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5329</v>
+        <v>5.0637</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1702</v>
+        <v>-0.8815</v>
       </c>
       <c r="K11" t="n">
         <v>136</v>
@@ -943,7 +943,7 @@
         <v>158</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3627</v>
+        <v>4.1822</v>
       </c>
       <c r="N11" t="n">
         <v>294</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3875</v>
+        <v>3.4157</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0894</v>
+        <v>2.1068</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.904</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3875</v>
+        <v>3.4157</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0521</v>
+        <v>3.3274</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3354</v>
+        <v>0.0883</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0521</v>
+        <v>6.2375</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6633</v>
+        <v>3.2432</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3354</v>
+        <v>0.0883</v>
       </c>
       <c r="K12" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="L12" t="n">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9987</v>
+        <v>3.3315</v>
       </c>
       <c r="N12" t="n">
-        <v>294</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1896</v>
+        <v>3.0727</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9674</v>
+        <v>1.8953</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8268</v>
+        <v>0.7492</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1896</v>
+        <v>3.0727</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1896</v>
+        <v>2.4977</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1896</v>
+        <v>3.3139</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1896</v>
+        <v>1.7231</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="K13" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1896</v>
+        <v>2.2981</v>
       </c>
       <c r="N13" t="n">
-        <v>134</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0388</v>
+        <v>3.0151</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8743</v>
+        <v>1.8597</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7667</v>
+        <v>0.7232</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0388</v>
+        <v>3.0151</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6371</v>
+        <v>2.6794</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4017</v>
+        <v>0.3357</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6371</v>
+        <v>2.6794</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6371</v>
+        <v>2.6794</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4017</v>
+        <v>0.3357</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -1081,7 +1081,7 @@
         <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0388</v>
+        <v>3.0151</v>
       </c>
       <c r="N14" t="n">
         <v>284</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9655</v>
+        <v>3.0023</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8291</v>
+        <v>1.8518</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7375</v>
+        <v>0.7174</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9655</v>
+        <v>3.0023</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8437</v>
+        <v>3.0023</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8782</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8437</v>
+        <v>3.2328</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8437</v>
+        <v>3.2328</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8782</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L15" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9655</v>
+        <v>3.2328</v>
       </c>
       <c r="N15" t="n">
-        <v>229</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8314</v>
+        <v>2.8941</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7464</v>
+        <v>1.7851</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6841</v>
+        <v>0.6685</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8314</v>
+        <v>2.8941</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8314</v>
+        <v>2.8941</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8314</v>
+        <v>2.9951</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8314</v>
+        <v>2.9951</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8314</v>
+        <v>2.9951</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5806</v>
+        <v>2.715</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5917</v>
+        <v>1.6746</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5806</v>
+        <v>2.715</v>
       </c>
       <c r="F17" t="n">
-        <v>1.077</v>
+        <v>1.3599</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5036</v>
+        <v>1.3551</v>
       </c>
       <c r="H17" t="n">
-        <v>1.077</v>
+        <v>1.3599</v>
       </c>
       <c r="I17" t="n">
-        <v>1.077</v>
+        <v>1.3599</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5036</v>
+        <v>1.3551</v>
       </c>
       <c r="K17" t="n">
         <v>140</v>
@@ -1219,7 +1219,7 @@
         <v>89</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5806</v>
+        <v>2.715</v>
       </c>
       <c r="N17" t="n">
         <v>229</v>
@@ -1228,446 +1228,446 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5727</v>
+        <v>2.6106</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5869</v>
+        <v>1.6102</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5405</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5727</v>
+        <v>2.6106</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5727</v>
+        <v>3.1841</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.5735</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5727</v>
+        <v>3.632</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5727</v>
+        <v>3.632</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.5735</v>
       </c>
       <c r="K18" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5727</v>
+        <v>3.0585</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2853</v>
+        <v>2.5902</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4096</v>
+        <v>1.5976</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4666</v>
+        <v>0.5313</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2853</v>
+        <v>2.5902</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8695</v>
+        <v>2.5902</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4158</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8695</v>
+        <v>2.5902</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5153</v>
+        <v>2.5902</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4158</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L19" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9311</v>
+        <v>2.5902</v>
       </c>
       <c r="N19" t="n">
-        <v>294</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0916</v>
+        <v>2.5855</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2901</v>
+        <v>1.5947</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3894</v>
+        <v>0.5292</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0916</v>
+        <v>2.5855</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8992</v>
+        <v>2.5837</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1924</v>
+        <v>0.0018</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8992</v>
+        <v>3.6171</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8992</v>
+        <v>1.8807</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1924</v>
+        <v>0.0018</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0916</v>
+        <v>1.8825</v>
       </c>
       <c r="N20" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8907</v>
+        <v>2.5465</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1662</v>
+        <v>1.5707</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3093</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8907</v>
+        <v>2.5465</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9624</v>
+        <v>2.225</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0717</v>
+        <v>0.3215</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9624</v>
+        <v>2.225</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5906</v>
+        <v>2.225</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0717</v>
+        <v>0.3215</v>
       </c>
       <c r="K21" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="L21" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5189</v>
+        <v>2.5465</v>
       </c>
       <c r="N21" t="n">
-        <v>192</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8076</v>
+        <v>2.5329</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1149</v>
+        <v>1.5623</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2762</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8076</v>
+        <v>2.5329</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8076</v>
+        <v>2.1106</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0.4223</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8076</v>
+        <v>2.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8076</v>
+        <v>1.0974</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>0.4223</v>
       </c>
       <c r="K22" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L22" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8076</v>
+        <v>1.5197</v>
       </c>
       <c r="N22" t="n">
-        <v>229</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>v1c7oR</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5813</v>
+        <v>2.1324</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9754</v>
+        <v>1.3153</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1861</v>
+        <v>0.3247</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5813</v>
+        <v>2.1324</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5813</v>
+        <v>2.492</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.3596</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5813</v>
+        <v>3.2939</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5813</v>
+        <v>1.7127</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.3596</v>
       </c>
       <c r="K23" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5813</v>
+        <v>1.3531</v>
       </c>
       <c r="N23" t="n">
-        <v>137</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5673</v>
+        <v>2.0273</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9667</v>
+        <v>1.2504</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1805</v>
+        <v>0.2772</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5673</v>
+        <v>2.0273</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5673</v>
+        <v>2.7105</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6832</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5673</v>
+        <v>2.7105</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5673</v>
+        <v>2.7105</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6832</v>
       </c>
       <c r="K24" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5673</v>
+        <v>2.0273</v>
       </c>
       <c r="N24" t="n">
-        <v>135</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9472</v>
+        <v>1.2059</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1679</v>
+        <v>0.2446</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5357</v>
+        <v>1.955</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>v1c7oR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5129</v>
+        <v>1.8299</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9332</v>
+        <v>1.1287</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1588</v>
+        <v>0.1881</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5129</v>
+        <v>1.8299</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1874</v>
+        <v>1.8299</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3255</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1874</v>
+        <v>1.8299</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9624</v>
+        <v>1.8299</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3255</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L26" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2879</v>
+        <v>1.8299</v>
       </c>
       <c r="N26" t="n">
-        <v>294</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7236</v>
+        <v>1.0953</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0235</v>
+        <v>0.1637</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1732</v>
+        <v>1.7758</v>
       </c>
       <c r="N27" t="n">
         <v>133</v>
@@ -1688,538 +1688,538 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1686</v>
+        <v>1.4921</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7208</v>
+        <v>0.9203</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0217</v>
+        <v>0.0356</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1686</v>
+        <v>1.4921</v>
       </c>
       <c r="F28" t="n">
-        <v>1.779</v>
+        <v>2.1341</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.642</v>
       </c>
       <c r="H28" t="n">
-        <v>1.779</v>
+        <v>2.1341</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4419</v>
+        <v>2.1341</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.642</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L28" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8314999999999999</v>
+        <v>1.4921</v>
       </c>
       <c r="N28" t="n">
-        <v>192</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1134</v>
+        <v>1.3503</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6868</v>
+        <v>0.8329</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0003</v>
+        <v>-0.0284</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1134</v>
+        <v>1.3503</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8655</v>
+        <v>1.3503</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7521</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8655</v>
+        <v>1.3503</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8655</v>
+        <v>1.3503</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7521</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L29" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1134</v>
+        <v>1.3503</v>
       </c>
       <c r="N29" t="n">
-        <v>284</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.1819</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5431</v>
+        <v>0.729</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0931</v>
+        <v>-0.1044</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.1819</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3023</v>
+        <v>1.1819</v>
       </c>
       <c r="G30" t="n">
-        <v>1.1828</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3023</v>
+        <v>1.1819</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3023</v>
+        <v>1.1819</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1828</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="L30" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8805000000000001</v>
+        <v>1.1819</v>
       </c>
       <c r="N30" t="n">
-        <v>284</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8109</v>
+        <v>1.099</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5002</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1208</v>
+        <v>-0.1419</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8109</v>
+        <v>1.099</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.16</v>
+        <v>1.099</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9709</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.16</v>
+        <v>1.099</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1613</v>
+        <v>1.099</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9709</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L31" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8096</v>
+        <v>1.099</v>
       </c>
       <c r="N31" t="n">
-        <v>347</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7987</v>
+        <v>1.0779</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4926</v>
+        <v>0.6649</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1257</v>
+        <v>-0.1514</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7987</v>
+        <v>1.0779</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9667</v>
+        <v>-0.0275</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.168</v>
+        <v>1.1054</v>
       </c>
       <c r="H32" t="n">
-        <v>1.9667</v>
+        <v>-0.0275</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9667</v>
+        <v>-0.0286</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.168</v>
+        <v>1.1054</v>
       </c>
       <c r="K32" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="L32" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7987</v>
+        <v>1.0768</v>
       </c>
       <c r="N32" t="n">
-        <v>284</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7464</v>
+        <v>1.0708</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4604</v>
+        <v>0.6605</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1465</v>
+        <v>-0.1546</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7464</v>
+        <v>1.0708</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7464</v>
+        <v>1.9543</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.8835</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7464</v>
+        <v>1.9543</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7464</v>
+        <v>1.9543</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.8835</v>
       </c>
       <c r="K33" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7464</v>
+        <v>1.0708</v>
       </c>
       <c r="N33" t="n">
-        <v>149</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5476</v>
+        <v>1.0451</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3378</v>
+        <v>0.6446</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2257</v>
+        <v>-0.1662</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5476</v>
+        <v>1.0451</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5476</v>
+        <v>0.0387</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.0064</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5476</v>
+        <v>0.0387</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5476</v>
+        <v>0.0387</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.0064</v>
       </c>
       <c r="K34" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5476</v>
+        <v>1.0451</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5261</v>
+        <v>0.7723</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3245</v>
+        <v>0.4764</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2343</v>
+        <v>-0.2894</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5261</v>
+        <v>0.7723</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5261</v>
+        <v>1.5144</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.7421</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5261</v>
+        <v>1.5144</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5261</v>
+        <v>1.5144</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.7421</v>
       </c>
       <c r="K35" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5261</v>
+        <v>0.7723</v>
       </c>
       <c r="N35" t="n">
-        <v>149</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4428</v>
+        <v>0.7362</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2731</v>
+        <v>0.4541</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2675</v>
+        <v>-0.3057</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4428</v>
+        <v>0.7362</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4428</v>
+        <v>0.7362</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4428</v>
+        <v>0.7362</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4428</v>
+        <v>0.7362</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L36" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4428000000000001</v>
+        <v>0.7362</v>
       </c>
       <c r="N36" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3881</v>
+        <v>0.6681</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2394</v>
+        <v>0.4121</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2893</v>
+        <v>-0.3364</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3881</v>
+        <v>0.6681</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3881</v>
+        <v>1.1747</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3881</v>
+        <v>1.1747</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3881</v>
+        <v>1.1747</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3881</v>
+        <v>0.6681</v>
       </c>
       <c r="N37" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2504</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1544</v>
+        <v>0.3883</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3442</v>
+        <v>-0.3538</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2504</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4625</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2121</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4625</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4625</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2121</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2504</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1224</v>
+        <v>0.3476</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3649</v>
+        <v>-0.3836</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1984</v>
+        <v>0.5635</v>
       </c>
       <c r="N39" t="n">
         <v>149</v>
@@ -2240,35 +2240,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1466</v>
+        <v>0.5397</v>
       </c>
       <c r="C40" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.3329</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3855</v>
+        <v>-0.3944</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1466</v>
+        <v>0.5397</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8316</v>
+        <v>0.5977</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8316</v>
+        <v>0.5977</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8316</v>
+        <v>0.5977</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="K40" t="n">
         <v>131</v>
@@ -2277,7 +2277,7 @@
         <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1466</v>
+        <v>0.5397</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0374</v>
+        <v>0.2509</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4198</v>
+        <v>-0.4544</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0606</v>
+        <v>0.4068</v>
       </c>
       <c r="N41" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0368</v>
+        <v>0.2409</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4677</v>
+        <v>-0.4617</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0596</v>
+        <v>0.3905</v>
       </c>
       <c r="N42" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0843</v>
+        <v>0.2335</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4984</v>
+        <v>-0.4671</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1367</v>
+        <v>0.3785</v>
       </c>
       <c r="N43" t="n">
         <v>134</v>
@@ -2424,323 +2424,323 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1494</v>
+        <v>0.2286</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5404</v>
+        <v>-0.4707</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.2422</v>
+        <v>0.3707</v>
       </c>
       <c r="N44" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2055</v>
+        <v>0.199</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5767</v>
+        <v>-0.4924</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.3332</v>
+        <v>0.3226</v>
       </c>
       <c r="N45" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2311</v>
+        <v>0.1496</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5285</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.3747</v>
+        <v>0.2426</v>
       </c>
       <c r="N46" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.3756</v>
+        <v>-0.0147</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2317</v>
+        <v>-0.0091</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5935</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.3756</v>
+        <v>-0.0147</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0479</v>
+        <v>-0.0147</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.3277</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0479</v>
+        <v>-0.0147</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0479</v>
+        <v>-0.0147</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.3277</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L47" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.3756</v>
+        <v>-0.0147</v>
       </c>
       <c r="N47" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4137</v>
+        <v>-0.0503</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2552</v>
+        <v>-0.031</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6087</v>
+        <v>-0.6607</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.4137</v>
+        <v>-0.0503</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.4137</v>
+        <v>0.2129</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.2632</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.4137</v>
+        <v>0.2129</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4137</v>
+        <v>0.2129</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.2632</v>
       </c>
       <c r="K48" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.4137</v>
+        <v>-0.05029999999999998</v>
       </c>
       <c r="N48" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4335</v>
+        <v>-0.0542</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2674</v>
+        <v>-0.0334</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6166</v>
+        <v>-0.6625</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.4335</v>
+        <v>-0.0542</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4335</v>
+        <v>0.2803</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.3345</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4335</v>
+        <v>0.2803</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4335</v>
+        <v>0.2803</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.3345</v>
       </c>
       <c r="K49" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.4335</v>
+        <v>-0.05420000000000003</v>
       </c>
       <c r="N49" t="n">
-        <v>149</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5295</v>
+        <v>-0.0578</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7859</v>
+        <v>-0.6803</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2983</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5601</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2983</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2983</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5601</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="L50" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>229</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.5686</v>
+        <v>-0.211</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8112</v>
+        <v>-0.7925</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="N51" t="n">
         <v>134</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>spyleadeR</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.1101</v>
+        <v>-0.5129</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.6847</v>
+        <v>-0.3164</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8862</v>
+        <v>-0.8696</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1101</v>
+        <v>-0.5129</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.1101</v>
+        <v>0.2917</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.8046</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.1101</v>
+        <v>0.2917</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.1101</v>
+        <v>0.2917</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.8046</v>
       </c>
       <c r="K52" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.1101</v>
+        <v>-0.5128999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>spyleadeR</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.696</v>
+        <v>-0.4582</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8935</v>
+        <v>-0.9734</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="G53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="J53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.1284</v>
+        <v>-0.7429</v>
       </c>
       <c r="N53" t="n">
-        <v>176</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.7262</v>
+        <v>-0.5598</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9129</v>
+        <v>-1.0477</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.1773</v>
+        <v>-0.9075</v>
       </c>
       <c r="N54" t="n">
         <v>137</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.9306</v>
+        <v>-0.6486</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.045</v>
+        <v>-1.1127</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.5087</v>
+        <v>-1.0515</v>
       </c>
       <c r="N55" t="n">
         <v>108</v>
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.7387</v>
+        <v>-1.4344</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.0724</v>
+        <v>-0.8847</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1366</v>
+        <v>-1.2856</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.7387</v>
+        <v>-1.4344</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.5738</v>
+        <v>-1.6007</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1649</v>
+        <v>0.1663</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.5738</v>
+        <v>-1.6007</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.2756</v>
+        <v>-0.8323</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1649</v>
+        <v>0.1663</v>
       </c>
       <c r="K56" t="n">
         <v>136</v>
@@ -3013,7 +3013,7 @@
         <v>158</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.4405</v>
+        <v>-0.666</v>
       </c>
       <c r="N56" t="n">
         <v>294</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.2688</v>
+        <v>-0.9777</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.2634</v>
+        <v>-1.3536</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-2.057</v>
+        <v>-1.5851</v>
       </c>
       <c r="N57" t="n">
         <v>137</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.6801</v>
+        <v>-1.1651</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.5291</v>
+        <v>-1.4908</v>
       </c>
       <c r="E58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.7238</v>
+        <v>-1.8889</v>
       </c>
       <c r="N58" t="n">
         <v>108</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.7778</v>
+        <v>-1.2317</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.5922</v>
+        <v>-1.5395</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.8822</v>
+        <v>-1.9969</v>
       </c>
       <c r="N59" t="n">
         <v>108</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.8698</v>
+        <v>-1.3237</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.6516</v>
+        <v>-1.6068</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="I60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.0314</v>
+        <v>-2.146</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.9605</v>
+        <v>-1.3691</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.7102</v>
+        <v>-1.6401</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-3.1785</v>
+        <v>-2.2197</v>
       </c>
       <c r="N61" t="n">
         <v>108</v>
@@ -3349,10 +3349,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4886</v>
+        <v>0.5764</v>
       </c>
       <c r="J2" t="n">
-        <v>17.5896</v>
+        <v>20.7504</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.21</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3924</v>
+        <v>0.4519</v>
       </c>
       <c r="J3" t="n">
-        <v>14.1264</v>
+        <v>16.2684</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1482</v>
+        <v>0.1585</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3352</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0994</v>
+        <v>-0.0515</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.5784</v>
+        <v>-1.854</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6958</v>
+        <v>-0.4671</v>
       </c>
       <c r="J6" t="n">
-        <v>-25.0488</v>
+        <v>-16.8156</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0489</v>
+        <v>1.0231</v>
       </c>
       <c r="J7" t="n">
-        <v>37.7604</v>
+        <v>36.8316</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7341</v>
+        <v>0.7187</v>
       </c>
       <c r="J8" t="n">
-        <v>26.4276</v>
+        <v>25.8732</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5834</v>
+        <v>0.5728</v>
       </c>
       <c r="J9" t="n">
-        <v>21.0024</v>
+        <v>20.6208</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2368</v>
+        <v>-0.1655</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.524800000000001</v>
+        <v>-5.958</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5893</v>
+        <v>-0.5269</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.2148</v>
+        <v>-18.9684</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1076</v>
+        <v>-0.1111</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0444</v>
+        <v>-2.1109</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.19</v>
+        <v>-0.1676</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.61</v>
+        <v>-3.1844</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3356</v>
+        <v>-0.2602</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.3764</v>
+        <v>-4.9438</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5463</v>
+        <v>-0.3702</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.3797</v>
+        <v>-7.0338</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.42</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8127</v>
+        <v>-0.5572</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.4413</v>
+        <v>-10.5868</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4557</v>
+        <v>1.3062</v>
       </c>
       <c r="J17" t="n">
-        <v>27.6583</v>
+        <v>24.8178</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2641</v>
+        <v>1.1876</v>
       </c>
       <c r="J18" t="n">
-        <v>24.0179</v>
+        <v>22.5644</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0582</v>
+        <v>1.0672</v>
       </c>
       <c r="J19" t="n">
-        <v>20.1058</v>
+        <v>20.2768</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3911</v>
+        <v>0.4943</v>
       </c>
       <c r="J20" t="n">
-        <v>7.4309</v>
+        <v>9.3917</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2156</v>
+        <v>0.3116</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0964</v>
+        <v>5.9204</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3381</v>
+        <v>0.3817</v>
       </c>
       <c r="J22" t="n">
-        <v>11.4954</v>
+        <v>12.9778</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.323</v>
+        <v>0.3629</v>
       </c>
       <c r="J23" t="n">
-        <v>10.982</v>
+        <v>12.3386</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1126</v>
+        <v>0.1153</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8284</v>
+        <v>3.9202</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3101</v>
+        <v>-0.1884</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.5434</v>
+        <v>-6.4056</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3845</v>
+        <v>-0.2395</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.073</v>
+        <v>-8.143000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9127</v>
+        <v>0.8955</v>
       </c>
       <c r="J27" t="n">
-        <v>31.0318</v>
+        <v>30.447</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5768</v>
+        <v>0.5562</v>
       </c>
       <c r="J28" t="n">
-        <v>19.6112</v>
+        <v>18.9108</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4674</v>
+        <v>0.454</v>
       </c>
       <c r="J29" t="n">
-        <v>15.8916</v>
+        <v>15.436</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1992</v>
+        <v>0.237</v>
       </c>
       <c r="J30" t="n">
-        <v>6.7728</v>
+        <v>8.058</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7285</v>
+        <v>-0.6772</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.769</v>
+        <v>-23.0248</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3972</v>
+        <v>0.4061</v>
       </c>
       <c r="J32" t="n">
-        <v>8.7384</v>
+        <v>8.934200000000001</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1919</v>
+        <v>0.2045</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2218</v>
+        <v>4.499</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1544</v>
+        <v>0.1613</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3968</v>
+        <v>3.5486</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.175</v>
+        <v>-0.1002</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.85</v>
+        <v>-2.2044</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.481</v>
+        <v>-0.3078</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.582</v>
+        <v>-6.7716</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.95</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9046</v>
+        <v>1.4327</v>
       </c>
       <c r="J37" t="n">
-        <v>41.9012</v>
+        <v>31.5194</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3085</v>
+        <v>0.3513</v>
       </c>
       <c r="J38" t="n">
-        <v>6.787</v>
+        <v>7.7286</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0949</v>
+        <v>0.1587</v>
       </c>
       <c r="J39" t="n">
-        <v>2.0878</v>
+        <v>3.4914</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4957</v>
+        <v>-0.4257</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.9054</v>
+        <v>-9.365399999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5095</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.6522</v>
+        <v>-11.209</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6047</v>
+        <v>0.4462</v>
       </c>
       <c r="J42" t="n">
-        <v>16.9316</v>
+        <v>12.4936</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3069</v>
+        <v>0.2564</v>
       </c>
       <c r="J43" t="n">
-        <v>8.5932</v>
+        <v>7.1792</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0169</v>
+        <v>0.0378</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4732</v>
+        <v>1.0584</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1242</v>
+        <v>-0.059</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.4776</v>
+        <v>-1.652</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.252</v>
+        <v>-0.1441</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.056</v>
+        <v>-4.0348</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5017</v>
+        <v>0.4066</v>
       </c>
       <c r="J47" t="n">
-        <v>14.0476</v>
+        <v>11.3848</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1259</v>
+        <v>0.1166</v>
       </c>
       <c r="J48" t="n">
-        <v>3.5252</v>
+        <v>3.2648</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0765</v>
+        <v>0.083</v>
       </c>
       <c r="J49" t="n">
-        <v>2.142</v>
+        <v>2.324</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1548</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.3344</v>
+        <v>-2.2876</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.93</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1921</v>
+        <v>-0.106</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.3788</v>
+        <v>-2.968</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I52" t="n">
-        <v>0.316</v>
+        <v>0.3326</v>
       </c>
       <c r="J52" t="n">
-        <v>7.268</v>
+        <v>7.6498</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.02</v>
+        <v>-0.0482</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.46</v>
+        <v>-1.1086</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.243</v>
+        <v>-0.1973</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.589</v>
+        <v>-4.5379</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7341</v>
+        <v>-0.498</v>
       </c>
       <c r="J55" t="n">
-        <v>-16.8843</v>
+        <v>-11.454</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8919</v>
+        <v>-0.6182</v>
       </c>
       <c r="J56" t="n">
-        <v>-20.5137</v>
+        <v>-14.2186</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.98</v>
       </c>
       <c r="I57" t="n">
-        <v>1.892</v>
+        <v>1.4122</v>
       </c>
       <c r="J57" t="n">
-        <v>43.516</v>
+        <v>32.4806</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.49</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1395</v>
+        <v>0.8289</v>
       </c>
       <c r="J58" t="n">
-        <v>26.2085</v>
+        <v>19.0647</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3436</v>
+        <v>0.3934</v>
       </c>
       <c r="J59" t="n">
-        <v>7.9028</v>
+        <v>9.0482</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0384</v>
+        <v>0.1218</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8832</v>
+        <v>2.8014</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3328</v>
+        <v>-0.2474</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.6544</v>
+        <v>-5.6902</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7302</v>
+        <v>0.548</v>
       </c>
       <c r="J62" t="n">
-        <v>29.9382</v>
+        <v>22.468</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.21</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6564</v>
+        <v>0.5037</v>
       </c>
       <c r="J63" t="n">
-        <v>26.9124</v>
+        <v>20.6517</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5533</v>
+        <v>0.4432</v>
       </c>
       <c r="J64" t="n">
-        <v>22.6853</v>
+        <v>18.1712</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.506</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.083</v>
+        <v>-20.746</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6147</v>
+        <v>-0.5598</v>
       </c>
       <c r="J66" t="n">
-        <v>-25.2027</v>
+        <v>-22.9518</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5702</v>
+        <v>0.5405</v>
       </c>
       <c r="J67" t="n">
-        <v>23.3782</v>
+        <v>22.1605</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.043</v>
+        <v>-0.0208</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.763</v>
+        <v>-0.8528</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0941</v>
+        <v>-0.0504</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.8581</v>
+        <v>-2.0664</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1162</v>
+        <v>-0.0636</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.7642</v>
+        <v>-2.6076</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.0728</v>
+        <v>-11.439</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.7229</v>
+        <v>1.2102</v>
       </c>
       <c r="J72" t="n">
-        <v>48.2412</v>
+        <v>33.8856</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5471</v>
+        <v>0.4685</v>
       </c>
       <c r="J73" t="n">
-        <v>15.3188</v>
+        <v>13.118</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3599</v>
+        <v>0.3815</v>
       </c>
       <c r="J74" t="n">
-        <v>10.0772</v>
+        <v>10.682</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2553</v>
+        <v>-0.178</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.1484</v>
+        <v>-4.984</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6286</v>
+        <v>-0.5661</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.6008</v>
+        <v>-15.8508</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.38</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6037</v>
       </c>
       <c r="J77" t="n">
-        <v>18.1636</v>
+        <v>16.9036</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1764</v>
+        <v>-0.1151</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.9392</v>
+        <v>-3.2228</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3477</v>
+        <v>-0.2196</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.7356</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.3988</v>
+        <v>-7.2604</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4497</v>
+        <v>-0.2886</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.5916</v>
+        <v>-8.0808</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.83</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6985</v>
+        <v>1.1999</v>
       </c>
       <c r="J82" t="n">
-        <v>35.6685</v>
+        <v>25.1979</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.58</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2397</v>
+        <v>0.9132</v>
       </c>
       <c r="J83" t="n">
-        <v>26.0337</v>
+        <v>19.1772</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.58</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2397</v>
+        <v>0.9132</v>
       </c>
       <c r="J84" t="n">
-        <v>26.0337</v>
+        <v>19.1772</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>11.4849</v>
+        <v>11.1447</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4338</v>
+        <v>0.4607</v>
       </c>
       <c r="J86" t="n">
-        <v>9.1098</v>
+        <v>9.6747</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.63</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.4045</v>
+        <v>-0.3289</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.4945</v>
+        <v>-6.9069</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.4357</v>
+        <v>-0.3492</v>
       </c>
       <c r="J88" t="n">
-        <v>-9.149699999999999</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5533</v>
+        <v>-0.4161</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.6193</v>
+        <v>-8.738099999999999</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.49</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6555</v>
+        <v>-0.4599</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.7655</v>
+        <v>-9.6579</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.5748</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.4762</v>
+        <v>-12.0708</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>2.01</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9273</v>
+        <v>1.4573</v>
       </c>
       <c r="J92" t="n">
-        <v>46.2552</v>
+        <v>34.9752</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4581</v>
+        <v>0.4568</v>
       </c>
       <c r="J93" t="n">
-        <v>10.9944</v>
+        <v>10.9632</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4581</v>
+        <v>0.4568</v>
       </c>
       <c r="J94" t="n">
-        <v>10.9944</v>
+        <v>10.9632</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2777</v>
+        <v>0.3509</v>
       </c>
       <c r="J95" t="n">
-        <v>6.6648</v>
+        <v>8.4216</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3877</v>
+        <v>-0.3057</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.3048</v>
+        <v>-7.3368</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3412</v>
+        <v>0.3581</v>
       </c>
       <c r="J97" t="n">
-        <v>8.188800000000001</v>
+        <v>8.5944</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.108</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>2.592</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2637</v>
+        <v>-0.1673</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3288</v>
+        <v>-4.0152</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2805</v>
+        <v>-0.1777</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.732</v>
+        <v>-4.2648</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5289</v>
+        <v>-0.3447</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.6936</v>
+        <v>-8.2728</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.85</v>
       </c>
       <c r="I102" t="n">
-        <v>1.804</v>
+        <v>1.3026</v>
       </c>
       <c r="J102" t="n">
-        <v>46.904</v>
+        <v>33.8676</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7454</v>
+        <v>0.5778</v>
       </c>
       <c r="J103" t="n">
-        <v>19.3804</v>
+        <v>15.0228</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.18</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4645</v>
+        <v>0.4394</v>
       </c>
       <c r="J104" t="n">
-        <v>12.077</v>
+        <v>11.4244</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3278</v>
+        <v>-0.2499</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.5228</v>
+        <v>-6.4974</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.73</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8894</v>
+        <v>-0.8509</v>
       </c>
       <c r="J106" t="n">
-        <v>-23.1244</v>
+        <v>-22.1234</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5661</v>
+        <v>0.536</v>
       </c>
       <c r="J107" t="n">
-        <v>14.7186</v>
+        <v>13.936</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0009</v>
+        <v>-0.0157</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.0234</v>
+        <v>-0.4082</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.3732</v>
+        <v>-2.7508</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2753</v>
+        <v>-0.1707</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.1578</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.612</v>
+        <v>-0.4045</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.912</v>
+        <v>-10.517</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6523</v>
+        <v>0.4972</v>
       </c>
       <c r="J112" t="n">
-        <v>22.1782</v>
+        <v>16.9048</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3048</v>
+        <v>0.2676</v>
       </c>
       <c r="J113" t="n">
-        <v>10.3632</v>
+        <v>9.0984</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0309</v>
+        <v>0.0452</v>
       </c>
       <c r="J114" t="n">
-        <v>1.0506</v>
+        <v>1.5368</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2433</v>
+        <v>-0.1402</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.2722</v>
+        <v>-4.7668</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4369</v>
+        <v>-0.2748</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.8546</v>
+        <v>-9.3432</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.29</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4985</v>
+        <v>0.3849</v>
       </c>
       <c r="J117" t="n">
-        <v>16.949</v>
+        <v>13.0866</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2839</v>
+        <v>0.227</v>
       </c>
       <c r="J118" t="n">
-        <v>9.6526</v>
+        <v>7.718</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1228</v>
+        <v>0.0958</v>
       </c>
       <c r="J119" t="n">
-        <v>4.1752</v>
+        <v>3.2572</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3458</v>
+        <v>-0.2116</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.7572</v>
+        <v>-7.1944</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3605</v>
+        <v>-0.2218</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.257</v>
+        <v>-7.5412</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2321</v>
+        <v>0.8727</v>
       </c>
       <c r="J122" t="n">
-        <v>35.7309</v>
+        <v>25.3083</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.34</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8949</v>
+        <v>0.6623</v>
       </c>
       <c r="J123" t="n">
-        <v>25.9521</v>
+        <v>19.2067</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8496</v>
+        <v>0.6353</v>
       </c>
       <c r="J124" t="n">
-        <v>24.6384</v>
+        <v>18.4237</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4421</v>
+        <v>-0.3692</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.8209</v>
+        <v>-10.7068</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6523</v>
+        <v>-0.5918</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.9167</v>
+        <v>-17.1622</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5205</v>
+        <v>0.499</v>
       </c>
       <c r="J127" t="n">
-        <v>15.0945</v>
+        <v>14.471</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.22</v>
       </c>
       <c r="I128" t="n">
-        <v>0.439</v>
+        <v>0.4342</v>
       </c>
       <c r="J128" t="n">
-        <v>12.731</v>
+        <v>12.5918</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J129" t="n">
-        <v>-11.8204</v>
+        <v>-7.5284</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5315</v>
+        <v>-0.3462</v>
       </c>
       <c r="J130" t="n">
-        <v>-15.4135</v>
+        <v>-10.0398</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5446</v>
+        <v>-0.3556</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.7934</v>
+        <v>-10.3124</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.46</v>
+        <v>0.5441</v>
       </c>
       <c r="J132" t="n">
-        <v>18.86</v>
+        <v>22.3081</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2371</v>
+        <v>0.2723</v>
       </c>
       <c r="J133" t="n">
-        <v>9.7211</v>
+        <v>11.1643</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.144</v>
+        <v>0.1726</v>
       </c>
       <c r="J134" t="n">
-        <v>5.904</v>
+        <v>7.0766</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0274</v>
+        <v>0.0578</v>
       </c>
       <c r="J135" t="n">
-        <v>1.1234</v>
+        <v>2.3698</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3537</v>
+        <v>-0.2156</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.5017</v>
+        <v>-8.839600000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1088</v>
+        <v>1.0586</v>
       </c>
       <c r="J137" t="n">
-        <v>45.4608</v>
+        <v>43.4026</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2837</v>
+        <v>0.2524</v>
       </c>
       <c r="J138" t="n">
-        <v>11.6317</v>
+        <v>10.3484</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2525</v>
+        <v>-0.2041</v>
       </c>
       <c r="J139" t="n">
-        <v>-10.3525</v>
+        <v>-8.3681</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4952</v>
+        <v>-0.4413</v>
       </c>
       <c r="J140" t="n">
-        <v>-20.3032</v>
+        <v>-18.0933</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5757</v>
+        <v>-0.5232</v>
       </c>
       <c r="J141" t="n">
-        <v>-23.6037</v>
+        <v>-21.4512</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7958</v>
+        <v>0.767</v>
       </c>
       <c r="J142" t="n">
-        <v>22.2824</v>
+        <v>21.476</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4927</v>
+        <v>0.4638</v>
       </c>
       <c r="J143" t="n">
-        <v>13.7956</v>
+        <v>12.9864</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3766</v>
+        <v>0.3561</v>
       </c>
       <c r="J144" t="n">
-        <v>10.5448</v>
+        <v>9.970800000000001</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1582</v>
+        <v>0.1831</v>
       </c>
       <c r="J145" t="n">
-        <v>4.4296</v>
+        <v>5.1268</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7652</v>
+        <v>-0.7186</v>
       </c>
       <c r="J146" t="n">
-        <v>-21.4256</v>
+        <v>-20.1208</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5682</v>
+        <v>0.6821</v>
       </c>
       <c r="J147" t="n">
-        <v>15.9096</v>
+        <v>19.0988</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1886</v>
+        <v>0.2027</v>
       </c>
       <c r="J148" t="n">
-        <v>5.2808</v>
+        <v>5.6756</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0968</v>
+        <v>-0.0509</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.7104</v>
+        <v>-1.4252</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1961</v>
+        <v>-0.1127</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.4908</v>
+        <v>-3.1556</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4692</v>
+        <v>-0.2991</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.1376</v>
+        <v>-8.3748</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6508</v>
+        <v>0.6014</v>
       </c>
       <c r="J152" t="n">
-        <v>18.8732</v>
+        <v>17.4406</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1724</v>
+        <v>0.1337</v>
       </c>
       <c r="J153" t="n">
-        <v>4.9996</v>
+        <v>3.8773</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1724</v>
+        <v>0.1337</v>
       </c>
       <c r="J154" t="n">
-        <v>4.9996</v>
+        <v>3.8773</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0456</v>
+        <v>-0.0514</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.3224</v>
+        <v>-1.4906</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9234</v>
+        <v>-0.8943</v>
       </c>
       <c r="J156" t="n">
-        <v>-26.7786</v>
+        <v>-25.9347</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.39</v>
+        <v>0.4631</v>
       </c>
       <c r="J157" t="n">
-        <v>11.31</v>
+        <v>13.4299</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3007</v>
+        <v>0.357</v>
       </c>
       <c r="J158" t="n">
-        <v>8.7203</v>
+        <v>10.353</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2165</v>
+        <v>0.2651</v>
       </c>
       <c r="J159" t="n">
-        <v>6.2785</v>
+        <v>7.6879</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1528</v>
+        <v>0.2082</v>
       </c>
       <c r="J160" t="n">
-        <v>4.4312</v>
+        <v>6.0378</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2222</v>
+        <v>-0.1231</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.4438</v>
+        <v>-3.5699</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0849</v>
+        <v>0.0437</v>
       </c>
       <c r="J162" t="n">
-        <v>2.1225</v>
+        <v>1.0925</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1466</v>
+        <v>-0.134</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.665</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2795</v>
+        <v>-0.2186</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.9875</v>
+        <v>-5.465</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.3588</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.395</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8094</v>
+        <v>-0.5544</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.235</v>
+        <v>-13.86</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1376</v>
+        <v>1.102</v>
       </c>
       <c r="J167" t="n">
-        <v>28.44</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9893</v>
+        <v>1.0091</v>
       </c>
       <c r="J168" t="n">
-        <v>24.7325</v>
+        <v>25.2275</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="J169" t="n">
-        <v>24.18</v>
+        <v>24.8225</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6615</v>
+        <v>0.7463</v>
       </c>
       <c r="J170" t="n">
-        <v>16.5375</v>
+        <v>18.6575</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0372</v>
+        <v>0.1209</v>
       </c>
       <c r="J171" t="n">
-        <v>0.93</v>
+        <v>3.0225</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0232</v>
+        <v>-0.0474</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.5336</v>
+        <v>-1.0902</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0614</v>
+        <v>-0.073</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.4122</v>
+        <v>-1.679</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4799</v>
+        <v>-0.3183</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.0377</v>
+        <v>-7.3209</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4799</v>
+        <v>-0.3183</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.0377</v>
+        <v>-7.3209</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4944</v>
+        <v>-0.3278</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.3712</v>
+        <v>-7.5394</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.84</v>
       </c>
       <c r="I177" t="n">
-        <v>1.797</v>
+        <v>1.5256</v>
       </c>
       <c r="J177" t="n">
-        <v>41.331</v>
+        <v>35.0888</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.5</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1639</v>
+        <v>1.1164</v>
       </c>
       <c r="J178" t="n">
-        <v>26.7697</v>
+        <v>25.6772</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6194</v>
+        <v>0.7032</v>
       </c>
       <c r="J179" t="n">
-        <v>14.2462</v>
+        <v>16.1736</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1555</v>
       </c>
       <c r="J180" t="n">
-        <v>1.656</v>
+        <v>3.5765</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4234</v>
+        <v>-0.3423</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.738200000000001</v>
+        <v>-7.8729</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.502</v>
+        <v>0.588</v>
       </c>
       <c r="J182" t="n">
-        <v>12.55</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0576</v>
+        <v>-0.0621</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.44</v>
+        <v>-1.5525</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2579</v>
+        <v>-0.1728</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.4475</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5042</v>
+        <v>-0.3292</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.605</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6355</v>
+        <v>-0.423</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.8875</v>
+        <v>-10.575</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4331</v>
+        <v>1.2859</v>
       </c>
       <c r="J187" t="n">
-        <v>35.8275</v>
+        <v>32.1475</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9695</v>
+        <v>0.9936</v>
       </c>
       <c r="J188" t="n">
-        <v>24.2375</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9695</v>
+        <v>0.9936</v>
       </c>
       <c r="J189" t="n">
-        <v>24.2375</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4683</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>11.7075</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2989</v>
+        <v>-0.2125</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.4725</v>
+        <v>-5.3125</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.63</v>
+        <v>0.7795</v>
       </c>
       <c r="J192" t="n">
-        <v>13.23</v>
+        <v>16.3695</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1672</v>
+        <v>-0.1468</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.5112</v>
+        <v>-3.0828</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.79</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2842</v>
+        <v>-0.2198</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.9682</v>
+        <v>-4.6158</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.41</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.8349</v>
+        <v>-0.5739</v>
       </c>
       <c r="J195" t="n">
-        <v>-17.5329</v>
+        <v>-12.0519</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.39</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8587</v>
+        <v>-0.5923</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.0327</v>
+        <v>-12.4383</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5406</v>
+        <v>1.3654</v>
       </c>
       <c r="J197" t="n">
-        <v>32.3526</v>
+        <v>28.6734</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>0.96</v>
+        <v>1.0369</v>
       </c>
       <c r="J198" t="n">
-        <v>20.16</v>
+        <v>21.7749</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.43</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.0086</v>
       </c>
       <c r="J199" t="n">
-        <v>19.1688</v>
+        <v>21.1806</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.8675</v>
+        <v>0.9761</v>
       </c>
       <c r="J200" t="n">
-        <v>18.2175</v>
+        <v>20.4981</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.3</v>
       </c>
       <c r="I201" t="n">
-        <v>0.6243</v>
+        <v>0.7433</v>
       </c>
       <c r="J201" t="n">
-        <v>13.1103</v>
+        <v>15.6093</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.26</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7064</v>
+        <v>0.7053</v>
       </c>
       <c r="J202" t="n">
-        <v>19.7792</v>
+        <v>19.7484</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7064</v>
+        <v>0.7053</v>
       </c>
       <c r="J203" t="n">
-        <v>19.7792</v>
+        <v>19.7484</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6042</v>
+        <v>0.6105</v>
       </c>
       <c r="J204" t="n">
-        <v>16.9176</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3325</v>
+        <v>0.3886</v>
       </c>
       <c r="J205" t="n">
-        <v>9.31</v>
+        <v>10.8808</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0576</v>
+        <v>0.1237</v>
       </c>
       <c r="J206" t="n">
-        <v>1.6128</v>
+        <v>3.4636</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6922</v>
+        <v>0.8531</v>
       </c>
       <c r="J207" t="n">
-        <v>19.3816</v>
+        <v>23.8868</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.89</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.2076</v>
+        <v>-3.8696</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.2076</v>
+        <v>-3.8696</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.352</v>
+        <v>-0.2213</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.856</v>
+        <v>-6.1964</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.67</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5471</v>
+        <v>-0.3571</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.3188</v>
+        <v>-9.998799999999999</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4758</v>
+        <v>0.5536</v>
       </c>
       <c r="J212" t="n">
-        <v>9.9918</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0154</v>
+        <v>-0.0211</v>
       </c>
       <c r="J213" t="n">
-        <v>0.3234</v>
+        <v>-0.4431</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.66</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3475</v>
       </c>
       <c r="J214" t="n">
-        <v>-11.0187</v>
+        <v>-7.2975</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.65</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5386</v>
+        <v>-0.3569</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.3106</v>
+        <v>-7.4949</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7579</v>
+        <v>-0.515</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.9159</v>
+        <v>-10.815</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.98</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9713</v>
+        <v>1.6707</v>
       </c>
       <c r="J217" t="n">
-        <v>41.3973</v>
+        <v>35.0847</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8881</v>
+        <v>0.95</v>
       </c>
       <c r="J218" t="n">
-        <v>18.6501</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.26</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5659</v>
+        <v>0.6683</v>
       </c>
       <c r="J219" t="n">
-        <v>11.8839</v>
+        <v>14.0343</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.24</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5189</v>
+        <v>0.6212</v>
       </c>
       <c r="J220" t="n">
-        <v>10.8969</v>
+        <v>13.0452</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0422</v>
+        <v>0.0423</v>
       </c>
       <c r="J221" t="n">
-        <v>-0.8862</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7809</v>
+        <v>0.7567</v>
       </c>
       <c r="J222" t="n">
-        <v>27.3315</v>
+        <v>26.4845</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7091</v>
+        <v>0.6836</v>
       </c>
       <c r="J223" t="n">
-        <v>24.8185</v>
+        <v>23.926</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.1</v>
       </c>
       <c r="I224" t="n">
-        <v>0.319</v>
+        <v>0.3235</v>
       </c>
       <c r="J224" t="n">
-        <v>11.165</v>
+        <v>11.3225</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0653</v>
+        <v>0.1105</v>
       </c>
       <c r="J225" t="n">
-        <v>2.2855</v>
+        <v>3.8675</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6019</v>
+        <v>-0.5431</v>
       </c>
       <c r="J226" t="n">
-        <v>-21.0665</v>
+        <v>-19.0085</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3119</v>
+        <v>0.3473</v>
       </c>
       <c r="J227" t="n">
-        <v>10.9165</v>
+        <v>12.1555</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.231</v>
+        <v>0.2484</v>
       </c>
       <c r="J228" t="n">
-        <v>8.085000000000001</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1587</v>
+        <v>0.1635</v>
       </c>
       <c r="J229" t="n">
-        <v>5.5545</v>
+        <v>5.7225</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2253</v>
+        <v>-0.1334</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.8855</v>
+        <v>-4.669</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.452</v>
+        <v>-0.2874</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.82</v>
+        <v>-10.059</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.407</v>
+        <v>0.4659</v>
       </c>
       <c r="J232" t="n">
-        <v>12.21</v>
+        <v>13.977</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1262</v>
+        <v>0.1215</v>
       </c>
       <c r="J233" t="n">
-        <v>3.786</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.96</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1013</v>
+        <v>-0.0609</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.039</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2364</v>
+        <v>-0.1424</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.092</v>
+        <v>-4.272</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.77</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4203</v>
+        <v>-0.2657</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.609</v>
+        <v>-7.971</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1098</v>
+        <v>1.0653</v>
       </c>
       <c r="J237" t="n">
-        <v>33.294</v>
+        <v>31.959</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>1.004</v>
+        <v>0.9879</v>
       </c>
       <c r="J238" t="n">
-        <v>30.12</v>
+        <v>29.637</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1117</v>
+        <v>0.1671</v>
       </c>
       <c r="J239" t="n">
-        <v>3.351</v>
+        <v>5.013</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.307</v>
+        <v>-0.2349</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.210000000000001</v>
+        <v>-7.047</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.89</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4847</v>
+        <v>-0.4168</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.541</v>
+        <v>-12.504</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4823</v>
+        <v>0.5609</v>
       </c>
       <c r="J242" t="n">
-        <v>13.9867</v>
+        <v>16.2661</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0605</v>
+        <v>0.0261</v>
       </c>
       <c r="J243" t="n">
-        <v>1.7545</v>
+        <v>0.7569</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1047</v>
+        <v>-0.089</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.0363</v>
+        <v>-2.581</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5748</v>
+        <v>-0.3785</v>
       </c>
       <c r="J245" t="n">
-        <v>-16.6692</v>
+        <v>-10.9765</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.626</v>
+        <v>-0.4158</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.154</v>
+        <v>-12.0582</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.64</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4745</v>
+        <v>1.3075</v>
       </c>
       <c r="J247" t="n">
-        <v>42.7605</v>
+        <v>37.9175</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9742</v>
+        <v>0.9779</v>
       </c>
       <c r="J248" t="n">
-        <v>28.2518</v>
+        <v>28.3591</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.13</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3024</v>
+        <v>0.3761</v>
       </c>
       <c r="J249" t="n">
-        <v>8.769600000000001</v>
+        <v>10.9069</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="J250" t="n">
-        <v>0.0174</v>
+        <v>2.1779</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1367</v>
+        <v>-0.058</v>
       </c>
       <c r="J251" t="n">
-        <v>-3.9643</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>0.9</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1004</v>
       </c>
       <c r="J252" t="n">
-        <v>-2.1362</v>
+        <v>-2.2088</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1986</v>
+        <v>-0.1677</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.3692</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3346</v>
+        <v>-0.2481</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.3612</v>
+        <v>-5.4582</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.73</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.398</v>
+        <v>-0.2753</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.756</v>
+        <v>-6.0566</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.51</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7111</v>
+        <v>-0.4809</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.6442</v>
+        <v>-10.5798</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.7166</v>
+        <v>1.4723</v>
       </c>
       <c r="J257" t="n">
-        <v>37.7652</v>
+        <v>32.3906</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9603</v>
+        <v>0.9908</v>
       </c>
       <c r="J258" t="n">
-        <v>21.1266</v>
+        <v>21.7976</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.38</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8912</v>
+        <v>0.9359</v>
       </c>
       <c r="J259" t="n">
-        <v>19.6064</v>
+        <v>20.5898</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7033</v>
+        <v>0.7887</v>
       </c>
       <c r="J260" t="n">
-        <v>15.4726</v>
+        <v>17.3514</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7136</v>
+        <v>-0.6548</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.6992</v>
+        <v>-14.4056</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.271</v>
+        <v>0.2938</v>
       </c>
       <c r="J262" t="n">
-        <v>7.317</v>
+        <v>7.9326</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="J263" t="n">
-        <v>2.1924</v>
+        <v>1.9089</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>0.019</v>
+        <v>0.0035</v>
       </c>
       <c r="J264" t="n">
-        <v>0.513</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.9</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2191</v>
+        <v>-0.1314</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.9157</v>
+        <v>-3.5478</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.83</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3326</v>
+        <v>-0.2056</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.9802</v>
+        <v>-5.5512</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.6</v>
       </c>
       <c r="I267" t="n">
-        <v>1.431</v>
+        <v>1.2763</v>
       </c>
       <c r="J267" t="n">
-        <v>38.637</v>
+        <v>34.4601</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7369</v>
+        <v>0.7316</v>
       </c>
       <c r="J268" t="n">
-        <v>19.8963</v>
+        <v>19.7532</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.7126</v>
+        <v>0.708</v>
       </c>
       <c r="J269" t="n">
-        <v>19.2402</v>
+        <v>19.116</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0114</v>
+        <v>0.0544</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.3078</v>
+        <v>1.4688</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.71</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.9278</v>
+        <v>-0.8939</v>
       </c>
       <c r="J271" t="n">
-        <v>-25.0506</v>
+        <v>-24.1353</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I272" t="n">
-        <v>0.0046</v>
+        <v>-0.0325</v>
       </c>
       <c r="J272" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.6825</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.184</v>
+        <v>-0.1646</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.864</v>
+        <v>-3.4566</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.6</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.5705</v>
+        <v>-0.3869</v>
       </c>
       <c r="J274" t="n">
-        <v>-11.9805</v>
+        <v>-8.1249</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.57</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.4149</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.8814</v>
+        <v>-8.712899999999999</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7212</v>
+        <v>-0.4898</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.1452</v>
+        <v>-10.2858</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.74</v>
       </c>
       <c r="I277" t="n">
-        <v>1.5655</v>
+        <v>1.3798</v>
       </c>
       <c r="J277" t="n">
-        <v>32.8755</v>
+        <v>28.9758</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.62</v>
       </c>
       <c r="I278" t="n">
-        <v>1.3415</v>
+        <v>1.2401</v>
       </c>
       <c r="J278" t="n">
-        <v>28.1715</v>
+        <v>26.0421</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.61</v>
       </c>
       <c r="I279" t="n">
-        <v>1.3222</v>
+        <v>1.2284</v>
       </c>
       <c r="J279" t="n">
-        <v>27.7662</v>
+        <v>25.7964</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1.22</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4481</v>
+        <v>0.5589</v>
       </c>
       <c r="J280" t="n">
-        <v>9.4101</v>
+        <v>11.7369</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>1.05</v>
       </c>
       <c r="I281" t="n">
-        <v>0.007</v>
+        <v>0.0959</v>
       </c>
       <c r="J281" t="n">
-        <v>0.147</v>
+        <v>2.0139</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.5</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2473</v>
+        <v>1.1546</v>
       </c>
       <c r="J282" t="n">
-        <v>44.9028</v>
+        <v>41.5656</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5188</v>
+        <v>0.5201</v>
       </c>
       <c r="J283" t="n">
-        <v>18.6768</v>
+        <v>18.7236</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.07</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1715</v>
+        <v>0.227</v>
       </c>
       <c r="J284" t="n">
-        <v>6.174</v>
+        <v>8.172000000000001</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1034</v>
+        <v>-0.0359</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.7224</v>
+        <v>-1.2924</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1034</v>
+        <v>-0.0359</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.7224</v>
+        <v>-1.2924</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.56</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8324</v>
+        <v>1.028</v>
       </c>
       <c r="J287" t="n">
-        <v>29.9664</v>
+        <v>37.008</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1935</v>
+        <v>0.2054</v>
       </c>
       <c r="J288" t="n">
-        <v>6.966</v>
+        <v>7.3944</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.93</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1736</v>
+        <v>-0.0998</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.2496</v>
+        <v>-3.5928</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4936</v>
+        <v>-0.317</v>
       </c>
       <c r="J290" t="n">
-        <v>-17.7696</v>
+        <v>-11.412</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5199</v>
+        <v>-0.336</v>
       </c>
       <c r="J291" t="n">
-        <v>-18.7164</v>
+        <v>-12.096</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3163</v>
+        <v>0.3509</v>
       </c>
       <c r="J292" t="n">
-        <v>9.172700000000001</v>
+        <v>10.1761</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2524</v>
+        <v>0.272</v>
       </c>
       <c r="J293" t="n">
-        <v>7.3196</v>
+        <v>7.888</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1441</v>
+        <v>0.1436</v>
       </c>
       <c r="J294" t="n">
-        <v>4.1789</v>
+        <v>4.1644</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2212</v>
+        <v>-0.132</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.4148</v>
+        <v>-3.828</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5296</v>
+        <v>-0.3434</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.3584</v>
+        <v>-9.958600000000001</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.51</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2775</v>
+        <v>1.1734</v>
       </c>
       <c r="J297" t="n">
-        <v>37.0475</v>
+        <v>34.0286</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5874</v>
+        <v>0.5744</v>
       </c>
       <c r="J298" t="n">
-        <v>17.0346</v>
+        <v>16.6576</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I299" t="n">
-        <v>0.448</v>
+        <v>0.4488</v>
       </c>
       <c r="J299" t="n">
-        <v>12.992</v>
+        <v>13.0152</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4535</v>
+        <v>-0.3854</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.1515</v>
+        <v>-11.1766</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4813</v>
+        <v>-0.4142</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.9577</v>
+        <v>-12.0118</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>1.6581</v>
+        <v>1.4362</v>
       </c>
       <c r="J302" t="n">
-        <v>36.4782</v>
+        <v>31.5964</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.146</v>
+        <v>1.1165</v>
       </c>
       <c r="J303" t="n">
-        <v>25.212</v>
+        <v>24.563</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.42</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9485</v>
+        <v>0.9994</v>
       </c>
       <c r="J304" t="n">
-        <v>20.867</v>
+        <v>21.9868</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I305" t="n">
-        <v>0.5119</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J305" t="n">
-        <v>11.2618</v>
+        <v>13.5828</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.0129</v>
+        <v>0.0732</v>
       </c>
       <c r="J306" t="n">
-        <v>-0.2838</v>
+        <v>1.6104</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.3</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6254</v>
+        <v>0.7758</v>
       </c>
       <c r="J307" t="n">
-        <v>13.7588</v>
+        <v>17.0676</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2573</v>
+        <v>-0.2069</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.6606</v>
+        <v>-4.5518</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.6022</v>
+        <v>-0.4041</v>
       </c>
       <c r="J309" t="n">
-        <v>-13.2484</v>
+        <v>-8.8902</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.5</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.7206</v>
+        <v>-0.4881</v>
       </c>
       <c r="J310" t="n">
-        <v>-15.8532</v>
+        <v>-10.7382</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.48</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7458</v>
+        <v>-0.5067</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.4076</v>
+        <v>-11.1474</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.46</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7081</v>
+        <v>0.8748</v>
       </c>
       <c r="J312" t="n">
-        <v>21.243</v>
+        <v>26.244</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.28</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4846</v>
+        <v>0.5722</v>
       </c>
       <c r="J313" t="n">
-        <v>14.538</v>
+        <v>17.166</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.87</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2851</v>
+        <v>-0.17</v>
       </c>
       <c r="J314" t="n">
-        <v>-8.553000000000001</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3755</v>
+        <v>-0.2322</v>
       </c>
       <c r="J315" t="n">
-        <v>-11.265</v>
+        <v>-6.966</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4991</v>
+        <v>-0.3203</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.973</v>
+        <v>-9.609</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.4</v>
       </c>
       <c r="I317" t="n">
-        <v>1.0788</v>
+        <v>1.0404</v>
       </c>
       <c r="J317" t="n">
-        <v>32.364</v>
+        <v>31.212</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.32</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.8831</v>
       </c>
       <c r="J318" t="n">
-        <v>27.141</v>
+        <v>26.493</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.02</v>
       </c>
       <c r="I319" t="n">
-        <v>0.0356</v>
+        <v>0.0776</v>
       </c>
       <c r="J319" t="n">
-        <v>1.068</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3139</v>
+        <v>-0.2509</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.417</v>
+        <v>-7.527</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8834</v>
+        <v>-0.8467</v>
       </c>
       <c r="J321" t="n">
-        <v>-26.502</v>
+        <v>-25.401</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.92</v>
       </c>
       <c r="I322" t="n">
-        <v>1.8726</v>
+        <v>1.5831</v>
       </c>
       <c r="J322" t="n">
-        <v>37.452</v>
+        <v>31.662</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.47</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0227</v>
+        <v>1.0619</v>
       </c>
       <c r="J323" t="n">
-        <v>20.454</v>
+        <v>21.238</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.33</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6931</v>
+        <v>0.8118</v>
       </c>
       <c r="J324" t="n">
-        <v>13.862</v>
+        <v>16.236</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.33</v>
       </c>
       <c r="I325" t="n">
-        <v>0.6931</v>
+        <v>0.8118</v>
       </c>
       <c r="J325" t="n">
-        <v>13.862</v>
+        <v>16.236</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4911</v>
+        <v>0.605</v>
       </c>
       <c r="J326" t="n">
-        <v>9.821999999999999</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9593</v>
+        <v>1.1788</v>
       </c>
       <c r="J327" t="n">
-        <v>19.186</v>
+        <v>23.576</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.5333</v>
+        <v>-0.3616</v>
       </c>
       <c r="J328" t="n">
-        <v>-10.666</v>
+        <v>-7.232</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4457</v>
       </c>
       <c r="J329" t="n">
-        <v>-13.196</v>
+        <v>-8.914</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.51</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.6995</v>
+        <v>-0.4737</v>
       </c>
       <c r="J330" t="n">
-        <v>-13.99</v>
+        <v>-9.474</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.27</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.6973</v>
       </c>
       <c r="J331" t="n">
-        <v>-19.828</v>
+        <v>-13.946</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4543</v>
+        <v>0.5298</v>
       </c>
       <c r="J332" t="n">
-        <v>13.1747</v>
+        <v>15.3642</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4268</v>
+        <v>0.494</v>
       </c>
       <c r="J333" t="n">
-        <v>12.3772</v>
+        <v>14.326</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1545</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.4805</v>
+        <v>-2.5491</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.79</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3975</v>
+        <v>-0.2488</v>
       </c>
       <c r="J335" t="n">
-        <v>-11.5275</v>
+        <v>-7.2152</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.78</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4116</v>
+        <v>-0.2587</v>
       </c>
       <c r="J336" t="n">
-        <v>-11.9364</v>
+        <v>-7.5023</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.25</v>
       </c>
       <c r="I337" t="n">
-        <v>0.699</v>
+        <v>0.6893</v>
       </c>
       <c r="J337" t="n">
-        <v>20.271</v>
+        <v>19.9897</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.23</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6491</v>
+        <v>0.6413</v>
       </c>
       <c r="J338" t="n">
-        <v>18.8239</v>
+        <v>18.5977</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4863</v>
+        <v>0.4946</v>
       </c>
       <c r="J339" t="n">
-        <v>14.1027</v>
+        <v>14.3434</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J340" t="n">
-        <v>9.335100000000001</v>
+        <v>10.6633</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1051</v>
+        <v>-0.0369</v>
       </c>
       <c r="J341" t="n">
-        <v>-3.0479</v>
+        <v>-1.0701</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.61</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3493</v>
+        <v>1.2381</v>
       </c>
       <c r="J342" t="n">
-        <v>29.6846</v>
+        <v>27.2382</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.53</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1918</v>
+        <v>1.1421</v>
       </c>
       <c r="J343" t="n">
-        <v>26.2196</v>
+        <v>25.1262</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.42</v>
       </c>
       <c r="I344" t="n">
-        <v>0.9556</v>
+        <v>1.0006</v>
       </c>
       <c r="J344" t="n">
-        <v>21.0232</v>
+        <v>22.0132</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.3</v>
       </c>
       <c r="I345" t="n">
-        <v>0.6555</v>
+        <v>0.7583</v>
       </c>
       <c r="J345" t="n">
-        <v>14.421</v>
+        <v>16.6826</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I346" t="n">
-        <v>0.1111</v>
+        <v>0.2013</v>
       </c>
       <c r="J346" t="n">
-        <v>2.4442</v>
+        <v>4.4286</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>0.76</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.2696</v>
+        <v>-0.227</v>
       </c>
       <c r="J347" t="n">
-        <v>-5.9312</v>
+        <v>-4.994</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3801</v>
+        <v>-0.2976</v>
       </c>
       <c r="J348" t="n">
-        <v>-8.3622</v>
+        <v>-6.5472</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.4132</v>
+        <v>-0.3166</v>
       </c>
       <c r="J349" t="n">
-        <v>-9.090400000000001</v>
+        <v>-6.9652</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.58</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.578</v>
+        <v>-0.3974</v>
       </c>
       <c r="J350" t="n">
-        <v>-12.716</v>
+        <v>-8.742800000000001</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7067</v>
+        <v>-0.4815</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.5474</v>
+        <v>-10.593</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5546</v>
+        <v>0.52</v>
       </c>
       <c r="J352" t="n">
-        <v>16.638</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4445</v>
+        <v>0.4139</v>
       </c>
       <c r="J353" t="n">
-        <v>13.335</v>
+        <v>12.417</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.12</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4155</v>
+        <v>0.3867</v>
       </c>
       <c r="J354" t="n">
-        <v>12.465</v>
+        <v>11.601</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.04</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1312</v>
+        <v>0.1532</v>
       </c>
       <c r="J355" t="n">
-        <v>3.936</v>
+        <v>4.596</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.614</v>
+        <v>-0.5592</v>
       </c>
       <c r="J356" t="n">
-        <v>-18.42</v>
+        <v>-16.776</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.48</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7199</v>
+        <v>0.8918</v>
       </c>
       <c r="J357" t="n">
-        <v>21.597</v>
+        <v>26.754</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2013</v>
+        <v>0.2329</v>
       </c>
       <c r="J358" t="n">
-        <v>6.039</v>
+        <v>6.987</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.03</v>
       </c>
       <c r="I359" t="n">
-        <v>0.05</v>
+        <v>0.0833</v>
       </c>
       <c r="J359" t="n">
-        <v>1.5</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1943</v>
+        <v>-0.1069</v>
       </c>
       <c r="J360" t="n">
-        <v>-5.829</v>
+        <v>-3.207</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.78</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.425</v>
+        <v>-0.2661</v>
       </c>
       <c r="J361" t="n">
-        <v>-12.75</v>
+        <v>-7.983</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.07</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2775</v>
+        <v>0.2846</v>
       </c>
       <c r="J362" t="n">
-        <v>6.105</v>
+        <v>6.2612</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.0424</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J363" t="n">
-        <v>-0.9328</v>
+        <v>-1.3904</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.7</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.4467</v>
+        <v>-0.3029</v>
       </c>
       <c r="J364" t="n">
-        <v>-9.827400000000001</v>
+        <v>-6.6638</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.58</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6194</v>
+        <v>-0.4153</v>
       </c>
       <c r="J365" t="n">
-        <v>-13.6268</v>
+        <v>-9.1366</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.45</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7855</v>
+        <v>-0.5362</v>
       </c>
       <c r="J366" t="n">
-        <v>-17.281</v>
+        <v>-11.7964</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.73</v>
       </c>
       <c r="I367" t="n">
-        <v>1.5883</v>
+        <v>1.3879</v>
       </c>
       <c r="J367" t="n">
-        <v>34.9426</v>
+        <v>30.5338</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.65</v>
       </c>
       <c r="I368" t="n">
-        <v>1.4412</v>
+        <v>1.2928</v>
       </c>
       <c r="J368" t="n">
-        <v>31.7064</v>
+        <v>28.4416</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.41</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9556</v>
+        <v>0.9895</v>
       </c>
       <c r="J369" t="n">
-        <v>21.0232</v>
+        <v>21.769</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.02</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.5708</v>
+        <v>0.2508</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3707</v>
+        <v>-0.286</v>
       </c>
       <c r="J371" t="n">
-        <v>-8.1554</v>
+        <v>-6.292</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.08</v>
       </c>
       <c r="I372" t="n">
-        <v>0.2023</v>
+        <v>0.2108</v>
       </c>
       <c r="J372" t="n">
-        <v>5.6644</v>
+        <v>5.9024</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.03</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1037</v>
+        <v>0.0965</v>
       </c>
       <c r="J373" t="n">
-        <v>2.9036</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0803</v>
+        <v>0.0703</v>
       </c>
       <c r="J374" t="n">
-        <v>2.2484</v>
+        <v>1.9684</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.2198</v>
+        <v>-0.1316</v>
       </c>
       <c r="J375" t="n">
-        <v>-6.1544</v>
+        <v>-3.6848</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.85</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3023</v>
+        <v>-0.1852</v>
       </c>
       <c r="J376" t="n">
-        <v>-8.464399999999999</v>
+        <v>-5.1856</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.77</v>
       </c>
       <c r="I377" t="n">
-        <v>1.7336</v>
+        <v>1.4812</v>
       </c>
       <c r="J377" t="n">
-        <v>48.5408</v>
+        <v>41.4736</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I378" t="n">
-        <v>0.749</v>
+        <v>0.7494</v>
       </c>
       <c r="J378" t="n">
-        <v>20.972</v>
+        <v>20.9832</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2402</v>
+        <v>0.3044</v>
       </c>
       <c r="J379" t="n">
-        <v>6.7256</v>
+        <v>8.523199999999999</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.97</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2582</v>
+        <v>-0.18</v>
       </c>
       <c r="J380" t="n">
-        <v>-7.2296</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.84</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.6308</v>
+        <v>-0.5681</v>
       </c>
       <c r="J381" t="n">
-        <v>-17.6624</v>
+        <v>-15.9068</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.82</v>
       </c>
       <c r="I382" t="n">
-        <v>1.6949</v>
+        <v>1.4654</v>
       </c>
       <c r="J382" t="n">
-        <v>35.5929</v>
+        <v>30.7734</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.74</v>
       </c>
       <c r="I383" t="n">
-        <v>1.5521</v>
+        <v>1.3741</v>
       </c>
       <c r="J383" t="n">
-        <v>32.5941</v>
+        <v>28.8561</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0248</v>
+        <v>1.0723</v>
       </c>
       <c r="J384" t="n">
-        <v>21.5208</v>
+        <v>22.5183</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.29</v>
       </c>
       <c r="I385" t="n">
-        <v>0.5966</v>
+        <v>0.7173</v>
       </c>
       <c r="J385" t="n">
-        <v>12.5286</v>
+        <v>15.0633</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.07</v>
       </c>
       <c r="I386" t="n">
-        <v>0.0595</v>
+        <v>0.152</v>
       </c>
       <c r="J386" t="n">
-        <v>1.2495</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.07</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2541</v>
+        <v>0.2543</v>
       </c>
       <c r="J387" t="n">
-        <v>5.3361</v>
+        <v>5.3403</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.97</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0128</v>
+        <v>-0.0225</v>
       </c>
       <c r="J388" t="n">
-        <v>0.2688</v>
+        <v>-0.4725</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.455</v>
+        <v>-0.301</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.555</v>
+        <v>-6.321</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.7</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4697</v>
+        <v>-0.3105</v>
       </c>
       <c r="J390" t="n">
-        <v>-9.8637</v>
+        <v>-6.5205</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.55</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.6722</v>
+        <v>-0.4512</v>
       </c>
       <c r="J391" t="n">
-        <v>-14.1162</v>
+        <v>-9.475199999999999</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>2.09</v>
       </c>
       <c r="I392" t="n">
-        <v>2.0482</v>
+        <v>1.7664</v>
       </c>
       <c r="J392" t="n">
-        <v>47.1086</v>
+        <v>40.6272</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.48</v>
       </c>
       <c r="I393" t="n">
-        <v>1.0185</v>
+        <v>1.0721</v>
       </c>
       <c r="J393" t="n">
-        <v>23.4255</v>
+        <v>24.6583</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.42</v>
       </c>
       <c r="I394" t="n">
-        <v>0.8793</v>
+        <v>0.9903</v>
       </c>
       <c r="J394" t="n">
-        <v>20.2239</v>
+        <v>22.7769</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>1.26</v>
       </c>
       <c r="I395" t="n">
-        <v>0.5283</v>
+        <v>0.6469</v>
       </c>
       <c r="J395" t="n">
-        <v>12.1509</v>
+        <v>14.8787</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>1.17</v>
       </c>
       <c r="I396" t="n">
-        <v>0.3192</v>
+        <v>0.427</v>
       </c>
       <c r="J396" t="n">
-        <v>7.3416</v>
+        <v>9.821</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>0.75</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.2605</v>
+        <v>-0.2245</v>
       </c>
       <c r="J397" t="n">
-        <v>-5.9915</v>
+        <v>-5.1635</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>0.64</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.4325</v>
+        <v>-0.3366</v>
       </c>
       <c r="J398" t="n">
-        <v>-9.9475</v>
+        <v>-7.7418</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.53</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.6314</v>
+        <v>-0.4357</v>
       </c>
       <c r="J399" t="n">
-        <v>-14.5222</v>
+        <v>-10.0211</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.53</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.6314</v>
+        <v>-0.4357</v>
       </c>
       <c r="J400" t="n">
-        <v>-14.5222</v>
+        <v>-10.0211</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.52</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.6465</v>
+        <v>-0.445</v>
       </c>
       <c r="J401" t="n">
-        <v>-14.8695</v>
+        <v>-10.235</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.58</v>
       </c>
       <c r="I402" t="n">
-        <v>1.41</v>
+        <v>1.2614</v>
       </c>
       <c r="J402" t="n">
-        <v>38.07</v>
+        <v>34.0578</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4064</v>
+        <v>0.4222</v>
       </c>
       <c r="J403" t="n">
-        <v>10.9728</v>
+        <v>11.3994</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3033</v>
+        <v>0.3439</v>
       </c>
       <c r="J404" t="n">
-        <v>8.1891</v>
+        <v>9.285299999999999</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.05</v>
       </c>
       <c r="I405" t="n">
-        <v>0.1127</v>
+        <v>0.1676</v>
       </c>
       <c r="J405" t="n">
-        <v>3.0429</v>
+        <v>4.5252</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6896</v>
+        <v>-0.6338</v>
       </c>
       <c r="J406" t="n">
-        <v>-18.6192</v>
+        <v>-17.1126</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1971</v>
+        <v>0.1907</v>
       </c>
       <c r="J407" t="n">
-        <v>5.3217</v>
+        <v>5.1489</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.03</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1372</v>
+        <v>0.1177</v>
       </c>
       <c r="J408" t="n">
-        <v>3.7044</v>
+        <v>3.1779</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1736</v>
+        <v>-0.1241</v>
       </c>
       <c r="J409" t="n">
-        <v>-4.6872</v>
+        <v>-3.3507</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.83</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.307</v>
+        <v>-0.1963</v>
       </c>
       <c r="J410" t="n">
-        <v>-8.289</v>
+        <v>-5.3001</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.66</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.5517</v>
+        <v>-0.3615</v>
       </c>
       <c r="J411" t="n">
-        <v>-14.8959</v>
+        <v>-9.7605</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.41</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1242</v>
+        <v>1.0692</v>
       </c>
       <c r="J412" t="n">
-        <v>29.2292</v>
+        <v>27.7992</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.35</v>
       </c>
       <c r="I413" t="n">
-        <v>0.9957</v>
+        <v>0.9699</v>
       </c>
       <c r="J413" t="n">
-        <v>25.8882</v>
+        <v>25.2174</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.99</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.1017</v>
+        <v>-0.0613</v>
       </c>
       <c r="J414" t="n">
-        <v>-2.6442</v>
+        <v>-1.5938</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.9</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.415</v>
+        <v>-0.3592</v>
       </c>
       <c r="J415" t="n">
-        <v>-10.79</v>
+        <v>-9.3392</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.53</v>
       </c>
       <c r="I416" t="n">
-        <v>-1.2758</v>
+        <v>-1.2887</v>
       </c>
       <c r="J416" t="n">
-        <v>-33.1708</v>
+        <v>-33.5062</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.19</v>
       </c>
       <c r="I417" t="n">
-        <v>0.36</v>
+        <v>0.4125</v>
       </c>
       <c r="J417" t="n">
-        <v>9.359999999999999</v>
+        <v>10.725</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.14</v>
       </c>
       <c r="I418" t="n">
-        <v>0.2839</v>
+        <v>0.3188</v>
       </c>
       <c r="J418" t="n">
-        <v>7.3814</v>
+        <v>8.2888</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.03</v>
       </c>
       <c r="I419" t="n">
-        <v>0.0764</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J419" t="n">
-        <v>1.9864</v>
+        <v>2.288</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>0.0463</v>
+        <v>0.063</v>
       </c>
       <c r="J420" t="n">
-        <v>1.2038</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.75</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4588</v>
+        <v>-0.2912</v>
       </c>
       <c r="J421" t="n">
-        <v>-11.9288</v>
+        <v>-7.5712</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.59</v>
       </c>
       <c r="I422" t="n">
-        <v>1.3695</v>
+        <v>1.2402</v>
       </c>
       <c r="J422" t="n">
-        <v>32.868</v>
+        <v>29.7648</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.41</v>
       </c>
       <c r="I423" t="n">
-        <v>1.0059</v>
+        <v>1.0072</v>
       </c>
       <c r="J423" t="n">
-        <v>24.1416</v>
+        <v>24.1728</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.25</v>
       </c>
       <c r="I424" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6677</v>
       </c>
       <c r="J424" t="n">
-        <v>14.6496</v>
+        <v>16.0248</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.15</v>
       </c>
       <c r="I425" t="n">
-        <v>0.346</v>
+        <v>0.424</v>
       </c>
       <c r="J425" t="n">
-        <v>8.304</v>
+        <v>10.176</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.9</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.4928</v>
+        <v>-0.418</v>
       </c>
       <c r="J426" t="n">
-        <v>-11.8272</v>
+        <v>-10.032</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.09</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2807</v>
+        <v>0.2898</v>
       </c>
       <c r="J427" t="n">
-        <v>6.7368</v>
+        <v>6.9552</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.04</v>
       </c>
       <c r="I428" t="n">
-        <v>0.1889</v>
+        <v>0.1722</v>
       </c>
       <c r="J428" t="n">
-        <v>4.5336</v>
+        <v>4.1328</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.3548</v>
+        <v>-0.2366</v>
       </c>
       <c r="J429" t="n">
-        <v>-8.5152</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4178</v>
+        <v>-0.2751</v>
       </c>
       <c r="J430" t="n">
-        <v>-10.0272</v>
+        <v>-6.6024</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.45</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.7983</v>
+        <v>-0.5457</v>
       </c>
       <c r="J431" t="n">
-        <v>-19.1592</v>
+        <v>-13.0968</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2036/event_2036_evp_summary.xlsx
+++ b/database/event/2036/event_2036_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.390499999999999</v>
+        <v>8.5939</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1753</v>
+        <v>5.3008</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1499</v>
+        <v>3.2879</v>
       </c>
       <c r="E2" t="n">
-        <v>8.390499999999999</v>
+        <v>8.5939</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4857</v>
+        <v>2.3508</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9048</v>
+        <v>6.2431</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4857</v>
+        <v>2.4202</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5879</v>
+        <v>2.4826</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9048</v>
+        <v>6.2431</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>207</v>
       </c>
       <c r="M2" t="n">
-        <v>8.492699999999999</v>
+        <v>8.7257</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0711</v>
+        <v>6.3153</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7447</v>
+        <v>3.8953</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1028</v>
+        <v>2.2507</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0711</v>
+        <v>6.3153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.761</v>
+        <v>0.7654</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3101</v>
+        <v>5.5499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.761</v>
+        <v>0.7654</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7923</v>
+        <v>0.7851</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3101</v>
+        <v>5.5499</v>
       </c>
       <c r="K3" t="n">
         <v>140</v>
@@ -575,7 +575,7 @@
         <v>207</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1024</v>
+        <v>6.335</v>
       </c>
       <c r="N3" t="n">
         <v>347</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8437</v>
+        <v>5.8559</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6044</v>
+        <v>3.6119</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0001</v>
+        <v>2.0415</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8437</v>
+        <v>5.8559</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9892</v>
+        <v>2.6844</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8545</v>
+        <v>3.1715</v>
       </c>
       <c r="H4" t="n">
-        <v>3.204</v>
+        <v>3.1504</v>
       </c>
       <c r="I4" t="n">
-        <v>3.204</v>
+        <v>3.1504</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8545</v>
+        <v>3.1715</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0585</v>
+        <v>6.321899999999999</v>
       </c>
       <c r="N4" t="n">
         <v>284</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5446</v>
+        <v>5.7309</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4199</v>
+        <v>3.5348</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8651</v>
+        <v>1.9846</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5446</v>
+        <v>5.7309</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1046</v>
+        <v>1.1059</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4401</v>
+        <v>4.625</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1046</v>
+        <v>1.1059</v>
       </c>
       <c r="I5" t="n">
-        <v>1.15</v>
+        <v>1.1344</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4401</v>
+        <v>4.625</v>
       </c>
       <c r="K5" t="n">
         <v>140</v>
@@ -667,7 +667,7 @@
         <v>207</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5901</v>
+        <v>5.7594</v>
       </c>
       <c r="N5" t="n">
         <v>347</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2945</v>
+        <v>4.2943</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6489</v>
+        <v>2.6487</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3007</v>
+        <v>1.3307</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2945</v>
+        <v>4.2943</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4518</v>
+        <v>4.4301</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1573</v>
+        <v>-0.1358</v>
       </c>
       <c r="H6" t="n">
-        <v>10.2462</v>
+        <v>9.7224</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3275</v>
+        <v>5.25</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1573</v>
+        <v>-0.1358</v>
       </c>
       <c r="K6" t="n">
         <v>119</v>
@@ -713,7 +713,7 @@
         <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>5.170199999999999</v>
+        <v>5.1142</v>
       </c>
       <c r="N6" t="n">
         <v>192</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0764</v>
+        <v>4.0748</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5143</v>
+        <v>2.5134</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2023</v>
+        <v>1.2307</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0764</v>
+        <v>4.0748</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0543</v>
+        <v>2.7621</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0221</v>
+        <v>1.3127</v>
       </c>
       <c r="H7" t="n">
-        <v>3.347</v>
+        <v>3.3203</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4846</v>
+        <v>3.4059</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0221</v>
+        <v>1.3127</v>
       </c>
       <c r="K7" t="n">
         <v>140</v>
@@ -759,7 +759,7 @@
         <v>207</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5067</v>
+        <v>4.7186</v>
       </c>
       <c r="N7" t="n">
         <v>347</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6956</v>
+        <v>3.699</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2795</v>
+        <v>2.2816</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0304</v>
+        <v>1.0597</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6956</v>
+        <v>3.699</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6956</v>
+        <v>2.4777</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.2213</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7551</v>
+        <v>3.2808</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7551</v>
+        <v>1.7716</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.2213</v>
       </c>
       <c r="K8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7551</v>
+        <v>2.9929</v>
       </c>
       <c r="N8" t="n">
-        <v>135</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6678</v>
+        <v>3.6036</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2623</v>
+        <v>2.2227</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0178</v>
+        <v>1.0162</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6678</v>
+        <v>3.6036</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3689</v>
+        <v>3.2911</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2989</v>
+        <v>0.3125</v>
       </c>
       <c r="H9" t="n">
-        <v>6.3836</v>
+        <v>5.9644</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3192</v>
+        <v>3.2207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2989</v>
+        <v>0.3125</v>
       </c>
       <c r="K9" t="n">
         <v>119</v>
@@ -851,7 +851,7 @@
         <v>73</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6181</v>
+        <v>3.5332</v>
       </c>
       <c r="N9" t="n">
         <v>192</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.651</v>
+        <v>3.4001</v>
       </c>
       <c r="C10" t="n">
-        <v>2.252</v>
+        <v>2.0972</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0102</v>
+        <v>0.9236</v>
       </c>
       <c r="E10" t="n">
-        <v>3.651</v>
+        <v>3.4001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.554</v>
+        <v>3.4001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.097</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5124</v>
+        <v>4.7168</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8263</v>
+        <v>4.7168</v>
       </c>
       <c r="J10" t="n">
-        <v>1.097</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L10" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9233</v>
+        <v>4.7168</v>
       </c>
       <c r="N10" t="n">
-        <v>294</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4397</v>
+        <v>3.3806</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1216</v>
+        <v>2.0852</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9147</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4397</v>
+        <v>3.3806</v>
       </c>
       <c r="F11" t="n">
-        <v>4.3212</v>
+        <v>4.255</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8815</v>
+        <v>-0.8744</v>
       </c>
       <c r="H11" t="n">
-        <v>9.738799999999999</v>
+        <v>9.144600000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>5.0637</v>
+        <v>4.938</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8815</v>
+        <v>-0.8744</v>
       </c>
       <c r="K11" t="n">
         <v>136</v>
@@ -943,7 +943,7 @@
         <v>158</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1822</v>
+        <v>4.0636</v>
       </c>
       <c r="N11" t="n">
         <v>294</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4157</v>
+        <v>3.3348</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1068</v>
+        <v>2.0569</v>
       </c>
       <c r="D12" t="n">
-        <v>0.904</v>
+        <v>0.8939</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4157</v>
+        <v>3.3348</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3274</v>
+        <v>3.2871</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0883</v>
+        <v>0.0477</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2375</v>
+        <v>5.951</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2432</v>
+        <v>3.2135</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0883</v>
+        <v>0.0477</v>
       </c>
       <c r="K12" t="n">
         <v>119</v>
@@ -989,7 +989,7 @@
         <v>73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3315</v>
+        <v>3.2612</v>
       </c>
       <c r="N12" t="n">
         <v>192</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0727</v>
+        <v>3.0684</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8953</v>
+        <v>1.8926</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7492</v>
+        <v>0.7726</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0727</v>
+        <v>3.0684</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4977</v>
+        <v>2.4512</v>
       </c>
       <c r="G13" t="n">
-        <v>0.575</v>
+        <v>0.6172</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3139</v>
+        <v>3.1934</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7231</v>
+        <v>1.7244</v>
       </c>
       <c r="J13" t="n">
-        <v>0.575</v>
+        <v>0.6172</v>
       </c>
       <c r="K13" t="n">
         <v>136</v>
@@ -1035,7 +1035,7 @@
         <v>158</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2981</v>
+        <v>2.3416</v>
       </c>
       <c r="N13" t="n">
         <v>294</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0151</v>
+        <v>2.87</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8597</v>
+        <v>1.7702</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7232</v>
+        <v>0.6823</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0151</v>
+        <v>2.87</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6794</v>
+        <v>2.4365</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3357</v>
+        <v>0.4335</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6794</v>
+        <v>2.6078</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6794</v>
+        <v>2.6078</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3357</v>
+        <v>0.4335</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -1081,7 +1081,7 @@
         <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0151</v>
+        <v>3.0413</v>
       </c>
       <c r="N14" t="n">
         <v>284</v>
@@ -1090,78 +1090,78 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0023</v>
+        <v>2.8432</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8518</v>
+        <v>1.7537</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7174</v>
+        <v>0.6701</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0023</v>
+        <v>2.8432</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0023</v>
+        <v>1.3492</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.494</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2328</v>
+        <v>1.3492</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2328</v>
+        <v>1.3492</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.494</v>
       </c>
       <c r="K15" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2328</v>
+        <v>2.8432</v>
       </c>
       <c r="N15" t="n">
-        <v>134</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8941</v>
+        <v>2.6695</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7851</v>
+        <v>1.6466</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6685</v>
+        <v>0.591</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8941</v>
+        <v>2.6695</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8941</v>
+        <v>2.6695</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9951</v>
+        <v>3.1177</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9951</v>
+        <v>3.1177</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9951</v>
+        <v>3.1177</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.715</v>
+        <v>2.5539</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6746</v>
+        <v>1.5753</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5877</v>
+        <v>0.5384</v>
       </c>
       <c r="E17" t="n">
-        <v>2.715</v>
+        <v>2.5539</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3599</v>
+        <v>2.5539</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3551</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3599</v>
+        <v>2.8647</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3599</v>
+        <v>2.8647</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3551</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L17" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.715</v>
+        <v>2.8647</v>
       </c>
       <c r="N17" t="n">
-        <v>229</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6106</v>
+        <v>2.5352</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6102</v>
+        <v>1.5637</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5405</v>
+        <v>0.5299</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6106</v>
+        <v>2.5352</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1841</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5735</v>
+        <v>0.3752</v>
       </c>
       <c r="H18" t="n">
-        <v>3.632</v>
+        <v>2.16</v>
       </c>
       <c r="I18" t="n">
-        <v>3.632</v>
+        <v>2.16</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5735</v>
+        <v>0.3752</v>
       </c>
       <c r="K18" t="n">
         <v>140</v>
@@ -1265,7 +1265,7 @@
         <v>89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0585</v>
+        <v>2.5352</v>
       </c>
       <c r="N18" t="n">
         <v>229</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5902</v>
+        <v>2.5169</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5976</v>
+        <v>1.5524</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5313</v>
+        <v>0.5215</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5902</v>
+        <v>2.5169</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5902</v>
+        <v>2.5175</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5902</v>
+        <v>3.4121</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5902</v>
+        <v>1.8425</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5902</v>
+        <v>1.8419</v>
       </c>
       <c r="N19" t="n">
-        <v>133</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5855</v>
+        <v>2.4657</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5947</v>
+        <v>1.5209</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5292</v>
+        <v>0.4982</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5855</v>
+        <v>2.4657</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5837</v>
+        <v>1.9848</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0018</v>
+        <v>0.4809</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6171</v>
+        <v>1.9848</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8807</v>
+        <v>1.0718</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0018</v>
+        <v>0.4809</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="L20" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8825</v>
+        <v>1.5527</v>
       </c>
       <c r="N20" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5465</v>
+        <v>2.4029</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5707</v>
+        <v>1.4821</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4696</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5465</v>
+        <v>2.4029</v>
       </c>
       <c r="F21" t="n">
-        <v>2.225</v>
+        <v>2.4029</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3215</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.225</v>
+        <v>2.5342</v>
       </c>
       <c r="I21" t="n">
-        <v>2.225</v>
+        <v>2.5342</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3215</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L21" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5465</v>
+        <v>2.5342</v>
       </c>
       <c r="N21" t="n">
-        <v>229</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5329</v>
+        <v>2.2563</v>
       </c>
       <c r="C22" t="n">
-        <v>1.5623</v>
+        <v>1.3917</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4029</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5329</v>
+        <v>2.2563</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1106</v>
+        <v>2.8612</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4223</v>
+        <v>-0.6049</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1106</v>
+        <v>3.5374</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0974</v>
+        <v>3.5374</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4223</v>
+        <v>-0.6049</v>
       </c>
       <c r="K22" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L22" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5197</v>
+        <v>2.9325</v>
       </c>
       <c r="N22" t="n">
-        <v>294</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1324</v>
+        <v>2.1113</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3153</v>
+        <v>1.3023</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3247</v>
+        <v>0.3369</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1324</v>
+        <v>2.1113</v>
       </c>
       <c r="F23" t="n">
-        <v>2.492</v>
+        <v>2.434</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3596</v>
+        <v>-0.3227</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2939</v>
+        <v>3.1363</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7127</v>
+        <v>1.6936</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3596</v>
+        <v>-0.3227</v>
       </c>
       <c r="K23" t="n">
         <v>119</v>
@@ -1495,7 +1495,7 @@
         <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3531</v>
+        <v>1.3709</v>
       </c>
       <c r="N23" t="n">
         <v>192</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.0273</v>
+        <v>1.868</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2504</v>
+        <v>1.1522</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2772</v>
+        <v>0.2261</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0273</v>
+        <v>1.868</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7105</v>
+        <v>1.868</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6832</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7105</v>
+        <v>1.868</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7105</v>
+        <v>1.868</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6832</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L24" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0273</v>
+        <v>1.868</v>
       </c>
       <c r="N24" t="n">
-        <v>229</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.955</v>
+        <v>1.7514</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2059</v>
+        <v>1.0803</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2446</v>
+        <v>0.1731</v>
       </c>
       <c r="E25" t="n">
-        <v>1.955</v>
+        <v>1.7514</v>
       </c>
       <c r="F25" t="n">
-        <v>1.955</v>
+        <v>2.4733</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.7219</v>
       </c>
       <c r="H25" t="n">
-        <v>1.955</v>
+        <v>2.6883</v>
       </c>
       <c r="I25" t="n">
-        <v>1.955</v>
+        <v>2.6883</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.7219</v>
       </c>
       <c r="K25" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M25" t="n">
-        <v>1.955</v>
+        <v>1.9664</v>
       </c>
       <c r="N25" t="n">
-        <v>135</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1287</v>
+        <v>1.0306</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1881</v>
+        <v>0.1364</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.8299</v>
+        <v>1.6708</v>
       </c>
       <c r="N26" t="n">
         <v>137</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0953</v>
+        <v>1.026</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1637</v>
+        <v>0.133</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7758</v>
+        <v>1.6634</v>
       </c>
       <c r="N27" t="n">
         <v>133</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4921</v>
+        <v>1.5097</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9203</v>
+        <v>0.9312</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0356</v>
+        <v>0.063</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4921</v>
+        <v>1.5097</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1341</v>
+        <v>2.0299</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.642</v>
+        <v>-0.5202</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1341</v>
+        <v>2.0299</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1341</v>
+        <v>2.0299</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.642</v>
+        <v>-0.5202</v>
       </c>
       <c r="K28" t="n">
         <v>126</v>
@@ -1725,7 +1725,7 @@
         <v>158</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4921</v>
+        <v>1.5097</v>
       </c>
       <c r="N28" t="n">
         <v>284</v>
@@ -1734,369 +1734,369 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3503</v>
+        <v>1.3864</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8329</v>
+        <v>0.8551</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0284</v>
+        <v>0.0069</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3503</v>
+        <v>1.3864</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3503</v>
+        <v>0.0703</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.3161</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3503</v>
+        <v>0.0703</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3503</v>
+        <v>0.0721</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.3161</v>
       </c>
       <c r="K29" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3503</v>
+        <v>1.3882</v>
       </c>
       <c r="N29" t="n">
-        <v>133</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="C30" t="n">
-        <v>0.729</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1044</v>
+        <v>-0.0004</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1819</v>
+        <v>1.3704</v>
       </c>
       <c r="N30" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.099</v>
+        <v>1.1971</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1419</v>
+        <v>-0.0793</v>
       </c>
       <c r="E31" t="n">
-        <v>1.099</v>
+        <v>1.1971</v>
       </c>
       <c r="F31" t="n">
-        <v>1.099</v>
+        <v>0.0896</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.1075</v>
       </c>
       <c r="H31" t="n">
-        <v>1.099</v>
+        <v>0.0896</v>
       </c>
       <c r="I31" t="n">
-        <v>1.099</v>
+        <v>0.0896</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.1075</v>
       </c>
       <c r="K31" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M31" t="n">
-        <v>1.099</v>
+        <v>1.1971</v>
       </c>
       <c r="N31" t="n">
-        <v>108</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0779</v>
+        <v>1.103</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6649</v>
+        <v>0.6803</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1514</v>
+        <v>-0.1221</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0779</v>
+        <v>1.103</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0275</v>
+        <v>1.9432</v>
       </c>
       <c r="G32" t="n">
-        <v>1.1054</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0275</v>
+        <v>1.9432</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0286</v>
+        <v>1.9432</v>
       </c>
       <c r="J32" t="n">
-        <v>1.1054</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L32" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0768</v>
+        <v>1.103</v>
       </c>
       <c r="N32" t="n">
-        <v>347</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0708</v>
+        <v>1.1016</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6605</v>
+        <v>0.6795</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1546</v>
+        <v>-0.1227</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0708</v>
+        <v>1.1016</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9543</v>
+        <v>1.1016</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8835</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.9543</v>
+        <v>1.1016</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9543</v>
+        <v>1.1016</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8835</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="L33" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0708</v>
+        <v>1.1016</v>
       </c>
       <c r="N33" t="n">
-        <v>284</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0451</v>
+        <v>0.9393</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6446</v>
+        <v>0.5794</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1662</v>
+        <v>-0.1966</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0451</v>
+        <v>0.9393</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0387</v>
+        <v>0.9393</v>
       </c>
       <c r="G34" t="n">
-        <v>1.0064</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0387</v>
+        <v>0.9393</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0387</v>
+        <v>0.9393</v>
       </c>
       <c r="J34" t="n">
-        <v>1.0064</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0451</v>
+        <v>0.9393</v>
       </c>
       <c r="N34" t="n">
-        <v>284</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7723</v>
+        <v>0.7219</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4764</v>
+        <v>0.4453</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2894</v>
+        <v>-0.2956</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7723</v>
+        <v>0.7219</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5144</v>
+        <v>0.7219</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7421</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5144</v>
+        <v>0.7219</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5144</v>
+        <v>0.7219</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7421</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L35" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7723</v>
+        <v>0.7219</v>
       </c>
       <c r="N35" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7362</v>
+        <v>0.6542</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4541</v>
+        <v>0.4035</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3057</v>
+        <v>-0.3264</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7362</v>
+        <v>0.6542</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7362</v>
+        <v>1.4211</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.7669</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7362</v>
+        <v>1.4211</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7362</v>
+        <v>1.4211</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.7669</v>
       </c>
       <c r="K36" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7362</v>
+        <v>0.6542</v>
       </c>
       <c r="N36" t="n">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6681</v>
+        <v>0.5566</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4121</v>
+        <v>0.3433</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3364</v>
+        <v>-0.3708</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6681</v>
+        <v>0.5566</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1747</v>
+        <v>1.1043</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5477</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1747</v>
+        <v>1.1043</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1747</v>
+        <v>1.1043</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5477</v>
       </c>
       <c r="K37" t="n">
         <v>131</v>
@@ -2139,7 +2139,7 @@
         <v>45</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6681</v>
+        <v>0.5566000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>176</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3883</v>
+        <v>0.3421</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3538</v>
+        <v>-0.3717</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5546</v>
       </c>
       <c r="N38" t="n">
         <v>135</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3476</v>
+        <v>0.3239</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3836</v>
+        <v>-0.3852</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5635</v>
+        <v>0.5251</v>
       </c>
       <c r="N39" t="n">
         <v>149</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5397</v>
+        <v>0.4591</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3329</v>
+        <v>0.2832</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3944</v>
+        <v>-0.4152</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5397</v>
+        <v>0.4591</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5977</v>
+        <v>0.5274</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.058</v>
+        <v>-0.0683</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5977</v>
+        <v>0.5274</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5977</v>
+        <v>0.5274</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.058</v>
+        <v>-0.0683</v>
       </c>
       <c r="K40" t="n">
         <v>131</v>
@@ -2277,7 +2277,7 @@
         <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5397</v>
+        <v>0.4591</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2286,185 +2286,185 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2509</v>
+        <v>0.2272</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4544</v>
+        <v>-0.4565</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4068</v>
+        <v>0.3683</v>
       </c>
       <c r="N41" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2409</v>
+        <v>0.2162</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4617</v>
+        <v>-0.4646</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3905</v>
+        <v>0.3505</v>
       </c>
       <c r="N42" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2335</v>
+        <v>0.2095</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4671</v>
+        <v>-0.4696</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3785</v>
+        <v>0.3396</v>
       </c>
       <c r="N43" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2286</v>
+        <v>0.2025</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4707</v>
+        <v>-0.4748</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3707</v>
+        <v>0.3283</v>
       </c>
       <c r="N44" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="C45" t="n">
-        <v>0.199</v>
+        <v>0.159</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4924</v>
+        <v>-0.5068</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3226</v>
+        <v>0.2578</v>
       </c>
       <c r="N45" t="n">
         <v>135</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1496</v>
+        <v>0.123</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5285</v>
+        <v>-0.5334</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2426</v>
+        <v>0.1994</v>
       </c>
       <c r="N46" t="n">
         <v>135</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0091</v>
+        <v>-0.0291</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0147</v>
+        <v>-0.0472</v>
       </c>
       <c r="N47" t="n">
         <v>134</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0503</v>
+        <v>-0.09</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.031</v>
+        <v>-0.0555</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6607</v>
+        <v>-0.6652</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0503</v>
+        <v>-0.09</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2129</v>
+        <v>-0.09</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2632</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2129</v>
+        <v>-0.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2129</v>
+        <v>-0.09</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2632</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L48" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.05029999999999998</v>
+        <v>-0.09</v>
       </c>
       <c r="N48" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49">
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0542</v>
+        <v>-0.0998</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0334</v>
+        <v>-0.0616</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6625</v>
+        <v>-0.6696</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0542</v>
+        <v>-0.0998</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2803</v>
+        <v>0.2531</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3345</v>
+        <v>-0.3529</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2803</v>
+        <v>0.2531</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2803</v>
+        <v>0.2531</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3345</v>
+        <v>-0.3529</v>
       </c>
       <c r="K49" t="n">
         <v>140</v>
@@ -2691,7 +2691,7 @@
         <v>89</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.05420000000000003</v>
+        <v>-0.0998</v>
       </c>
       <c r="N49" t="n">
         <v>229</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1338</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0578</v>
+        <v>-0.0825</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6803</v>
+        <v>-0.6851</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1338</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.1517</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.2855</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.1517</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.1517</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.2855</v>
       </c>
       <c r="K50" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1338</v>
       </c>
       <c r="N50" t="n">
-        <v>149</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.211</v>
+        <v>-0.1874</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7925</v>
+        <v>-0.7625</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3421</v>
+        <v>-0.3039</v>
       </c>
       <c r="N51" t="n">
         <v>134</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5129</v>
+        <v>-0.5944</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3164</v>
+        <v>-0.3666</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8696</v>
+        <v>-0.8948</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5129</v>
+        <v>-0.5944</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2917</v>
+        <v>0.241</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.8046</v>
+        <v>-0.8354</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2917</v>
+        <v>0.241</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2917</v>
+        <v>0.241</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8046</v>
+        <v>-0.8354</v>
       </c>
       <c r="K52" t="n">
         <v>131</v>
@@ -2829,7 +2829,7 @@
         <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5128999999999999</v>
+        <v>-0.5944</v>
       </c>
       <c r="N52" t="n">
         <v>176</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4582</v>
+        <v>-0.4949</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9734</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.7429</v>
+        <v>-0.8023</v>
       </c>
       <c r="N53" t="n">
         <v>137</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.5598</v>
+        <v>-0.5934</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0477</v>
+        <v>-1.0621</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.9075</v>
+        <v>-0.962</v>
       </c>
       <c r="N54" t="n">
         <v>137</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.6486</v>
+        <v>-0.7029</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.1127</v>
+        <v>-1.143</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.0515</v>
+        <v>-1.1396</v>
       </c>
       <c r="N55" t="n">
         <v>108</v>
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.4344</v>
+        <v>-1.1678</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.8847</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.2856</v>
+        <v>-1.1558</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.4344</v>
+        <v>-1.1678</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.6007</v>
+        <v>-1.4037</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1663</v>
+        <v>0.2359</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.6007</v>
+        <v>-1.4037</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8323</v>
+        <v>-0.758</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1663</v>
+        <v>0.2359</v>
       </c>
       <c r="K56" t="n">
         <v>136</v>
@@ -3013,7 +3013,7 @@
         <v>158</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.666</v>
+        <v>-0.5221</v>
       </c>
       <c r="N56" t="n">
         <v>294</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.9777</v>
+        <v>-1.0064</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.3536</v>
+        <v>-1.367</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.5851</v>
+        <v>-1.6317</v>
       </c>
       <c r="N57" t="n">
         <v>137</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.1651</v>
+        <v>-1.2173</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.4908</v>
+        <v>-1.5226</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.8889</v>
+        <v>-1.9735</v>
       </c>
       <c r="N58" t="n">
         <v>108</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.2317</v>
+        <v>-1.2796</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.5395</v>
+        <v>-1.5686</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.9969</v>
+        <v>-2.0746</v>
       </c>
       <c r="N59" t="n">
         <v>108</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.3237</v>
+        <v>-1.3438</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.6068</v>
+        <v>-1.616</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.146</v>
+        <v>-2.1787</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.3691</v>
+        <v>-1.4073</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.6401</v>
+        <v>-1.6628</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.2197</v>
+        <v>-2.2816</v>
       </c>
       <c r="N61" t="n">
         <v>108</v>
@@ -3349,10 +3349,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5764</v>
+        <v>0.5613</v>
       </c>
       <c r="J2" t="n">
-        <v>20.7504</v>
+        <v>20.2068</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.21</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4519</v>
+        <v>0.447</v>
       </c>
       <c r="J3" t="n">
-        <v>16.2684</v>
+        <v>16.092</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1585</v>
+        <v>0.1678</v>
       </c>
       <c r="J4" t="n">
-        <v>5.706</v>
+        <v>6.0408</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0515</v>
+        <v>-0.0593</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.854</v>
+        <v>-2.1348</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4671</v>
+        <v>-0.4731</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.8156</v>
+        <v>-17.0316</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0231</v>
+        <v>0.9677</v>
       </c>
       <c r="J7" t="n">
-        <v>36.8316</v>
+        <v>34.8372</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7187</v>
+        <v>0.6835</v>
       </c>
       <c r="J8" t="n">
-        <v>25.8732</v>
+        <v>24.606</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5728</v>
+        <v>0.5538</v>
       </c>
       <c r="J9" t="n">
-        <v>20.6208</v>
+        <v>19.9368</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1655</v>
+        <v>-0.16</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.958</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5269</v>
+        <v>-0.4958</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.9684</v>
+        <v>-17.8488</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1111</v>
+        <v>-0.1345</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1109</v>
+        <v>-2.5555</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1676</v>
+        <v>-0.1905</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1844</v>
+        <v>-3.6195</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2602</v>
+        <v>-0.2812</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.9438</v>
+        <v>-5.3428</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3702</v>
+        <v>-0.3878</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.0338</v>
+        <v>-7.3682</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.42</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5572</v>
+        <v>-0.5635</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.5868</v>
+        <v>-10.7065</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3062</v>
+        <v>1.3887</v>
       </c>
       <c r="J17" t="n">
-        <v>24.8178</v>
+        <v>26.3853</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1876</v>
+        <v>1.2173</v>
       </c>
       <c r="J18" t="n">
-        <v>22.5644</v>
+        <v>23.1287</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0672</v>
+        <v>1.0414</v>
       </c>
       <c r="J19" t="n">
-        <v>20.2768</v>
+        <v>19.7866</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4943</v>
+        <v>0.4947</v>
       </c>
       <c r="J20" t="n">
-        <v>9.3917</v>
+        <v>9.3993</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3116</v>
+        <v>0.329</v>
       </c>
       <c r="J21" t="n">
-        <v>5.9204</v>
+        <v>6.251</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3817</v>
+        <v>0.3809</v>
       </c>
       <c r="J22" t="n">
-        <v>12.9778</v>
+        <v>12.9506</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3629</v>
+        <v>0.3633</v>
       </c>
       <c r="J23" t="n">
-        <v>12.3386</v>
+        <v>12.3522</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1153</v>
+        <v>0.1241</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9202</v>
+        <v>4.2194</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1884</v>
+        <v>-0.2018</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.4056</v>
+        <v>-6.8612</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2395</v>
+        <v>-0.2528</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.143000000000001</v>
+        <v>-8.5952</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8955</v>
+        <v>0.8365</v>
       </c>
       <c r="J27" t="n">
-        <v>30.447</v>
+        <v>28.441</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5562</v>
+        <v>0.5372</v>
       </c>
       <c r="J28" t="n">
-        <v>18.9108</v>
+        <v>18.2648</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.454</v>
+        <v>0.445</v>
       </c>
       <c r="J29" t="n">
-        <v>15.436</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.237</v>
+        <v>0.2439</v>
       </c>
       <c r="J30" t="n">
-        <v>8.058</v>
+        <v>8.2926</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6772</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.0248</v>
+        <v>-21.4744</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4061</v>
+        <v>0.4457</v>
       </c>
       <c r="J32" t="n">
-        <v>8.934200000000001</v>
+        <v>9.805400000000001</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2045</v>
+        <v>0.2121</v>
       </c>
       <c r="J33" t="n">
-        <v>4.499</v>
+        <v>4.6662</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1613</v>
+        <v>0.1698</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5486</v>
+        <v>3.7356</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1002</v>
+        <v>-0.1117</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.2044</v>
+        <v>-2.4574</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3078</v>
+        <v>-0.32</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.7716</v>
+        <v>-7.04</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.95</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4327</v>
+        <v>1.5509</v>
       </c>
       <c r="J37" t="n">
-        <v>31.5194</v>
+        <v>34.1198</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3513</v>
+        <v>0.3651</v>
       </c>
       <c r="J38" t="n">
-        <v>7.7286</v>
+        <v>8.0322</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1587</v>
+        <v>0.1739</v>
       </c>
       <c r="J39" t="n">
-        <v>3.4914</v>
+        <v>3.8258</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4257</v>
+        <v>-0.4019</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.365399999999999</v>
+        <v>-8.841799999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5095</v>
+        <v>-0.4781</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.209</v>
+        <v>-10.5182</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4462</v>
+        <v>0.5047</v>
       </c>
       <c r="J42" t="n">
-        <v>12.4936</v>
+        <v>14.1316</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2564</v>
+        <v>0.2714</v>
       </c>
       <c r="J43" t="n">
-        <v>7.1792</v>
+        <v>7.5992</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0378</v>
+        <v>0.0477</v>
       </c>
       <c r="J44" t="n">
-        <v>1.0584</v>
+        <v>1.3356</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.059</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.652</v>
+        <v>-1.8228</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1441</v>
+        <v>-0.1546</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.0348</v>
+        <v>-4.3288</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4066</v>
+        <v>0.4509</v>
       </c>
       <c r="J47" t="n">
-        <v>11.3848</v>
+        <v>12.6252</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1166</v>
+        <v>0.128</v>
       </c>
       <c r="J48" t="n">
-        <v>3.2648</v>
+        <v>3.584</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0.083</v>
+        <v>0.0934</v>
       </c>
       <c r="J49" t="n">
-        <v>2.324</v>
+        <v>2.6152</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0905</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.2876</v>
+        <v>-2.534</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.93</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.106</v>
+        <v>-0.1161</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.968</v>
+        <v>-3.2508</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3326</v>
+        <v>0.314</v>
       </c>
       <c r="J52" t="n">
-        <v>7.6498</v>
+        <v>7.222</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0482</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.1086</v>
+        <v>-1.5663</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1973</v>
+        <v>-0.2181</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.5379</v>
+        <v>-5.0163</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.498</v>
+        <v>-0.5074</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.454</v>
+        <v>-11.6702</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6182</v>
+        <v>-0.6193</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.2186</v>
+        <v>-14.2439</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.98</v>
       </c>
       <c r="I57" t="n">
-        <v>1.4122</v>
+        <v>1.5378</v>
       </c>
       <c r="J57" t="n">
-        <v>32.4806</v>
+        <v>35.3694</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.49</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8289</v>
+        <v>0.9204</v>
       </c>
       <c r="J58" t="n">
-        <v>19.0647</v>
+        <v>21.1692</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3934</v>
+        <v>0.4349</v>
       </c>
       <c r="J59" t="n">
-        <v>9.0482</v>
+        <v>10.0027</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1218</v>
+        <v>0.1482</v>
       </c>
       <c r="J60" t="n">
-        <v>2.8014</v>
+        <v>3.4086</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2474</v>
+        <v>-0.2267</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.6902</v>
+        <v>-5.2141</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.548</v>
+        <v>0.6019</v>
       </c>
       <c r="J62" t="n">
-        <v>22.468</v>
+        <v>24.6779</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.21</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5037</v>
+        <v>0.5527</v>
       </c>
       <c r="J63" t="n">
-        <v>20.6517</v>
+        <v>22.6607</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4432</v>
+        <v>0.4849</v>
       </c>
       <c r="J64" t="n">
-        <v>18.1712</v>
+        <v>19.8809</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.506</v>
+        <v>-0.4812</v>
       </c>
       <c r="J65" t="n">
-        <v>-20.746</v>
+        <v>-19.7292</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5598</v>
+        <v>-0.5294</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.9518</v>
+        <v>-21.7054</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5405</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>22.1605</v>
+        <v>24.6533</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0208</v>
+        <v>-0.0254</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.8528</v>
+        <v>-1.0414</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0504</v>
+        <v>-0.0585</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.0664</v>
+        <v>-2.3985</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0636</v>
+        <v>-0.0728</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.6076</v>
+        <v>-2.9848</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.439</v>
+        <v>-11.9638</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2102</v>
+        <v>1.3193</v>
       </c>
       <c r="J72" t="n">
-        <v>33.8856</v>
+        <v>36.9404</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4685</v>
+        <v>0.5185</v>
       </c>
       <c r="J73" t="n">
-        <v>13.118</v>
+        <v>14.518</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3815</v>
+        <v>0.4117</v>
       </c>
       <c r="J74" t="n">
-        <v>10.682</v>
+        <v>11.5276</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.178</v>
+        <v>-0.1687</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.984</v>
+        <v>-4.7236</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5661</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.8508</v>
+        <v>-14.8036</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.38</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6037</v>
+        <v>0.6681</v>
       </c>
       <c r="J77" t="n">
-        <v>16.9036</v>
+        <v>18.7068</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1151</v>
+        <v>-0.1294</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.2228</v>
+        <v>-3.6232</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2196</v>
+        <v>-0.2351</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.1488</v>
+        <v>-6.5828</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.2604</v>
+        <v>-7.6832</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2886</v>
+        <v>-0.303</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.0808</v>
+        <v>-8.484</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.83</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1999</v>
+        <v>1.3219</v>
       </c>
       <c r="J82" t="n">
-        <v>25.1979</v>
+        <v>27.7599</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.58</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9132</v>
+        <v>1.0163</v>
       </c>
       <c r="J83" t="n">
-        <v>19.1772</v>
+        <v>21.3423</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.58</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9132</v>
+        <v>1.0163</v>
       </c>
       <c r="J84" t="n">
-        <v>19.1772</v>
+        <v>21.3423</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5972</v>
       </c>
       <c r="J85" t="n">
-        <v>11.1447</v>
+        <v>12.5412</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4607</v>
+        <v>0.5191</v>
       </c>
       <c r="J86" t="n">
-        <v>9.6747</v>
+        <v>10.9011</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.63</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.3289</v>
+        <v>-0.3542</v>
       </c>
       <c r="J87" t="n">
-        <v>-6.9069</v>
+        <v>-7.4382</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3492</v>
+        <v>-0.3733</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.3332</v>
+        <v>-7.8393</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4161</v>
+        <v>-0.4363</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.738099999999999</v>
+        <v>-9.1623</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.49</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4599</v>
+        <v>-0.4776</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.6579</v>
+        <v>-10.0296</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5748</v>
+        <v>-0.5838</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.0708</v>
+        <v>-12.2598</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>2.01</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4573</v>
+        <v>1.5832</v>
       </c>
       <c r="J92" t="n">
-        <v>34.9752</v>
+        <v>37.9968</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4568</v>
+        <v>0.5085</v>
       </c>
       <c r="J93" t="n">
-        <v>10.9632</v>
+        <v>12.204</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4568</v>
+        <v>0.5085</v>
       </c>
       <c r="J94" t="n">
-        <v>10.9632</v>
+        <v>12.204</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3509</v>
+        <v>0.3707</v>
       </c>
       <c r="J95" t="n">
-        <v>8.4216</v>
+        <v>8.896800000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3057</v>
+        <v>-0.284</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.3368</v>
+        <v>-6.816</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3581</v>
+        <v>0.368</v>
       </c>
       <c r="J97" t="n">
-        <v>8.5944</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0878</v>
       </c>
       <c r="J98" t="n">
-        <v>2.064</v>
+        <v>2.1072</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1673</v>
+        <v>-0.1831</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.0152</v>
+        <v>-4.3944</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1777</v>
+        <v>-0.1935</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.2648</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3447</v>
+        <v>-0.3578</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.2728</v>
+        <v>-8.587199999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.85</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3026</v>
+        <v>1.4168</v>
       </c>
       <c r="J102" t="n">
-        <v>33.8676</v>
+        <v>36.8368</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5778</v>
+        <v>0.6412</v>
       </c>
       <c r="J103" t="n">
-        <v>15.0228</v>
+        <v>16.6712</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.18</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4394</v>
+        <v>0.4856</v>
       </c>
       <c r="J104" t="n">
-        <v>11.4244</v>
+        <v>12.6256</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2499</v>
+        <v>-0.2369</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4974</v>
+        <v>-6.1594</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.73</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8509</v>
+        <v>-0.7806</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.1234</v>
+        <v>-20.2956</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.536</v>
+        <v>0.5929</v>
       </c>
       <c r="J107" t="n">
-        <v>13.936</v>
+        <v>15.4154</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0157</v>
+        <v>-0.0215</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.4082</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.7508</v>
+        <v>-3.0966</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1707</v>
+        <v>-0.1857</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.4382</v>
+        <v>-4.8282</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4045</v>
+        <v>-0.4146</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.517</v>
+        <v>-10.7796</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4972</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>16.9048</v>
+        <v>18.938</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2676</v>
+        <v>0.277</v>
       </c>
       <c r="J113" t="n">
-        <v>9.0984</v>
+        <v>9.417999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0452</v>
+        <v>0.0537</v>
       </c>
       <c r="J114" t="n">
-        <v>1.5368</v>
+        <v>1.8258</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1402</v>
+        <v>-0.1516</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.7668</v>
+        <v>-5.1544</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2748</v>
+        <v>-0.2865</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.3432</v>
+        <v>-9.741</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.29</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3849</v>
+        <v>0.4255</v>
       </c>
       <c r="J117" t="n">
-        <v>13.0866</v>
+        <v>14.467</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.227</v>
+        <v>0.24</v>
       </c>
       <c r="J118" t="n">
-        <v>7.718</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0958</v>
+        <v>0.1074</v>
       </c>
       <c r="J119" t="n">
-        <v>3.2572</v>
+        <v>3.6516</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2116</v>
+        <v>-0.2245</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1944</v>
+        <v>-7.633</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2218</v>
+        <v>-0.2347</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.5412</v>
+        <v>-7.9798</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8727</v>
+        <v>0.9614</v>
       </c>
       <c r="J122" t="n">
-        <v>25.3083</v>
+        <v>27.8806</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.34</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6623</v>
+        <v>0.7336</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2067</v>
+        <v>21.2744</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6353</v>
+        <v>0.7039</v>
       </c>
       <c r="J124" t="n">
-        <v>18.4237</v>
+        <v>20.4131</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3692</v>
+        <v>-0.3496</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.7068</v>
+        <v>-10.1384</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5918</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.1622</v>
+        <v>-16.0051</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.499</v>
+        <v>0.5498</v>
       </c>
       <c r="J127" t="n">
-        <v>14.471</v>
+        <v>15.9442</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.22</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4342</v>
+        <v>0.4756</v>
       </c>
       <c r="J128" t="n">
-        <v>12.5918</v>
+        <v>13.7924</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.5284</v>
+        <v>-7.9634</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3462</v>
+        <v>-0.3589</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.0398</v>
+        <v>-10.4081</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3556</v>
+        <v>-0.3681</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.3124</v>
+        <v>-10.6749</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5441</v>
+        <v>0.5345</v>
       </c>
       <c r="J132" t="n">
-        <v>22.3081</v>
+        <v>21.9145</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2723</v>
+        <v>0.2806</v>
       </c>
       <c r="J133" t="n">
-        <v>11.1643</v>
+        <v>11.5046</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1726</v>
+        <v>0.1838</v>
       </c>
       <c r="J134" t="n">
-        <v>7.0766</v>
+        <v>7.5358</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0578</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>2.3698</v>
+        <v>2.7716</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2156</v>
+        <v>-0.2277</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.839600000000001</v>
+        <v>-9.335699999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0586</v>
+        <v>0.9997</v>
       </c>
       <c r="J137" t="n">
-        <v>43.4026</v>
+        <v>40.9877</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2524</v>
+        <v>0.2543</v>
       </c>
       <c r="J138" t="n">
-        <v>10.3484</v>
+        <v>10.4263</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2041</v>
+        <v>-0.205</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.3681</v>
+        <v>-8.404999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4413</v>
+        <v>-0.4247</v>
       </c>
       <c r="J140" t="n">
-        <v>-18.0933</v>
+        <v>-17.4127</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5232</v>
+        <v>-0.4986</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.4512</v>
+        <v>-20.4426</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.767</v>
+        <v>0.7215</v>
       </c>
       <c r="J142" t="n">
-        <v>21.476</v>
+        <v>20.202</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4638</v>
+        <v>0.4517</v>
       </c>
       <c r="J143" t="n">
-        <v>12.9864</v>
+        <v>12.6476</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3561</v>
+        <v>0.3534</v>
       </c>
       <c r="J144" t="n">
-        <v>9.970800000000001</v>
+        <v>9.895200000000001</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1831</v>
+        <v>0.1907</v>
       </c>
       <c r="J145" t="n">
-        <v>5.1268</v>
+        <v>5.3396</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7186</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.1208</v>
+        <v>-18.7572</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6821</v>
+        <v>0.6569</v>
       </c>
       <c r="J147" t="n">
-        <v>19.0988</v>
+        <v>18.3932</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2027</v>
+        <v>0.2108</v>
       </c>
       <c r="J148" t="n">
-        <v>5.6756</v>
+        <v>5.9024</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0509</v>
+        <v>-0.0589</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.4252</v>
+        <v>-1.6492</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1127</v>
+        <v>-0.1245</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.1556</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2991</v>
+        <v>-0.3113</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.3748</v>
+        <v>-8.7164</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6014</v>
+        <v>0.5687</v>
       </c>
       <c r="J152" t="n">
-        <v>17.4406</v>
+        <v>16.4923</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1337</v>
+        <v>0.1379</v>
       </c>
       <c r="J153" t="n">
-        <v>3.8773</v>
+        <v>3.9991</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1337</v>
+        <v>0.1379</v>
       </c>
       <c r="J154" t="n">
-        <v>3.8773</v>
+        <v>3.9991</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0514</v>
+        <v>-0.0574</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.4906</v>
+        <v>-1.6646</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8943</v>
+        <v>-0.8275</v>
       </c>
       <c r="J156" t="n">
-        <v>-25.9347</v>
+        <v>-23.9975</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4631</v>
+        <v>0.4621</v>
       </c>
       <c r="J157" t="n">
-        <v>13.4299</v>
+        <v>13.4009</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.357</v>
+        <v>0.363</v>
       </c>
       <c r="J158" t="n">
-        <v>10.353</v>
+        <v>10.527</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2651</v>
+        <v>0.2755</v>
       </c>
       <c r="J159" t="n">
-        <v>7.6879</v>
+        <v>7.9895</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2082</v>
+        <v>0.2201</v>
       </c>
       <c r="J160" t="n">
-        <v>6.0378</v>
+        <v>6.3829</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1231</v>
+        <v>-0.1325</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.5699</v>
+        <v>-3.8425</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0437</v>
+        <v>0.0159</v>
       </c>
       <c r="J162" t="n">
-        <v>1.0925</v>
+        <v>0.3975</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.134</v>
+        <v>-0.1549</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.35</v>
+        <v>-3.8725</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2186</v>
+        <v>-0.2389</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.465</v>
+        <v>-5.9725</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3588</v>
+        <v>-0.3756</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5544</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.86</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.102</v>
+        <v>1.0668</v>
       </c>
       <c r="J167" t="n">
-        <v>27.55</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0091</v>
+        <v>0.9593</v>
       </c>
       <c r="J168" t="n">
-        <v>25.2275</v>
+        <v>23.9825</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9929</v>
+        <v>0.9418</v>
       </c>
       <c r="J169" t="n">
-        <v>24.8225</v>
+        <v>23.545</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7463</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>18.6575</v>
+        <v>17.905</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1209</v>
+        <v>0.1476</v>
       </c>
       <c r="J171" t="n">
-        <v>3.0225</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0474</v>
+        <v>-0.0641</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.0902</v>
+        <v>-1.4743</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.073</v>
+        <v>-0.0907</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.679</v>
+        <v>-2.0861</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3183</v>
+        <v>-0.3354</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.3209</v>
+        <v>-7.7142</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3183</v>
+        <v>-0.3354</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.3209</v>
+        <v>-7.7142</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3278</v>
+        <v>-0.3445</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.5394</v>
+        <v>-7.9235</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.84</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5256</v>
+        <v>1.517</v>
       </c>
       <c r="J177" t="n">
-        <v>35.0888</v>
+        <v>34.891</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.5</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1164</v>
+        <v>1.0822</v>
       </c>
       <c r="J178" t="n">
-        <v>25.6772</v>
+        <v>24.8906</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7032</v>
+        <v>0.6776</v>
       </c>
       <c r="J179" t="n">
-        <v>16.1736</v>
+        <v>15.5848</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1555</v>
+        <v>0.1797</v>
       </c>
       <c r="J180" t="n">
-        <v>3.5765</v>
+        <v>4.1331</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3423</v>
+        <v>-0.3171</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.8729</v>
+        <v>-7.2933</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.588</v>
+        <v>0.5605</v>
       </c>
       <c r="J182" t="n">
-        <v>14.7</v>
+        <v>14.0125</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0621</v>
+        <v>-0.0756</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.5525</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1728</v>
+        <v>-0.1898</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.32</v>
+        <v>-4.745</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3292</v>
+        <v>-0.3439</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.23</v>
+        <v>-8.5975</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.423</v>
+        <v>-0.4338</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.575</v>
+        <v>-10.845</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2859</v>
+        <v>1.2641</v>
       </c>
       <c r="J187" t="n">
-        <v>32.1475</v>
+        <v>31.6025</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9936</v>
+        <v>0.9424</v>
       </c>
       <c r="J188" t="n">
-        <v>24.84</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9936</v>
+        <v>0.9424</v>
       </c>
       <c r="J189" t="n">
-        <v>24.84</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5503</v>
       </c>
       <c r="J190" t="n">
-        <v>14</v>
+        <v>13.7575</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2125</v>
+        <v>-0.1929</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.3125</v>
+        <v>-4.8225</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7795</v>
+        <v>0.7207</v>
       </c>
       <c r="J192" t="n">
-        <v>16.3695</v>
+        <v>15.1347</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1468</v>
+        <v>-0.1674</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.0828</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.79</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2198</v>
+        <v>-0.2398</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.6158</v>
+        <v>-5.0358</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.41</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5739</v>
+        <v>-0.578</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.0519</v>
+        <v>-12.138</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.39</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5923</v>
+        <v>-0.5951</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.4383</v>
+        <v>-12.4971</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3654</v>
+        <v>1.3535</v>
       </c>
       <c r="J197" t="n">
-        <v>28.6734</v>
+        <v>28.4235</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0369</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>21.7749</v>
+        <v>20.8845</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.43</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0086</v>
+        <v>0.9626</v>
       </c>
       <c r="J199" t="n">
-        <v>21.1806</v>
+        <v>20.2146</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.9761</v>
+        <v>0.9282</v>
       </c>
       <c r="J200" t="n">
-        <v>20.4981</v>
+        <v>19.4922</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.3</v>
       </c>
       <c r="I201" t="n">
-        <v>0.7433</v>
+        <v>0.7185</v>
       </c>
       <c r="J201" t="n">
-        <v>15.6093</v>
+        <v>15.0885</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.26</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7053</v>
+        <v>0.6742</v>
       </c>
       <c r="J202" t="n">
-        <v>19.7484</v>
+        <v>18.8776</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7053</v>
+        <v>0.6742</v>
       </c>
       <c r="J203" t="n">
-        <v>19.7484</v>
+        <v>18.8776</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6105</v>
+        <v>0.5899</v>
       </c>
       <c r="J204" t="n">
-        <v>17.094</v>
+        <v>16.5172</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3886</v>
+        <v>0.3885</v>
       </c>
       <c r="J205" t="n">
-        <v>10.8808</v>
+        <v>10.878</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1237</v>
+        <v>0.1409</v>
       </c>
       <c r="J206" t="n">
-        <v>3.4636</v>
+        <v>3.9452</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8531</v>
+        <v>0.8047</v>
       </c>
       <c r="J207" t="n">
-        <v>23.8868</v>
+        <v>22.5316</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.89</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.8696</v>
+        <v>-4.2784</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.8696</v>
+        <v>-4.2784</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2213</v>
+        <v>-0.2365</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.1964</v>
+        <v>-6.622</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.67</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3571</v>
+        <v>-0.3692</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.998799999999999</v>
+        <v>-10.3376</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5536</v>
+        <v>0.5219</v>
       </c>
       <c r="J212" t="n">
-        <v>11.6256</v>
+        <v>10.9599</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0211</v>
+        <v>-0.0359</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.4431</v>
+        <v>-0.7539</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.66</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3475</v>
+        <v>-0.3634</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.2975</v>
+        <v>-7.6314</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.65</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3569</v>
+        <v>-0.3724</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.4949</v>
+        <v>-7.8204</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.515</v>
+        <v>-0.5222</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.815</v>
+        <v>-10.9662</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.98</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6707</v>
+        <v>1.6715</v>
       </c>
       <c r="J217" t="n">
-        <v>35.0847</v>
+        <v>35.1015</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.95</v>
+        <v>0.9001</v>
       </c>
       <c r="J218" t="n">
-        <v>19.95</v>
+        <v>18.9021</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.26</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6683</v>
+        <v>0.6489</v>
       </c>
       <c r="J219" t="n">
-        <v>14.0343</v>
+        <v>13.6269</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.24</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6212</v>
+        <v>0.6071</v>
       </c>
       <c r="J220" t="n">
-        <v>13.0452</v>
+        <v>12.7491</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0423</v>
+        <v>0.0747</v>
       </c>
       <c r="J221" t="n">
-        <v>0.8883</v>
+        <v>1.5687</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7567</v>
+        <v>0.7144</v>
       </c>
       <c r="J222" t="n">
-        <v>26.4845</v>
+        <v>25.004</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6836</v>
+        <v>0.65</v>
       </c>
       <c r="J223" t="n">
-        <v>23.926</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.1</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3235</v>
+        <v>0.3246</v>
       </c>
       <c r="J224" t="n">
-        <v>11.3225</v>
+        <v>11.361</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1105</v>
+        <v>0.1222</v>
       </c>
       <c r="J225" t="n">
-        <v>3.8675</v>
+        <v>4.277</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5431</v>
+        <v>-0.5125</v>
       </c>
       <c r="J226" t="n">
-        <v>-19.0085</v>
+        <v>-17.9375</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3473</v>
+        <v>0.3479</v>
       </c>
       <c r="J227" t="n">
-        <v>12.1555</v>
+        <v>12.1765</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2484</v>
+        <v>0.254</v>
       </c>
       <c r="J228" t="n">
-        <v>8.694000000000001</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1635</v>
+        <v>0.1714</v>
       </c>
       <c r="J229" t="n">
-        <v>5.7225</v>
+        <v>5.999</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1334</v>
+        <v>-0.1463</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.669</v>
+        <v>-5.1205</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2874</v>
+        <v>-0.3002</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.059</v>
+        <v>-10.507</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4659</v>
+        <v>0.4572</v>
       </c>
       <c r="J232" t="n">
-        <v>13.977</v>
+        <v>13.716</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1215</v>
+        <v>0.1285</v>
       </c>
       <c r="J233" t="n">
-        <v>3.645</v>
+        <v>3.855</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.96</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0609</v>
+        <v>-0.0708</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.827</v>
+        <v>-2.124</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1424</v>
+        <v>-0.156</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.272</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.77</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2657</v>
+        <v>-0.2794</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.971</v>
+        <v>-8.382</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0653</v>
+        <v>1.0155</v>
       </c>
       <c r="J237" t="n">
-        <v>31.959</v>
+        <v>30.465</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9879</v>
+        <v>0.9266</v>
       </c>
       <c r="J238" t="n">
-        <v>29.637</v>
+        <v>27.798</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1671</v>
+        <v>0.1797</v>
       </c>
       <c r="J239" t="n">
-        <v>5.013</v>
+        <v>5.391</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2349</v>
+        <v>-0.2264</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.047</v>
+        <v>-6.792</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.89</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4168</v>
+        <v>-0.3957</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.504</v>
+        <v>-11.871</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5609</v>
+        <v>0.5373</v>
       </c>
       <c r="J242" t="n">
-        <v>16.2661</v>
+        <v>15.5817</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0261</v>
+        <v>0.0188</v>
       </c>
       <c r="J243" t="n">
-        <v>0.7569</v>
+        <v>0.5452</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.089</v>
+        <v>-0.1031</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.581</v>
+        <v>-2.9899</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3785</v>
+        <v>-0.391</v>
       </c>
       <c r="J245" t="n">
-        <v>-10.9765</v>
+        <v>-11.339</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4158</v>
+        <v>-0.4266</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.0582</v>
+        <v>-12.3714</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.64</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3075</v>
+        <v>1.2832</v>
       </c>
       <c r="J247" t="n">
-        <v>37.9175</v>
+        <v>37.2128</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9779</v>
+        <v>0.922</v>
       </c>
       <c r="J248" t="n">
-        <v>28.3591</v>
+        <v>26.738</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.13</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3761</v>
+        <v>0.3799</v>
       </c>
       <c r="J249" t="n">
-        <v>10.9069</v>
+        <v>11.0171</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0751</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J250" t="n">
-        <v>2.1779</v>
+        <v>2.8304</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.058</v>
+        <v>-0.0402</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.682</v>
+        <v>-1.1658</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>0.9</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.1004</v>
+        <v>-0.1209</v>
       </c>
       <c r="J252" t="n">
-        <v>-2.2088</v>
+        <v>-2.6598</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1677</v>
+        <v>-0.1884</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.6894</v>
+        <v>-4.1448</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2481</v>
+        <v>-0.2678</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.4582</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.73</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2753</v>
+        <v>-0.2947</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.0566</v>
+        <v>-6.4834</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.51</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4809</v>
+        <v>-0.4911</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.5798</v>
+        <v>-10.8042</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4723</v>
+        <v>1.462</v>
       </c>
       <c r="J257" t="n">
-        <v>32.3906</v>
+        <v>32.164</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9908</v>
+        <v>0.9401</v>
       </c>
       <c r="J258" t="n">
-        <v>21.7976</v>
+        <v>20.6822</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.38</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9359</v>
+        <v>0.8855</v>
       </c>
       <c r="J259" t="n">
-        <v>20.5898</v>
+        <v>19.481</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7887</v>
+        <v>0.7541</v>
       </c>
       <c r="J260" t="n">
-        <v>17.3514</v>
+        <v>16.5902</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6548</v>
+        <v>-0.6014</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.4056</v>
+        <v>-13.2308</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2938</v>
+        <v>0.2962</v>
       </c>
       <c r="J262" t="n">
-        <v>7.9326</v>
+        <v>7.9974</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0707</v>
+        <v>0.0767</v>
       </c>
       <c r="J263" t="n">
-        <v>1.9089</v>
+        <v>2.0709</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="J264" t="n">
-        <v>0.0945</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.9</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1314</v>
+        <v>-0.1447</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.5478</v>
+        <v>-3.9069</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.83</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.5512</v>
+        <v>-5.9346</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.6</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2763</v>
+        <v>1.2468</v>
       </c>
       <c r="J267" t="n">
-        <v>34.4601</v>
+        <v>33.6636</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7316</v>
+        <v>0.6969</v>
       </c>
       <c r="J268" t="n">
-        <v>19.7532</v>
+        <v>18.8163</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.708</v>
+        <v>0.6761</v>
       </c>
       <c r="J269" t="n">
-        <v>19.116</v>
+        <v>18.2547</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0544</v>
+        <v>0.0725</v>
       </c>
       <c r="J270" t="n">
-        <v>1.4688</v>
+        <v>1.9575</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.71</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8939</v>
+        <v>-0.8193</v>
       </c>
       <c r="J271" t="n">
-        <v>-24.1353</v>
+        <v>-22.1211</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0325</v>
+        <v>-0.0557</v>
       </c>
       <c r="J272" t="n">
-        <v>-0.6825</v>
+        <v>-1.1697</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1646</v>
+        <v>-0.1882</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.4566</v>
+        <v>-3.9522</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.6</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3869</v>
+        <v>-0.404</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.1249</v>
+        <v>-8.484</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.57</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4149</v>
+        <v>-0.4306</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.712899999999999</v>
+        <v>-9.0426</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4898</v>
+        <v>-0.501</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.2858</v>
+        <v>-10.521</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.74</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3798</v>
+        <v>1.3683</v>
       </c>
       <c r="J277" t="n">
-        <v>28.9758</v>
+        <v>28.7343</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.62</v>
       </c>
       <c r="I278" t="n">
-        <v>1.2401</v>
+        <v>1.2194</v>
       </c>
       <c r="J278" t="n">
-        <v>26.0421</v>
+        <v>25.6074</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.61</v>
       </c>
       <c r="I279" t="n">
-        <v>1.2284</v>
+        <v>1.2068</v>
       </c>
       <c r="J279" t="n">
-        <v>25.7964</v>
+        <v>25.3428</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1.22</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5589</v>
+        <v>0.5544</v>
       </c>
       <c r="J280" t="n">
-        <v>11.7369</v>
+        <v>11.6424</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>1.05</v>
       </c>
       <c r="I281" t="n">
-        <v>0.0959</v>
+        <v>0.13</v>
       </c>
       <c r="J281" t="n">
-        <v>2.0139</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.5</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1546</v>
+        <v>1.1158</v>
       </c>
       <c r="J282" t="n">
-        <v>41.5656</v>
+        <v>40.1688</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5201</v>
+        <v>0.5071</v>
       </c>
       <c r="J283" t="n">
-        <v>18.7236</v>
+        <v>18.2556</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.07</v>
       </c>
       <c r="I284" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="J284" t="n">
-        <v>8.172000000000001</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0359</v>
+        <v>-0.0247</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.2924</v>
+        <v>-0.8892</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.0359</v>
+        <v>-0.0247</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.2924</v>
+        <v>-0.8892</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.56</v>
       </c>
       <c r="I287" t="n">
-        <v>1.028</v>
+        <v>0.9811</v>
       </c>
       <c r="J287" t="n">
-        <v>37.008</v>
+        <v>35.3196</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2054</v>
+        <v>0.2127</v>
       </c>
       <c r="J288" t="n">
-        <v>7.3944</v>
+        <v>7.6572</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.93</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0998</v>
+        <v>-0.1113</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.5928</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.317</v>
+        <v>-0.329</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.412</v>
+        <v>-11.844</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.336</v>
+        <v>-0.3475</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.096</v>
+        <v>-12.51</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3509</v>
+        <v>0.3505</v>
       </c>
       <c r="J292" t="n">
-        <v>10.1761</v>
+        <v>10.1645</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.272</v>
+        <v>0.2758</v>
       </c>
       <c r="J293" t="n">
-        <v>7.888</v>
+        <v>7.9982</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1436</v>
+        <v>0.151</v>
       </c>
       <c r="J294" t="n">
-        <v>4.1644</v>
+        <v>4.379</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.132</v>
+        <v>-0.1452</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.828</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3434</v>
+        <v>-0.3551</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.958600000000001</v>
+        <v>-10.2979</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.51</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1734</v>
+        <v>1.1348</v>
       </c>
       <c r="J297" t="n">
-        <v>34.0286</v>
+        <v>32.9092</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5744</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>16.6576</v>
+        <v>16.0921</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4488</v>
+        <v>0.4415</v>
       </c>
       <c r="J299" t="n">
-        <v>13.0152</v>
+        <v>12.8035</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3854</v>
+        <v>-0.3674</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.1766</v>
+        <v>-10.6546</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4142</v>
+        <v>-0.3938</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.0118</v>
+        <v>-11.4202</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4362</v>
+        <v>1.4262</v>
       </c>
       <c r="J302" t="n">
-        <v>31.5964</v>
+        <v>31.3764</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1165</v>
+        <v>1.0848</v>
       </c>
       <c r="J303" t="n">
-        <v>24.563</v>
+        <v>23.8656</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.42</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9994</v>
+        <v>0.951</v>
       </c>
       <c r="J304" t="n">
-        <v>21.9868</v>
+        <v>20.922</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6045</v>
       </c>
       <c r="J305" t="n">
-        <v>13.5828</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.0732</v>
+        <v>0.1056</v>
       </c>
       <c r="J306" t="n">
-        <v>1.6104</v>
+        <v>2.3232</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.3</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7758</v>
+        <v>0.7151</v>
       </c>
       <c r="J307" t="n">
-        <v>17.0676</v>
+        <v>15.7322</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2069</v>
+        <v>-0.2276</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.5518</v>
+        <v>-5.0072</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4041</v>
+        <v>-0.419</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.8902</v>
+        <v>-9.218</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.5</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4881</v>
+        <v>-0.4982</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.7382</v>
+        <v>-10.9604</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.48</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5067</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.1474</v>
+        <v>-11.3432</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.46</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8748</v>
+        <v>0.8308</v>
       </c>
       <c r="J312" t="n">
-        <v>26.244</v>
+        <v>24.924</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.28</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5722</v>
+        <v>0.5583</v>
       </c>
       <c r="J313" t="n">
-        <v>17.166</v>
+        <v>16.749</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.87</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.17</v>
+        <v>-0.1827</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.1</v>
+        <v>-5.481</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2322</v>
+        <v>-0.245</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.966</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3203</v>
+        <v>-0.3316</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.609</v>
+        <v>-9.948</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.4</v>
       </c>
       <c r="I317" t="n">
-        <v>1.0404</v>
+        <v>0.9816</v>
       </c>
       <c r="J317" t="n">
-        <v>31.212</v>
+        <v>29.448</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.32</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8831</v>
+        <v>0.8237</v>
       </c>
       <c r="J318" t="n">
-        <v>26.493</v>
+        <v>24.711</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.02</v>
       </c>
       <c r="I319" t="n">
-        <v>0.0776</v>
+        <v>0.0886</v>
       </c>
       <c r="J319" t="n">
-        <v>2.328</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2509</v>
+        <v>-0.2456</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.527</v>
+        <v>-7.368</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8467</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="J321" t="n">
-        <v>-25.401</v>
+        <v>-23.454</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.92</v>
       </c>
       <c r="I322" t="n">
-        <v>1.5831</v>
+        <v>1.583</v>
       </c>
       <c r="J322" t="n">
-        <v>31.662</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.47</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0619</v>
+        <v>1.0242</v>
       </c>
       <c r="J323" t="n">
-        <v>21.238</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.33</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8118</v>
+        <v>0.7786</v>
       </c>
       <c r="J324" t="n">
-        <v>16.236</v>
+        <v>15.572</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.33</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8118</v>
+        <v>0.7786</v>
       </c>
       <c r="J325" t="n">
-        <v>16.236</v>
+        <v>15.572</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.605</v>
+        <v>0.5958</v>
       </c>
       <c r="J326" t="n">
-        <v>12.1</v>
+        <v>11.916</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>1.1788</v>
+        <v>1.1293</v>
       </c>
       <c r="J327" t="n">
-        <v>23.576</v>
+        <v>22.586</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.3616</v>
+        <v>-0.3794</v>
       </c>
       <c r="J328" t="n">
-        <v>-7.232</v>
+        <v>-7.588</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4457</v>
+        <v>-0.4591</v>
       </c>
       <c r="J329" t="n">
-        <v>-8.914</v>
+        <v>-9.182</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.51</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4737</v>
+        <v>-0.4855</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.474</v>
+        <v>-9.710000000000001</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.27</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6973</v>
+        <v>-0.6927</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.946</v>
+        <v>-13.854</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5298</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J332" t="n">
-        <v>15.3642</v>
+        <v>15.0104</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.494</v>
+        <v>0.4847</v>
       </c>
       <c r="J333" t="n">
-        <v>14.326</v>
+        <v>14.0563</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="J334" t="n">
-        <v>-2.5491</v>
+        <v>-2.8681</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.79</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2488</v>
+        <v>-0.2621</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.2152</v>
+        <v>-7.6009</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.78</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2587</v>
+        <v>-0.2719</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.5023</v>
+        <v>-7.8851</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.25</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6893</v>
+        <v>0.6585</v>
       </c>
       <c r="J337" t="n">
-        <v>19.9897</v>
+        <v>19.0965</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.23</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6413</v>
+        <v>0.6159</v>
       </c>
       <c r="J338" t="n">
-        <v>18.5977</v>
+        <v>17.8611</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4946</v>
+        <v>0.4842</v>
       </c>
       <c r="J339" t="n">
-        <v>14.3434</v>
+        <v>14.0418</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J340" t="n">
-        <v>10.6633</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.0369</v>
+        <v>-0.0254</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.0701</v>
+        <v>-0.7366</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.61</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2381</v>
+        <v>1.2153</v>
       </c>
       <c r="J342" t="n">
-        <v>27.2382</v>
+        <v>26.7366</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.53</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1421</v>
+        <v>1.1122</v>
       </c>
       <c r="J343" t="n">
-        <v>25.1262</v>
+        <v>24.4684</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.42</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0006</v>
+        <v>0.952</v>
       </c>
       <c r="J344" t="n">
-        <v>22.0132</v>
+        <v>20.944</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.3</v>
       </c>
       <c r="I345" t="n">
-        <v>0.7583</v>
+        <v>0.7289</v>
       </c>
       <c r="J345" t="n">
-        <v>16.6826</v>
+        <v>16.0358</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2013</v>
+        <v>0.2263</v>
       </c>
       <c r="J346" t="n">
-        <v>4.4286</v>
+        <v>4.9786</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>0.76</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.227</v>
+        <v>-0.2515</v>
       </c>
       <c r="J347" t="n">
-        <v>-4.994</v>
+        <v>-5.533</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2976</v>
+        <v>-0.3195</v>
       </c>
       <c r="J348" t="n">
-        <v>-6.5472</v>
+        <v>-7.029</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3166</v>
+        <v>-0.3378</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.9652</v>
+        <v>-7.4316</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.58</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3974</v>
+        <v>-0.4153</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.742800000000001</v>
+        <v>-9.1366</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4815</v>
+        <v>-0.4945</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.593</v>
+        <v>-10.879</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.52</v>
+        <v>0.5017</v>
       </c>
       <c r="J352" t="n">
-        <v>15.6</v>
+        <v>15.051</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4139</v>
+        <v>0.4057</v>
       </c>
       <c r="J353" t="n">
-        <v>12.417</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.12</v>
       </c>
       <c r="I354" t="n">
-        <v>0.3867</v>
+        <v>0.3808</v>
       </c>
       <c r="J354" t="n">
-        <v>11.601</v>
+        <v>11.424</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.04</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1532</v>
+        <v>0.1613</v>
       </c>
       <c r="J355" t="n">
-        <v>4.596</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5592</v>
+        <v>-0.529</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.776</v>
+        <v>-15.87</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.48</v>
       </c>
       <c r="I357" t="n">
-        <v>0.8918</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>26.754</v>
+        <v>25.449</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2329</v>
+        <v>0.2428</v>
       </c>
       <c r="J358" t="n">
-        <v>6.987</v>
+        <v>7.284</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.03</v>
       </c>
       <c r="I359" t="n">
-        <v>0.0833</v>
+        <v>0.094</v>
       </c>
       <c r="J359" t="n">
-        <v>2.499</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1069</v>
+        <v>-0.1168</v>
       </c>
       <c r="J360" t="n">
-        <v>-3.207</v>
+        <v>-3.504</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.78</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2661</v>
+        <v>-0.2777</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.983</v>
+        <v>-8.331</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.07</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2846</v>
+        <v>0.2657</v>
       </c>
       <c r="J362" t="n">
-        <v>6.2612</v>
+        <v>5.8454</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J363" t="n">
-        <v>-1.3904</v>
+        <v>-1.8282</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.7</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3029</v>
+        <v>-0.3216</v>
       </c>
       <c r="J364" t="n">
-        <v>-6.6638</v>
+        <v>-7.0752</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.58</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4153</v>
+        <v>-0.4293</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.1366</v>
+        <v>-9.444599999999999</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.45</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5362</v>
+        <v>-0.543</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.7964</v>
+        <v>-11.946</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.73</v>
       </c>
       <c r="I367" t="n">
-        <v>1.3879</v>
+        <v>1.3733</v>
       </c>
       <c r="J367" t="n">
-        <v>30.5338</v>
+        <v>30.2126</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.65</v>
       </c>
       <c r="I368" t="n">
-        <v>1.2928</v>
+        <v>1.2724</v>
       </c>
       <c r="J368" t="n">
-        <v>28.4416</v>
+        <v>27.9928</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.41</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9895</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J369" t="n">
-        <v>21.769</v>
+        <v>20.658</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.02</v>
       </c>
       <c r="I370" t="n">
-        <v>0.0114</v>
+        <v>0.0424</v>
       </c>
       <c r="J370" t="n">
-        <v>0.2508</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.286</v>
+        <v>-0.2623</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.292</v>
+        <v>-5.7706</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.08</v>
       </c>
       <c r="I372" t="n">
-        <v>0.2108</v>
+        <v>0.2167</v>
       </c>
       <c r="J372" t="n">
-        <v>5.9024</v>
+        <v>6.0676</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.03</v>
       </c>
       <c r="I373" t="n">
-        <v>0.0965</v>
+        <v>0.1033</v>
       </c>
       <c r="J373" t="n">
-        <v>2.702</v>
+        <v>2.8924</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0703</v>
+        <v>0.0765</v>
       </c>
       <c r="J374" t="n">
-        <v>1.9684</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1316</v>
+        <v>-0.1449</v>
       </c>
       <c r="J375" t="n">
-        <v>-3.6848</v>
+        <v>-4.0572</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.85</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1852</v>
+        <v>-0.1993</v>
       </c>
       <c r="J376" t="n">
-        <v>-5.1856</v>
+        <v>-5.5804</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.77</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4812</v>
+        <v>1.4641</v>
       </c>
       <c r="J377" t="n">
-        <v>41.4736</v>
+        <v>40.9948</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7494</v>
+        <v>0.7137</v>
       </c>
       <c r="J378" t="n">
-        <v>20.9832</v>
+        <v>19.9836</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.3044</v>
+        <v>0.3115</v>
       </c>
       <c r="J379" t="n">
-        <v>8.523199999999999</v>
+        <v>8.722</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.97</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.18</v>
+        <v>-0.1701</v>
       </c>
       <c r="J380" t="n">
-        <v>-5.04</v>
+        <v>-4.7628</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.84</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5681</v>
+        <v>-0.5301</v>
       </c>
       <c r="J381" t="n">
-        <v>-15.9068</v>
+        <v>-14.8428</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.82</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4654</v>
+        <v>1.4599</v>
       </c>
       <c r="J382" t="n">
-        <v>30.7734</v>
+        <v>30.6579</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.74</v>
       </c>
       <c r="I383" t="n">
-        <v>1.3741</v>
+        <v>1.3633</v>
       </c>
       <c r="J383" t="n">
-        <v>28.8561</v>
+        <v>28.6293</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0723</v>
+        <v>1.0369</v>
       </c>
       <c r="J384" t="n">
-        <v>22.5183</v>
+        <v>21.7749</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.29</v>
       </c>
       <c r="I385" t="n">
-        <v>0.7173</v>
+        <v>0.6962</v>
       </c>
       <c r="J385" t="n">
-        <v>15.0633</v>
+        <v>14.6202</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.07</v>
       </c>
       <c r="I386" t="n">
-        <v>0.152</v>
+        <v>0.1847</v>
       </c>
       <c r="J386" t="n">
-        <v>3.192</v>
+        <v>3.8787</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.07</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2543</v>
+        <v>0.2434</v>
       </c>
       <c r="J387" t="n">
-        <v>5.3403</v>
+        <v>5.1114</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.97</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.0225</v>
+        <v>-0.0369</v>
       </c>
       <c r="J388" t="n">
-        <v>-0.4725</v>
+        <v>-0.7749</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.301</v>
+        <v>-0.3183</v>
       </c>
       <c r="J389" t="n">
-        <v>-6.321</v>
+        <v>-6.6843</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.7</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3105</v>
+        <v>-0.3276</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.5205</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.55</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4512</v>
+        <v>-0.462</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.475199999999999</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>2.09</v>
       </c>
       <c r="I392" t="n">
-        <v>1.7664</v>
+        <v>1.7754</v>
       </c>
       <c r="J392" t="n">
-        <v>40.6272</v>
+        <v>40.8342</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.48</v>
       </c>
       <c r="I393" t="n">
-        <v>1.0721</v>
+        <v>1.0368</v>
       </c>
       <c r="J393" t="n">
-        <v>24.6583</v>
+        <v>23.8464</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.42</v>
       </c>
       <c r="I394" t="n">
-        <v>0.9903</v>
+        <v>0.9436</v>
       </c>
       <c r="J394" t="n">
-        <v>22.7769</v>
+        <v>21.7028</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>1.26</v>
       </c>
       <c r="I395" t="n">
-        <v>0.6469</v>
+        <v>0.6341</v>
       </c>
       <c r="J395" t="n">
-        <v>14.8787</v>
+        <v>14.5843</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>1.17</v>
       </c>
       <c r="I396" t="n">
-        <v>0.427</v>
+        <v>0.4374</v>
       </c>
       <c r="J396" t="n">
-        <v>9.821</v>
+        <v>10.0602</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>0.75</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.2245</v>
+        <v>-0.2514</v>
       </c>
       <c r="J397" t="n">
-        <v>-5.1635</v>
+        <v>-5.7822</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>0.64</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.3366</v>
+        <v>-0.3585</v>
       </c>
       <c r="J398" t="n">
-        <v>-7.7418</v>
+        <v>-8.2455</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.53</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.4357</v>
+        <v>-0.4529</v>
       </c>
       <c r="J399" t="n">
-        <v>-10.0211</v>
+        <v>-10.4167</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.53</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4357</v>
+        <v>-0.4529</v>
       </c>
       <c r="J400" t="n">
-        <v>-10.0211</v>
+        <v>-10.4167</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.52</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.445</v>
+        <v>-0.4616</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.235</v>
+        <v>-10.6168</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.58</v>
       </c>
       <c r="I402" t="n">
-        <v>1.2614</v>
+        <v>1.2291</v>
       </c>
       <c r="J402" t="n">
-        <v>34.0578</v>
+        <v>33.1857</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4222</v>
+        <v>0.4174</v>
       </c>
       <c r="J403" t="n">
-        <v>11.3994</v>
+        <v>11.2698</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3439</v>
+        <v>0.3453</v>
       </c>
       <c r="J404" t="n">
-        <v>9.285299999999999</v>
+        <v>9.3231</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.05</v>
       </c>
       <c r="I405" t="n">
-        <v>0.1676</v>
+        <v>0.1801</v>
       </c>
       <c r="J405" t="n">
-        <v>4.5252</v>
+        <v>4.8627</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6338</v>
+        <v>-0.5914</v>
       </c>
       <c r="J406" t="n">
-        <v>-17.1126</v>
+        <v>-15.9678</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1907</v>
+        <v>0.1911</v>
       </c>
       <c r="J407" t="n">
-        <v>5.1489</v>
+        <v>5.1597</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.03</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1177</v>
+        <v>0.1187</v>
       </c>
       <c r="J408" t="n">
-        <v>3.1779</v>
+        <v>3.2049</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1241</v>
+        <v>-0.1392</v>
       </c>
       <c r="J409" t="n">
-        <v>-3.3507</v>
+        <v>-3.7584</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.83</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1963</v>
+        <v>-0.2126</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.3001</v>
+        <v>-5.7402</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.66</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3615</v>
+        <v>-0.3744</v>
       </c>
       <c r="J411" t="n">
-        <v>-9.7605</v>
+        <v>-10.1088</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.41</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0692</v>
+        <v>1.0134</v>
       </c>
       <c r="J412" t="n">
-        <v>27.7992</v>
+        <v>26.3484</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.35</v>
       </c>
       <c r="I413" t="n">
-        <v>0.9699</v>
+        <v>0.9005</v>
       </c>
       <c r="J413" t="n">
-        <v>25.2174</v>
+        <v>23.413</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.99</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.0613</v>
+        <v>-0.0641</v>
       </c>
       <c r="J414" t="n">
-        <v>-1.5938</v>
+        <v>-1.6666</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.9</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3592</v>
+        <v>-0.3492</v>
       </c>
       <c r="J415" t="n">
-        <v>-9.3392</v>
+        <v>-9.0792</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.53</v>
       </c>
       <c r="I416" t="n">
-        <v>-1.2887</v>
+        <v>-1.164</v>
       </c>
       <c r="J416" t="n">
-        <v>-33.5062</v>
+        <v>-30.264</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.19</v>
       </c>
       <c r="I417" t="n">
-        <v>0.4125</v>
+        <v>0.4109</v>
       </c>
       <c r="J417" t="n">
-        <v>10.725</v>
+        <v>10.6834</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.14</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3188</v>
+        <v>0.323</v>
       </c>
       <c r="J418" t="n">
-        <v>8.2888</v>
+        <v>8.398</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.03</v>
       </c>
       <c r="I419" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0973</v>
       </c>
       <c r="J419" t="n">
-        <v>2.288</v>
+        <v>2.5298</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>0.063</v>
+        <v>0.0713</v>
       </c>
       <c r="J420" t="n">
-        <v>1.638</v>
+        <v>1.8538</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.75</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.2912</v>
+        <v>-0.3033</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.5712</v>
+        <v>-7.8858</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.59</v>
       </c>
       <c r="I422" t="n">
-        <v>1.2402</v>
+        <v>1.2126</v>
       </c>
       <c r="J422" t="n">
-        <v>29.7648</v>
+        <v>29.1024</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.41</v>
       </c>
       <c r="I423" t="n">
-        <v>1.0072</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J423" t="n">
-        <v>24.1728</v>
+        <v>22.8984</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.25</v>
       </c>
       <c r="I424" t="n">
-        <v>0.6677</v>
+        <v>0.6438</v>
       </c>
       <c r="J424" t="n">
-        <v>16.0248</v>
+        <v>15.4512</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.15</v>
       </c>
       <c r="I425" t="n">
-        <v>0.424</v>
+        <v>0.4246</v>
       </c>
       <c r="J425" t="n">
-        <v>10.176</v>
+        <v>10.1904</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.9</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.418</v>
+        <v>-0.3903</v>
       </c>
       <c r="J426" t="n">
-        <v>-10.032</v>
+        <v>-9.3672</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.09</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2898</v>
+        <v>0.2795</v>
       </c>
       <c r="J427" t="n">
-        <v>6.9552</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.04</v>
       </c>
       <c r="I428" t="n">
-        <v>0.1722</v>
+        <v>0.1655</v>
       </c>
       <c r="J428" t="n">
-        <v>4.1328</v>
+        <v>3.972</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2366</v>
+        <v>-0.2547</v>
       </c>
       <c r="J429" t="n">
-        <v>-5.6784</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.2751</v>
+        <v>-0.2926</v>
       </c>
       <c r="J430" t="n">
-        <v>-6.6024</v>
+        <v>-7.0224</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.45</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.5457</v>
+        <v>-0.5505</v>
       </c>
       <c r="J431" t="n">
-        <v>-13.0968</v>
+        <v>-13.212</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2036/event_2036_evp_summary.xlsx
+++ b/database/event/2036/event_2036_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5939</v>
+        <v>8.569900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.3008</v>
+        <v>5.286</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2879</v>
+        <v>3.2982</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5939</v>
+        <v>8.569900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3508</v>
+        <v>2.3332</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2431</v>
+        <v>6.2367</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4202</v>
+        <v>2.3968</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4826</v>
+        <v>2.4608</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2431</v>
+        <v>6.2367</v>
       </c>
       <c r="K2" t="n">
         <v>140</v>
@@ -529,7 +529,7 @@
         <v>207</v>
       </c>
       <c r="M2" t="n">
-        <v>8.7257</v>
+        <v>8.6975</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3153</v>
+        <v>6.1848</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8953</v>
+        <v>3.8148</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2507</v>
+        <v>2.2117</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3153</v>
+        <v>6.1848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7654</v>
+        <v>0.7195</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5499</v>
+        <v>5.4653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7654</v>
+        <v>0.7195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7851</v>
+        <v>0.7387</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5499</v>
+        <v>5.4653</v>
       </c>
       <c r="K3" t="n">
         <v>140</v>
@@ -575,7 +575,7 @@
         <v>207</v>
       </c>
       <c r="M3" t="n">
-        <v>6.335</v>
+        <v>6.204</v>
       </c>
       <c r="N3" t="n">
         <v>347</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8559</v>
+        <v>5.7181</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6119</v>
+        <v>3.5269</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0415</v>
+        <v>1.9991</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8559</v>
+        <v>5.7181</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6844</v>
+        <v>2.6052</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1715</v>
+        <v>3.1129</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1504</v>
+        <v>3.0202</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1504</v>
+        <v>3.0202</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1715</v>
+        <v>3.1129</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>6.321899999999999</v>
+        <v>6.1331</v>
       </c>
       <c r="N4" t="n">
         <v>284</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7309</v>
+        <v>5.6112</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5348</v>
+        <v>3.461</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9846</v>
+        <v>1.9504</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7309</v>
+        <v>5.6112</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1059</v>
+        <v>1.0937</v>
       </c>
       <c r="G5" t="n">
-        <v>4.625</v>
+        <v>4.5174</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1059</v>
+        <v>1.0937</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1344</v>
+        <v>1.123</v>
       </c>
       <c r="J5" t="n">
-        <v>4.625</v>
+        <v>4.5174</v>
       </c>
       <c r="K5" t="n">
         <v>140</v>
@@ -667,7 +667,7 @@
         <v>207</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7594</v>
+        <v>5.640400000000001</v>
       </c>
       <c r="N5" t="n">
         <v>347</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2943</v>
+        <v>4.0598</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6487</v>
+        <v>2.5041</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3307</v>
+        <v>1.2436</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2943</v>
+        <v>4.0598</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4301</v>
+        <v>2.727</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1358</v>
+        <v>1.3328</v>
       </c>
       <c r="H6" t="n">
-        <v>9.7224</v>
+        <v>3.2992</v>
       </c>
       <c r="I6" t="n">
-        <v>5.25</v>
+        <v>3.3874</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1358</v>
+        <v>1.3328</v>
       </c>
       <c r="K6" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="L6" t="n">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1142</v>
+        <v>4.7202</v>
       </c>
       <c r="N6" t="n">
-        <v>192</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0748</v>
+        <v>3.9677</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5134</v>
+        <v>2.4473</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2307</v>
+        <v>1.2017</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0748</v>
+        <v>3.9677</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7621</v>
+        <v>4.2146</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3127</v>
+        <v>-0.2469</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3203</v>
+        <v>9.380800000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4059</v>
+        <v>5.267</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3127</v>
+        <v>-0.2469</v>
       </c>
       <c r="K7" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="L7" t="n">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7186</v>
+        <v>5.0201</v>
       </c>
       <c r="N7" t="n">
-        <v>347</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.699</v>
+        <v>3.7826</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2816</v>
+        <v>2.3331</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0597</v>
+        <v>1.1174</v>
       </c>
       <c r="E8" t="n">
-        <v>3.699</v>
+        <v>3.7826</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4777</v>
+        <v>2.5218</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2213</v>
+        <v>1.2608</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2808</v>
+        <v>3.0253</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7716</v>
+        <v>1.6986</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2213</v>
+        <v>1.2608</v>
       </c>
       <c r="K8" t="n">
         <v>136</v>
@@ -805,7 +805,7 @@
         <v>158</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9929</v>
+        <v>2.9594</v>
       </c>
       <c r="N8" t="n">
         <v>294</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6036</v>
+        <v>3.535</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2227</v>
+        <v>2.1804</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0162</v>
+        <v>1.0046</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6036</v>
+        <v>3.535</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2911</v>
+        <v>3.2483</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3125</v>
+        <v>0.2867</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9644</v>
+        <v>5.7529</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2207</v>
+        <v>3.2301</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3125</v>
+        <v>0.2867</v>
       </c>
       <c r="K9" t="n">
         <v>119</v>
@@ -851,7 +851,7 @@
         <v>73</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5332</v>
+        <v>3.5168</v>
       </c>
       <c r="N9" t="n">
         <v>192</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4001</v>
+        <v>3.3407</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0972</v>
+        <v>2.0606</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9236</v>
+        <v>0.9161</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4001</v>
+        <v>3.3407</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4001</v>
+        <v>3.3407</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7168</v>
+        <v>4.7059</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7168</v>
+        <v>4.7059</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7168</v>
+        <v>4.7059</v>
       </c>
       <c r="N10" t="n">
         <v>135</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3806</v>
+        <v>3.2693</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0852</v>
+        <v>2.0165</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9147</v>
+        <v>0.8835</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3806</v>
+        <v>3.2693</v>
       </c>
       <c r="F11" t="n">
-        <v>4.255</v>
+        <v>4.0702</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8744</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>9.144600000000001</v>
+        <v>8.838800000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>4.938</v>
+        <v>4.9627</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8744</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>136</v>
@@ -943,7 +943,7 @@
         <v>158</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0636</v>
+        <v>4.161799999999999</v>
       </c>
       <c r="N11" t="n">
         <v>294</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3348</v>
+        <v>3.2546</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0569</v>
+        <v>2.0075</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8939</v>
+        <v>0.8768</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3348</v>
+        <v>3.2546</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2871</v>
+        <v>3.2073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0477</v>
+        <v>0.0473</v>
       </c>
       <c r="H12" t="n">
-        <v>5.951</v>
+        <v>5.5989</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2135</v>
+        <v>3.1436</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0477</v>
+        <v>0.0473</v>
       </c>
       <c r="K12" t="n">
         <v>119</v>
@@ -989,7 +989,7 @@
         <v>73</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2612</v>
+        <v>3.1909</v>
       </c>
       <c r="N12" t="n">
         <v>192</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0684</v>
+        <v>2.9843</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8926</v>
+        <v>1.8407</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7726</v>
+        <v>0.7537</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0684</v>
+        <v>2.9843</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4512</v>
+        <v>2.454</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6172</v>
+        <v>0.5303</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1934</v>
+        <v>2.7706</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7244</v>
+        <v>1.5556</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6172</v>
+        <v>0.5303</v>
       </c>
       <c r="K13" t="n">
         <v>136</v>
@@ -1035,7 +1035,7 @@
         <v>158</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3416</v>
+        <v>2.0859</v>
       </c>
       <c r="N13" t="n">
         <v>294</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.87</v>
+        <v>2.9314</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7702</v>
+        <v>1.8081</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6823</v>
+        <v>0.7296</v>
       </c>
       <c r="E14" t="n">
-        <v>2.87</v>
+        <v>2.9314</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4365</v>
+        <v>2.388</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4335</v>
+        <v>0.5434</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6078</v>
+        <v>2.5225</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6078</v>
+        <v>2.5225</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4335</v>
+        <v>0.5434</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -1081,7 +1081,7 @@
         <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0413</v>
+        <v>3.0659</v>
       </c>
       <c r="N14" t="n">
         <v>284</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8432</v>
+        <v>2.6153</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7537</v>
+        <v>1.6131</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6701</v>
+        <v>0.5856</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8432</v>
+        <v>2.6153</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3492</v>
+        <v>1.2635</v>
       </c>
       <c r="G15" t="n">
-        <v>1.494</v>
+        <v>1.3518</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3492</v>
+        <v>1.2635</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3492</v>
+        <v>1.2635</v>
       </c>
       <c r="J15" t="n">
-        <v>1.494</v>
+        <v>1.3518</v>
       </c>
       <c r="K15" t="n">
         <v>140</v>
@@ -1127,7 +1127,7 @@
         <v>89</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8432</v>
+        <v>2.6153</v>
       </c>
       <c r="N15" t="n">
         <v>229</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6695</v>
+        <v>2.6003</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6466</v>
+        <v>1.6039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.591</v>
+        <v>0.5788</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6695</v>
+        <v>2.6003</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6695</v>
+        <v>2.6003</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1177</v>
+        <v>3.0089</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1177</v>
+        <v>3.0089</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1177</v>
+        <v>3.0089</v>
       </c>
       <c r="N16" t="n">
         <v>134</v>
@@ -1182,231 +1182,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5539</v>
+        <v>2.5262</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5753</v>
+        <v>1.5582</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5384</v>
+        <v>0.545</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5539</v>
+        <v>2.5262</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5539</v>
+        <v>2.5628</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.0366</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8647</v>
+        <v>3.1792</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8647</v>
+        <v>1.785</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.0366</v>
       </c>
       <c r="K17" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8647</v>
+        <v>1.7484</v>
       </c>
       <c r="N17" t="n">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5352</v>
+        <v>2.5006</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5637</v>
+        <v>1.5424</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5299</v>
+        <v>0.5334</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5352</v>
+        <v>2.5006</v>
       </c>
       <c r="F18" t="n">
-        <v>2.16</v>
+        <v>2.5006</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3752</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.16</v>
+        <v>2.7806</v>
       </c>
       <c r="I18" t="n">
-        <v>2.16</v>
+        <v>2.7806</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3752</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L18" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5352</v>
+        <v>2.7806</v>
       </c>
       <c r="N18" t="n">
-        <v>229</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5169</v>
+        <v>2.4538</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5524</v>
+        <v>1.5135</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5215</v>
+        <v>0.512</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5169</v>
+        <v>2.4538</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5175</v>
+        <v>2.0311</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4227</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4121</v>
+        <v>2.0311</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8425</v>
+        <v>1.1404</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4227</v>
       </c>
       <c r="K19" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8419</v>
+        <v>1.5631</v>
       </c>
       <c r="N19" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4657</v>
+        <v>2.3501</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5209</v>
+        <v>1.4496</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4982</v>
+        <v>0.4648</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4657</v>
+        <v>2.3501</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9848</v>
+        <v>2.3501</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4809</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9848</v>
+        <v>2.4356</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0718</v>
+        <v>2.4356</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4809</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L20" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5527</v>
+        <v>2.4356</v>
       </c>
       <c r="N20" t="n">
-        <v>294</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4029</v>
+        <v>2.3449</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4821</v>
+        <v>1.4463</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4696</v>
+        <v>0.4624</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4029</v>
+        <v>2.3449</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4029</v>
+        <v>2.0361</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.3088</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5342</v>
+        <v>2.0361</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5342</v>
+        <v>2.0361</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.3088</v>
       </c>
       <c r="K21" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5342</v>
+        <v>2.3449</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2563</v>
+        <v>2.3</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3917</v>
+        <v>1.4187</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4029</v>
+        <v>0.442</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2563</v>
+        <v>2.3</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8612</v>
+        <v>2.8646</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6049</v>
+        <v>-0.5646</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5374</v>
+        <v>3.6146</v>
       </c>
       <c r="I22" t="n">
-        <v>3.5374</v>
+        <v>3.6146</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6049</v>
+        <v>-0.5646</v>
       </c>
       <c r="K22" t="n">
         <v>140</v>
@@ -1449,7 +1449,7 @@
         <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9325</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
         <v>229</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1113</v>
+        <v>2.1426</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3023</v>
+        <v>1.3216</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3369</v>
+        <v>0.3703</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1113</v>
+        <v>2.1426</v>
       </c>
       <c r="F23" t="n">
-        <v>2.434</v>
+        <v>2.494</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3227</v>
+        <v>-0.3514</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1363</v>
+        <v>2.9211</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6936</v>
+        <v>1.6401</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3227</v>
+        <v>-0.3514</v>
       </c>
       <c r="K23" t="n">
         <v>119</v>
@@ -1495,7 +1495,7 @@
         <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3709</v>
+        <v>1.2887</v>
       </c>
       <c r="N23" t="n">
         <v>192</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.868</v>
+        <v>1.7692</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1522</v>
+        <v>1.0913</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2261</v>
+        <v>0.2002</v>
       </c>
       <c r="E24" t="n">
-        <v>1.868</v>
+        <v>1.7692</v>
       </c>
       <c r="F24" t="n">
-        <v>1.868</v>
+        <v>2.4397</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6705</v>
       </c>
       <c r="H24" t="n">
-        <v>1.868</v>
+        <v>2.6408</v>
       </c>
       <c r="I24" t="n">
-        <v>1.868</v>
+        <v>2.6408</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6705</v>
       </c>
       <c r="K24" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M24" t="n">
-        <v>1.868</v>
+        <v>1.9703</v>
       </c>
       <c r="N24" t="n">
-        <v>135</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7514</v>
+        <v>1.7417</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0803</v>
+        <v>1.0743</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1731</v>
+        <v>0.1876</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7514</v>
+        <v>1.7417</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4733</v>
+        <v>1.7417</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7219</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6883</v>
+        <v>1.7417</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6883</v>
+        <v>1.7417</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7219</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L25" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9664</v>
+        <v>1.7417</v>
       </c>
       <c r="N25" t="n">
-        <v>229</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>v1c7oR</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0306</v>
+        <v>1.074</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1364</v>
+        <v>0.1875</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6708</v>
+        <v>1.7413</v>
       </c>
       <c r="N26" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>v1c7oR</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="C27" t="n">
-        <v>1.026</v>
+        <v>0.9759</v>
       </c>
       <c r="D27" t="n">
-        <v>0.133</v>
+        <v>0.115</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6634</v>
+        <v>1.5822</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5097</v>
+        <v>1.5543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9312</v>
+        <v>0.9587</v>
       </c>
       <c r="D28" t="n">
-        <v>0.063</v>
+        <v>0.1023</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5097</v>
+        <v>1.5543</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0299</v>
+        <v>2.0387</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5202</v>
+        <v>-0.4844</v>
       </c>
       <c r="H28" t="n">
-        <v>2.0299</v>
+        <v>2.0387</v>
       </c>
       <c r="I28" t="n">
-        <v>2.0299</v>
+        <v>2.0387</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5202</v>
+        <v>-0.4844</v>
       </c>
       <c r="K28" t="n">
         <v>126</v>
@@ -1725,7 +1725,7 @@
         <v>158</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5097</v>
+        <v>1.5543</v>
       </c>
       <c r="N28" t="n">
         <v>284</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3864</v>
+        <v>1.434</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8551</v>
+        <v>0.8845</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0069</v>
+        <v>0.0475</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3864</v>
+        <v>1.434</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0703</v>
+        <v>-0.0198</v>
       </c>
       <c r="G29" t="n">
-        <v>1.3161</v>
+        <v>1.4538</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0703</v>
+        <v>-0.0198</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0721</v>
+        <v>-0.0204</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3161</v>
+        <v>1.4538</v>
       </c>
       <c r="K29" t="n">
         <v>140</v>
@@ -1771,7 +1771,7 @@
         <v>207</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3882</v>
+        <v>1.4334</v>
       </c>
       <c r="N29" t="n">
         <v>347</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3704</v>
+        <v>1.187</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.7321</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0004</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3704</v>
+        <v>1.187</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3704</v>
+        <v>0.0612</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.1258</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3704</v>
+        <v>0.0612</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3704</v>
+        <v>0.0612</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.1258</v>
       </c>
       <c r="K30" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3704</v>
+        <v>1.187</v>
       </c>
       <c r="N30" t="n">
-        <v>133</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1971</v>
+        <v>1.1803</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.728</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0793</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1971</v>
+        <v>1.1803</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0896</v>
+        <v>1.1803</v>
       </c>
       <c r="G31" t="n">
-        <v>1.1075</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0896</v>
+        <v>1.1803</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0896</v>
+        <v>1.1803</v>
       </c>
       <c r="J31" t="n">
-        <v>1.1075</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L31" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1971</v>
+        <v>1.1803</v>
       </c>
       <c r="N31" t="n">
-        <v>284</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.103</v>
+        <v>1.1632</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6803</v>
+        <v>0.7175</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1221</v>
+        <v>-0.0759</v>
       </c>
       <c r="E32" t="n">
-        <v>1.103</v>
+        <v>1.1632</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9432</v>
+        <v>1.9166</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.7534</v>
       </c>
       <c r="H32" t="n">
-        <v>1.9432</v>
+        <v>1.9166</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9432</v>
+        <v>1.9166</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.7534</v>
       </c>
       <c r="K32" t="n">
         <v>126</v>
@@ -1909,7 +1909,7 @@
         <v>158</v>
       </c>
       <c r="M32" t="n">
-        <v>1.103</v>
+        <v>1.1632</v>
       </c>
       <c r="N32" t="n">
         <v>284</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6795</v>
+        <v>0.6056</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1227</v>
+        <v>-0.1585</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1016</v>
+        <v>0.9819</v>
       </c>
       <c r="N33" t="n">
         <v>149</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5794</v>
+        <v>0.5945</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1966</v>
+        <v>-0.1667</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9393</v>
+        <v>0.9638</v>
       </c>
       <c r="N34" t="n">
         <v>108</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4453</v>
+        <v>0.4812</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2956</v>
+        <v>-0.2504</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7219</v>
+        <v>0.7801</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6542</v>
+        <v>0.6325</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4035</v>
+        <v>0.3901</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3264</v>
+        <v>-0.3177</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6542</v>
+        <v>0.6325</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4211</v>
+        <v>1.388</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7669</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4211</v>
+        <v>1.388</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4211</v>
+        <v>1.388</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7669</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>131</v>
@@ -2093,7 +2093,7 @@
         <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6542</v>
+        <v>0.6325</v>
       </c>
       <c r="N36" t="n">
         <v>176</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5566</v>
+        <v>0.5506</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3433</v>
+        <v>0.3396</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3708</v>
+        <v>-0.355</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5566</v>
+        <v>0.5506</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1043</v>
+        <v>0.5506</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5477</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1043</v>
+        <v>0.5506</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1043</v>
+        <v>0.5506</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5477</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5566000000000001</v>
+        <v>0.5506</v>
       </c>
       <c r="N37" t="n">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5546</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3421</v>
+        <v>0.3137</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3717</v>
+        <v>-0.3741</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5546</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5546</v>
+        <v>1.0292</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5206</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5546</v>
+        <v>1.0292</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5546</v>
+        <v>1.0292</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5206</v>
       </c>
       <c r="K38" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5546</v>
+        <v>0.5085999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3239</v>
+        <v>0.3064</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3852</v>
+        <v>-0.3795</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5251</v>
+        <v>0.4967</v>
       </c>
       <c r="N39" t="n">
         <v>149</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4591</v>
+        <v>0.4397</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2832</v>
+        <v>0.2712</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4152</v>
+        <v>-0.4055</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4591</v>
+        <v>0.4397</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5274</v>
+        <v>0.5584</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0683</v>
+        <v>-0.1187</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5274</v>
+        <v>0.5584</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5274</v>
+        <v>0.5584</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0683</v>
+        <v>-0.1187</v>
       </c>
       <c r="K40" t="n">
         <v>131</v>
@@ -2277,7 +2277,7 @@
         <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4591</v>
+        <v>0.4397</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2286,231 +2286,231 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2272</v>
+        <v>0.2027</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4565</v>
+        <v>-0.456</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3683</v>
+        <v>0.3287</v>
       </c>
       <c r="N41" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2162</v>
+        <v>0.1897</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4646</v>
+        <v>-0.4657</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3505</v>
+        <v>0.3076</v>
       </c>
       <c r="N42" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2095</v>
+        <v>0.1678</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4696</v>
+        <v>-0.4818</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3396</v>
+        <v>0.2721</v>
       </c>
       <c r="N43" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2025</v>
+        <v>0.1632</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4748</v>
+        <v>-0.4853</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3283</v>
+        <v>0.2646</v>
       </c>
       <c r="N44" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="C45" t="n">
-        <v>0.159</v>
+        <v>0.1533</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5068</v>
+        <v>-0.4925</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2578</v>
+        <v>0.2486</v>
       </c>
       <c r="N45" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="C46" t="n">
-        <v>0.123</v>
+        <v>0.1422</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5334</v>
+        <v>-0.5008</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1994</v>
+        <v>0.2305</v>
       </c>
       <c r="N46" t="n">
         <v>135</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0291</v>
+        <v>0.0372</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.5783</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0472</v>
+        <v>0.0603</v>
       </c>
       <c r="N47" t="n">
         <v>134</v>
@@ -2608,139 +2608,139 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.09</v>
+        <v>-0.0827</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0555</v>
+        <v>-0.051</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6652</v>
+        <v>-0.6435</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.09</v>
+        <v>-0.0827</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.09</v>
+        <v>0.2598</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.3425</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.09</v>
+        <v>0.2598</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.09</v>
+        <v>0.2598</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.3425</v>
       </c>
       <c r="K48" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.09</v>
+        <v>-0.08270000000000005</v>
       </c>
       <c r="N48" t="n">
-        <v>149</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0998</v>
+        <v>-0.1151</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0616</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6696</v>
+        <v>-0.6582</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0998</v>
+        <v>-0.1151</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2531</v>
+        <v>0.189</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3529</v>
+        <v>-0.3041</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2531</v>
+        <v>0.189</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2531</v>
+        <v>0.189</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3529</v>
+        <v>-0.3041</v>
       </c>
       <c r="K49" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="L49" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0998</v>
+        <v>-0.1151</v>
       </c>
       <c r="N49" t="n">
-        <v>229</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1338</v>
+        <v>-0.1392</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0825</v>
+        <v>-0.0859</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6851</v>
+        <v>-0.6692</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1338</v>
+        <v>-0.1392</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1517</v>
+        <v>-0.1392</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.2855</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1517</v>
+        <v>-0.1392</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1517</v>
+        <v>-0.1392</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.2855</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1338</v>
+        <v>-0.1392</v>
       </c>
       <c r="N50" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1874</v>
+        <v>-0.2437</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7625</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3039</v>
+        <v>-0.3951</v>
       </c>
       <c r="N51" t="n">
         <v>134</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5944</v>
+        <v>-0.5496</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3666</v>
+        <v>-0.339</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8948</v>
+        <v>-0.8562</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5944</v>
+        <v>-0.5496</v>
       </c>
       <c r="F52" t="n">
-        <v>0.241</v>
+        <v>0.2692</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.8354</v>
+        <v>-0.8188</v>
       </c>
       <c r="H52" t="n">
-        <v>0.241</v>
+        <v>0.2692</v>
       </c>
       <c r="I52" t="n">
-        <v>0.241</v>
+        <v>0.2692</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8354</v>
+        <v>-0.8188</v>
       </c>
       <c r="K52" t="n">
         <v>131</v>
@@ -2829,7 +2829,7 @@
         <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5944</v>
+        <v>-0.5496</v>
       </c>
       <c r="N52" t="n">
         <v>176</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4949</v>
+        <v>-0.4921</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.8023</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="N53" t="n">
         <v>137</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.5934</v>
+        <v>-0.5581</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0621</v>
+        <v>-1.018</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.962</v>
+        <v>-0.9048</v>
       </c>
       <c r="N54" t="n">
         <v>137</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.7029</v>
+        <v>-0.7036</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.143</v>
+        <v>-1.1254</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.1396</v>
+        <v>-1.1407</v>
       </c>
       <c r="N55" t="n">
         <v>108</v>
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.1678</v>
+        <v>-1.1463</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.707</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1558</v>
+        <v>-1.128</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.1678</v>
+        <v>-1.1463</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.4037</v>
+        <v>-1.2936</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2359</v>
+        <v>0.1473</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.4037</v>
+        <v>-1.2936</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.758</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2359</v>
+        <v>0.1473</v>
       </c>
       <c r="K56" t="n">
         <v>136</v>
@@ -3013,7 +3013,7 @@
         <v>158</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.5221</v>
+        <v>-0.579</v>
       </c>
       <c r="N56" t="n">
         <v>294</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.0064</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.367</v>
+        <v>-1.3053</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.6317</v>
+        <v>-1.5355</v>
       </c>
       <c r="N57" t="n">
         <v>137</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.2173</v>
+        <v>-1.1889</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.5226</v>
+        <v>-1.4839</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.9735</v>
+        <v>-1.9275</v>
       </c>
       <c r="N58" t="n">
         <v>108</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.2796</v>
+        <v>-1.2577</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.5686</v>
+        <v>-1.5346</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.0746</v>
+        <v>-2.039</v>
       </c>
       <c r="N59" t="n">
         <v>108</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.3438</v>
+        <v>-1.3005</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.616</v>
+        <v>-1.5663</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.1787</v>
+        <v>-2.1084</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.4073</v>
+        <v>-1.4046</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.6628</v>
+        <v>-1.6432</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.2816</v>
+        <v>-2.2772</v>
       </c>
       <c r="N61" t="n">
         <v>108</v>
@@ -3349,10 +3349,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5613</v>
+        <v>0.5018</v>
       </c>
       <c r="J2" t="n">
-        <v>20.2068</v>
+        <v>18.0648</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.21</v>
       </c>
       <c r="I3" t="n">
-        <v>0.447</v>
+        <v>0.389</v>
       </c>
       <c r="J3" t="n">
-        <v>16.092</v>
+        <v>14.004</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1678</v>
+        <v>0.1314</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0408</v>
+        <v>4.7304</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0593</v>
+        <v>-0.0464</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1348</v>
+        <v>-1.6704</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4731</v>
+        <v>-0.4714</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.0316</v>
+        <v>-16.9704</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9677</v>
+        <v>0.956</v>
       </c>
       <c r="J7" t="n">
-        <v>34.8372</v>
+        <v>34.416</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.26</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6835</v>
+        <v>0.6504</v>
       </c>
       <c r="J8" t="n">
-        <v>24.606</v>
+        <v>23.4144</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5538</v>
+        <v>0.5165</v>
       </c>
       <c r="J9" t="n">
-        <v>19.9368</v>
+        <v>18.594</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.16</v>
+        <v>-0.1284</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.76</v>
+        <v>-4.6224</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4958</v>
+        <v>-0.4548</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.8488</v>
+        <v>-16.3728</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1345</v>
+        <v>-0.1183</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5555</v>
+        <v>-2.2477</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>0.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1905</v>
+        <v>-0.1751</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6195</v>
+        <v>-3.3269</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>0.74</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2812</v>
+        <v>-0.2672</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.3428</v>
+        <v>-5.0768</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3878</v>
+        <v>-0.3763</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.3682</v>
+        <v>-7.1497</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.42</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5635</v>
+        <v>-0.5704</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.7065</v>
+        <v>-10.8376</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3887</v>
+        <v>1.4246</v>
       </c>
       <c r="J17" t="n">
-        <v>26.3853</v>
+        <v>27.0674</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.57</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2173</v>
+        <v>1.2377</v>
       </c>
       <c r="J18" t="n">
-        <v>23.1287</v>
+        <v>23.5163</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.47</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0414</v>
+        <v>1.0442</v>
       </c>
       <c r="J19" t="n">
-        <v>19.7866</v>
+        <v>19.8398</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.19</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4947</v>
+        <v>0.4653</v>
       </c>
       <c r="J20" t="n">
-        <v>9.3993</v>
+        <v>8.8407</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.329</v>
+        <v>0.2966</v>
       </c>
       <c r="J21" t="n">
-        <v>6.251</v>
+        <v>5.6354</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3809</v>
+        <v>0.3254</v>
       </c>
       <c r="J22" t="n">
-        <v>12.9506</v>
+        <v>11.0636</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3633</v>
+        <v>0.3087</v>
       </c>
       <c r="J23" t="n">
-        <v>12.3522</v>
+        <v>10.4958</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1241</v>
+        <v>0.0939</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2194</v>
+        <v>3.1926</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2018</v>
+        <v>-0.1812</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.8612</v>
+        <v>-6.1608</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2528</v>
+        <v>-0.2329</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.5952</v>
+        <v>-7.9186</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8365</v>
+        <v>0.8128</v>
       </c>
       <c r="J27" t="n">
-        <v>28.441</v>
+        <v>27.6352</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.19</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5372</v>
+        <v>0.4982</v>
       </c>
       <c r="J28" t="n">
-        <v>18.2648</v>
+        <v>16.9388</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.445</v>
+        <v>0.4055</v>
       </c>
       <c r="J29" t="n">
-        <v>15.13</v>
+        <v>13.787</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2439</v>
+        <v>0.2112</v>
       </c>
       <c r="J30" t="n">
-        <v>8.2926</v>
+        <v>7.1808</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.5959</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.4744</v>
+        <v>-20.2606</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4457</v>
+        <v>0.3922</v>
       </c>
       <c r="J32" t="n">
-        <v>9.805400000000001</v>
+        <v>8.628399999999999</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2121</v>
+        <v>0.1698</v>
       </c>
       <c r="J33" t="n">
-        <v>4.6662</v>
+        <v>3.7356</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1698</v>
+        <v>0.1327</v>
       </c>
       <c r="J34" t="n">
-        <v>3.7356</v>
+        <v>2.9194</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1117</v>
+        <v>-0.0939</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.4574</v>
+        <v>-2.0658</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.32</v>
+        <v>-0.3033</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.04</v>
+        <v>-6.6726</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.95</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5509</v>
+        <v>1.585</v>
       </c>
       <c r="J37" t="n">
-        <v>34.1198</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3651</v>
+        <v>0.3303</v>
       </c>
       <c r="J38" t="n">
-        <v>8.0322</v>
+        <v>7.2666</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1739</v>
+        <v>0.1474</v>
       </c>
       <c r="J39" t="n">
-        <v>3.8258</v>
+        <v>3.2428</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>0.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4019</v>
+        <v>-0.3603</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.841799999999999</v>
+        <v>-7.9266</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4781</v>
+        <v>-0.4374</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.5182</v>
+        <v>-9.6228</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5047</v>
+        <v>0.4588</v>
       </c>
       <c r="J42" t="n">
-        <v>14.1316</v>
+        <v>12.8464</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2714</v>
+        <v>0.2194</v>
       </c>
       <c r="J43" t="n">
-        <v>7.5992</v>
+        <v>6.1432</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0477</v>
+        <v>0.0332</v>
       </c>
       <c r="J44" t="n">
-        <v>1.3356</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0511</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.8228</v>
+        <v>-1.4308</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1546</v>
+        <v>-0.1346</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.3288</v>
+        <v>-3.7688</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4509</v>
+        <v>0.4598</v>
       </c>
       <c r="J47" t="n">
-        <v>12.6252</v>
+        <v>12.8744</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I48" t="n">
-        <v>0.128</v>
+        <v>0.1134</v>
       </c>
       <c r="J48" t="n">
-        <v>3.584</v>
+        <v>3.1752</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0934</v>
+        <v>0.0805</v>
       </c>
       <c r="J49" t="n">
-        <v>2.6152</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0905</v>
+        <v>-0.074</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.534</v>
+        <v>-2.072</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.93</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1161</v>
+        <v>-0.0977</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.2508</v>
+        <v>-2.7356</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.09</v>
       </c>
       <c r="I52" t="n">
-        <v>0.314</v>
+        <v>0.2758</v>
       </c>
       <c r="J52" t="n">
-        <v>7.222</v>
+        <v>6.3434</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0544</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.5663</v>
+        <v>-1.2512</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2181</v>
+        <v>-0.2025</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.0163</v>
+        <v>-4.6575</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.49</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5074</v>
+        <v>-0.5069</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.6702</v>
+        <v>-11.6587</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6193</v>
+        <v>-0.6361</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.2439</v>
+        <v>-14.6303</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.98</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5378</v>
+        <v>1.5619</v>
       </c>
       <c r="J57" t="n">
-        <v>35.3694</v>
+        <v>35.9237</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.49</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9204</v>
+        <v>0.9074</v>
       </c>
       <c r="J58" t="n">
-        <v>21.1692</v>
+        <v>20.8702</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4349</v>
+        <v>0.4062</v>
       </c>
       <c r="J59" t="n">
-        <v>10.0027</v>
+        <v>9.342599999999999</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1482</v>
+        <v>0.1218</v>
       </c>
       <c r="J60" t="n">
-        <v>3.4086</v>
+        <v>2.8014</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2267</v>
+        <v>-0.1948</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.2141</v>
+        <v>-4.4804</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6019</v>
+        <v>0.5889</v>
       </c>
       <c r="J62" t="n">
-        <v>24.6779</v>
+        <v>24.1449</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.21</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5527</v>
+        <v>0.5414</v>
       </c>
       <c r="J63" t="n">
-        <v>22.6607</v>
+        <v>22.1974</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4849</v>
+        <v>0.4601</v>
       </c>
       <c r="J64" t="n">
-        <v>19.8809</v>
+        <v>18.8641</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4812</v>
+        <v>-0.4388</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.7292</v>
+        <v>-17.9908</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5294</v>
+        <v>-0.4883</v>
       </c>
       <c r="J66" t="n">
-        <v>-21.7054</v>
+        <v>-20.0203</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.5735</v>
       </c>
       <c r="J67" t="n">
-        <v>24.6533</v>
+        <v>23.5135</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0254</v>
+        <v>-0.0182</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.0414</v>
+        <v>-0.7462</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>0.97</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0585</v>
+        <v>-0.0458</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.3985</v>
+        <v>-1.8778</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0728</v>
+        <v>-0.0584</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.9848</v>
+        <v>-2.3944</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.9638</v>
+        <v>-11.2135</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3193</v>
+        <v>1.3275</v>
       </c>
       <c r="J72" t="n">
-        <v>36.9404</v>
+        <v>37.17</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5185</v>
+        <v>0.5083</v>
       </c>
       <c r="J73" t="n">
-        <v>14.518</v>
+        <v>14.2324</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4117</v>
+        <v>0.3771</v>
       </c>
       <c r="J74" t="n">
-        <v>11.5276</v>
+        <v>10.5588</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1687</v>
+        <v>-0.1372</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.7236</v>
+        <v>-3.8416</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.4898</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.8036</v>
+        <v>-13.7144</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.38</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6681</v>
+        <v>0.6403</v>
       </c>
       <c r="J77" t="n">
-        <v>18.7068</v>
+        <v>17.9284</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1294</v>
+        <v>-0.1119</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.6232</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2351</v>
+        <v>-0.2151</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.5828</v>
+        <v>-6.0228</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.77</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.6832</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.484</v>
+        <v>-7.9828</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.83</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3219</v>
+        <v>1.326</v>
       </c>
       <c r="J82" t="n">
-        <v>27.7599</v>
+        <v>27.846</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.58</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0163</v>
+        <v>1.0089</v>
       </c>
       <c r="J83" t="n">
-        <v>21.3423</v>
+        <v>21.1869</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.58</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0163</v>
+        <v>1.0089</v>
       </c>
       <c r="J84" t="n">
-        <v>21.3423</v>
+        <v>21.1869</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5972</v>
+        <v>0.5945</v>
       </c>
       <c r="J85" t="n">
-        <v>12.5412</v>
+        <v>12.4845</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>1.22</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5191</v>
+        <v>0.5157</v>
       </c>
       <c r="J86" t="n">
-        <v>10.9011</v>
+        <v>10.8297</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.63</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.3542</v>
+        <v>-0.3468</v>
       </c>
       <c r="J87" t="n">
-        <v>-7.4382</v>
+        <v>-7.2828</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.61</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3733</v>
+        <v>-0.3672</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.8393</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.1623</v>
+        <v>-9.0909</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.49</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4776</v>
+        <v>-0.4756</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.0296</v>
+        <v>-9.9876</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5838</v>
+        <v>-0.592</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.2598</v>
+        <v>-12.432</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>2.01</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5832</v>
+        <v>1.6137</v>
       </c>
       <c r="J92" t="n">
-        <v>37.9968</v>
+        <v>38.7288</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5085</v>
+        <v>0.5007</v>
       </c>
       <c r="J93" t="n">
-        <v>12.204</v>
+        <v>12.0168</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5085</v>
+        <v>0.5007</v>
       </c>
       <c r="J94" t="n">
-        <v>12.204</v>
+        <v>12.0168</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1.13</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3707</v>
+        <v>0.3385</v>
       </c>
       <c r="J95" t="n">
-        <v>8.896800000000001</v>
+        <v>8.124000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.284</v>
+        <v>-0.2477</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.816</v>
+        <v>-5.9448</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.368</v>
+        <v>0.3142</v>
       </c>
       <c r="J97" t="n">
-        <v>8.832000000000001</v>
+        <v>7.5408</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0878</v>
+        <v>0.0631</v>
       </c>
       <c r="J98" t="n">
-        <v>2.1072</v>
+        <v>1.5144</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1831</v>
+        <v>-0.1635</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.3944</v>
+        <v>-3.924</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1935</v>
+        <v>-0.1738</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.644</v>
+        <v>-4.1712</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.68</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3578</v>
+        <v>-0.3432</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.587199999999999</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.85</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4168</v>
+        <v>1.4339</v>
       </c>
       <c r="J102" t="n">
-        <v>36.8368</v>
+        <v>37.2814</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6412</v>
+        <v>0.6293</v>
       </c>
       <c r="J103" t="n">
-        <v>16.6712</v>
+        <v>16.3618</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.18</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4856</v>
+        <v>0.4674</v>
       </c>
       <c r="J104" t="n">
-        <v>12.6256</v>
+        <v>12.1524</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2369</v>
+        <v>-0.2003</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.1594</v>
+        <v>-5.2078</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.73</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7806</v>
+        <v>-0.7584</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.2956</v>
+        <v>-19.7184</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5929</v>
+        <v>0.5674</v>
       </c>
       <c r="J107" t="n">
-        <v>15.4154</v>
+        <v>14.7524</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0215</v>
+        <v>-0.016</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.416</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.0966</v>
+        <v>-2.6468</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1857</v>
+        <v>-0.1656</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.8282</v>
+        <v>-4.3056</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.62</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4146</v>
+        <v>-0.4053</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.7796</v>
+        <v>-10.5378</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5887</v>
       </c>
       <c r="J112" t="n">
-        <v>18.938</v>
+        <v>20.0158</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.277</v>
+        <v>0.264</v>
       </c>
       <c r="J113" t="n">
-        <v>9.417999999999999</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0537</v>
+        <v>0.0441</v>
       </c>
       <c r="J114" t="n">
-        <v>1.8258</v>
+        <v>1.4994</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1516</v>
+        <v>-0.1316</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.1544</v>
+        <v>-4.4744</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2865</v>
+        <v>-0.2683</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.741</v>
+        <v>-9.122199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.29</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4255</v>
+        <v>0.3621</v>
       </c>
       <c r="J117" t="n">
-        <v>14.467</v>
+        <v>12.3114</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.24</v>
+        <v>0.1906</v>
       </c>
       <c r="J118" t="n">
-        <v>8.16</v>
+        <v>6.4804</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1074</v>
+        <v>0.0786</v>
       </c>
       <c r="J119" t="n">
-        <v>3.6516</v>
+        <v>2.6724</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2245</v>
+        <v>-0.2041</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.633</v>
+        <v>-6.9394</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2347</v>
+        <v>-0.2144</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.9798</v>
+        <v>-7.2896</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9614</v>
+        <v>0.9477</v>
       </c>
       <c r="J122" t="n">
-        <v>27.8806</v>
+        <v>27.4833</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.34</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7336</v>
+        <v>0.7185</v>
       </c>
       <c r="J123" t="n">
-        <v>21.2744</v>
+        <v>20.8365</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.32</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7039</v>
+        <v>0.6895</v>
       </c>
       <c r="J124" t="n">
-        <v>20.4131</v>
+        <v>19.9955</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3496</v>
+        <v>-0.3085</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.1384</v>
+        <v>-8.9465</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5138</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.0051</v>
+        <v>-14.9002</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5498</v>
+        <v>0.5256</v>
       </c>
       <c r="J127" t="n">
-        <v>15.9442</v>
+        <v>15.2424</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.22</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4756</v>
+        <v>0.4317</v>
       </c>
       <c r="J128" t="n">
-        <v>13.7924</v>
+        <v>12.5193</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>0.77</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2746</v>
+        <v>-0.2555</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.9634</v>
+        <v>-7.4095</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3589</v>
+        <v>-0.3445</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.4081</v>
+        <v>-9.990500000000001</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3681</v>
+        <v>-0.3543</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.6749</v>
+        <v>-10.2747</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.27</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5345</v>
+        <v>0.4748</v>
       </c>
       <c r="J132" t="n">
-        <v>21.9145</v>
+        <v>19.4668</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2806</v>
+        <v>0.2329</v>
       </c>
       <c r="J133" t="n">
-        <v>11.5046</v>
+        <v>9.5489</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1838</v>
+        <v>0.1467</v>
       </c>
       <c r="J134" t="n">
-        <v>7.5358</v>
+        <v>6.0147</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="J135" t="n">
-        <v>2.7716</v>
+        <v>2.0336</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2277</v>
+        <v>-0.2074</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.335699999999999</v>
+        <v>-8.503399999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9997</v>
+        <v>0.9992</v>
       </c>
       <c r="J137" t="n">
-        <v>40.9877</v>
+        <v>40.9672</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2543</v>
+        <v>0.217</v>
       </c>
       <c r="J138" t="n">
-        <v>10.4263</v>
+        <v>8.897</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.205</v>
+        <v>-0.1695</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.404999999999999</v>
+        <v>-6.9495</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4247</v>
+        <v>-0.3816</v>
       </c>
       <c r="J140" t="n">
-        <v>-17.4127</v>
+        <v>-15.6456</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4986</v>
+        <v>-0.4564</v>
       </c>
       <c r="J141" t="n">
-        <v>-20.4426</v>
+        <v>-18.7124</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7215</v>
+        <v>0.6893</v>
       </c>
       <c r="J142" t="n">
-        <v>20.202</v>
+        <v>19.3004</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4517</v>
+        <v>0.4106</v>
       </c>
       <c r="J143" t="n">
-        <v>12.6476</v>
+        <v>11.4968</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3534</v>
+        <v>0.3138</v>
       </c>
       <c r="J144" t="n">
-        <v>9.895200000000001</v>
+        <v>8.7864</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1907</v>
+        <v>0.1604</v>
       </c>
       <c r="J145" t="n">
-        <v>5.3396</v>
+        <v>4.4912</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>0.77</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6359</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.7572</v>
+        <v>-17.8052</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.34</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6569</v>
+        <v>0.5989</v>
       </c>
       <c r="J147" t="n">
-        <v>18.3932</v>
+        <v>16.7692</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2108</v>
+        <v>0.1688</v>
       </c>
       <c r="J148" t="n">
-        <v>5.9024</v>
+        <v>4.7264</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0589</v>
+        <v>-0.0461</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.6492</v>
+        <v>-1.2908</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1245</v>
+        <v>-0.1058</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.486</v>
+        <v>-2.9624</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3113</v>
+        <v>-0.2941</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.7164</v>
+        <v>-8.2348</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5687</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>16.4923</v>
+        <v>15.3323</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1379</v>
+        <v>0.1093</v>
       </c>
       <c r="J153" t="n">
-        <v>3.9991</v>
+        <v>3.1697</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1379</v>
+        <v>0.1093</v>
       </c>
       <c r="J154" t="n">
-        <v>3.9991</v>
+        <v>3.1697</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0574</v>
+        <v>-0.0422</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.6646</v>
+        <v>-1.2238</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8275</v>
+        <v>-0.8044</v>
       </c>
       <c r="J156" t="n">
-        <v>-23.9975</v>
+        <v>-23.3276</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4621</v>
+        <v>0.4046</v>
       </c>
       <c r="J157" t="n">
-        <v>13.4009</v>
+        <v>11.7334</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.363</v>
+        <v>0.3103</v>
       </c>
       <c r="J158" t="n">
-        <v>10.527</v>
+        <v>8.998699999999999</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2755</v>
+        <v>0.2298</v>
       </c>
       <c r="J159" t="n">
-        <v>7.9895</v>
+        <v>6.6642</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2201</v>
+        <v>0.1801</v>
       </c>
       <c r="J160" t="n">
-        <v>6.3829</v>
+        <v>5.2229</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1325</v>
+        <v>-0.1133</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.8425</v>
+        <v>-3.2857</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0159</v>
+        <v>0.0255</v>
       </c>
       <c r="J162" t="n">
-        <v>0.3975</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1549</v>
+        <v>-0.1394</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.8725</v>
+        <v>-3.485</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2389</v>
+        <v>-0.2232</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.9725</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.64</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3756</v>
+        <v>-0.3626</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.065</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>-14</v>
+        <v>-14.175</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0668</v>
+        <v>1.0766</v>
       </c>
       <c r="J167" t="n">
-        <v>26.67</v>
+        <v>26.915</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9593</v>
+        <v>0.9538</v>
       </c>
       <c r="J168" t="n">
-        <v>23.9825</v>
+        <v>23.845</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9418</v>
+        <v>0.9341</v>
       </c>
       <c r="J169" t="n">
-        <v>23.545</v>
+        <v>23.3525</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>1.29</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6939</v>
       </c>
       <c r="J170" t="n">
-        <v>17.905</v>
+        <v>17.3475</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1476</v>
+        <v>0.1211</v>
       </c>
       <c r="J171" t="n">
-        <v>3.69</v>
+        <v>3.0275</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0641</v>
+        <v>-0.0521</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.4743</v>
+        <v>-1.1983</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0907</v>
+        <v>-0.0772</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.0861</v>
+        <v>-1.7756</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3354</v>
+        <v>-0.3198</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.7142</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3354</v>
+        <v>-0.3198</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.7142</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3445</v>
+        <v>-0.3294</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.9235</v>
+        <v>-7.5762</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.84</v>
       </c>
       <c r="I177" t="n">
-        <v>1.517</v>
+        <v>1.5508</v>
       </c>
       <c r="J177" t="n">
-        <v>34.891</v>
+        <v>35.6684</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.5</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0822</v>
+        <v>1.0933</v>
       </c>
       <c r="J178" t="n">
-        <v>24.8906</v>
+        <v>25.1459</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6776</v>
+        <v>0.6531</v>
       </c>
       <c r="J179" t="n">
-        <v>15.5848</v>
+        <v>15.0213</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1797</v>
+        <v>0.1517</v>
       </c>
       <c r="J180" t="n">
-        <v>4.1331</v>
+        <v>3.4891</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3171</v>
+        <v>-0.2804</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.2933</v>
+        <v>-6.4492</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5605</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>14.0125</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0756</v>
+        <v>-0.0633</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.89</v>
+        <v>-1.5825</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1898</v>
+        <v>-0.1711</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.745</v>
+        <v>-4.2775</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3439</v>
+        <v>-0.3283</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.5975</v>
+        <v>-8.2075</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.59</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4338</v>
+        <v>-0.4258</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.845</v>
+        <v>-10.645</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2641</v>
+        <v>1.2817</v>
       </c>
       <c r="J187" t="n">
-        <v>31.6025</v>
+        <v>32.0425</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9424</v>
+        <v>0.9346</v>
       </c>
       <c r="J188" t="n">
-        <v>23.56</v>
+        <v>23.365</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9424</v>
+        <v>0.9346</v>
       </c>
       <c r="J189" t="n">
-        <v>23.56</v>
+        <v>23.365</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.21</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5503</v>
+        <v>0.5215</v>
       </c>
       <c r="J190" t="n">
-        <v>13.7575</v>
+        <v>13.0375</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1929</v>
+        <v>-0.1637</v>
       </c>
       <c r="J191" t="n">
-        <v>-4.8225</v>
+        <v>-4.0925</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.31</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7207</v>
+        <v>0.6917</v>
       </c>
       <c r="J192" t="n">
-        <v>15.1347</v>
+        <v>14.5257</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1674</v>
+        <v>-0.1517</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.5154</v>
+        <v>-3.1857</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.79</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2398</v>
+        <v>-0.2239</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.0358</v>
+        <v>-4.7019</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.41</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.578</v>
+        <v>-0.5879</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.138</v>
+        <v>-12.3459</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.39</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5951</v>
+        <v>-0.6079</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.4971</v>
+        <v>-12.7659</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3535</v>
+        <v>1.3765</v>
       </c>
       <c r="J197" t="n">
-        <v>28.4235</v>
+        <v>28.9065</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.45</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.0002</v>
       </c>
       <c r="J198" t="n">
-        <v>20.8845</v>
+        <v>21.0042</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.43</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9626</v>
+        <v>0.964</v>
       </c>
       <c r="J199" t="n">
-        <v>20.2146</v>
+        <v>20.244</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.9282</v>
+        <v>0.9256</v>
       </c>
       <c r="J200" t="n">
-        <v>19.4922</v>
+        <v>19.4376</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>1.3</v>
       </c>
       <c r="I201" t="n">
-        <v>0.7185</v>
+        <v>0.7008</v>
       </c>
       <c r="J201" t="n">
-        <v>15.0885</v>
+        <v>14.7168</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.26</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6742</v>
+        <v>0.6425</v>
       </c>
       <c r="J202" t="n">
-        <v>18.8776</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6742</v>
+        <v>0.6425</v>
       </c>
       <c r="J203" t="n">
-        <v>18.8776</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5899</v>
+        <v>0.5556</v>
       </c>
       <c r="J204" t="n">
-        <v>16.5172</v>
+        <v>15.5568</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>1.13</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3885</v>
+        <v>0.3535</v>
       </c>
       <c r="J205" t="n">
-        <v>10.878</v>
+        <v>9.898</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>1.04</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1409</v>
+        <v>0.1171</v>
       </c>
       <c r="J206" t="n">
-        <v>3.9452</v>
+        <v>3.2788</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.42</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8047</v>
+        <v>0.7579</v>
       </c>
       <c r="J207" t="n">
-        <v>22.5316</v>
+        <v>21.2212</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.89</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.2784</v>
+        <v>-3.7464</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.2784</v>
+        <v>-3.7464</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2365</v>
+        <v>-0.2164</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.622</v>
+        <v>-6.0592</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.67</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3692</v>
+        <v>-0.3556</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.3376</v>
+        <v>-9.956799999999999</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5219</v>
+        <v>0.4752</v>
       </c>
       <c r="J212" t="n">
-        <v>10.9599</v>
+        <v>9.979200000000001</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0359</v>
+        <v>-0.0264</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.7539</v>
+        <v>-0.5544</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.66</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3634</v>
+        <v>-0.3492</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.6314</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.65</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3724</v>
+        <v>-0.3589</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.8204</v>
+        <v>-7.5369</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.48</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5222</v>
+        <v>-0.5243</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.9662</v>
+        <v>-11.0103</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.98</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6715</v>
+        <v>1.7182</v>
       </c>
       <c r="J217" t="n">
-        <v>35.1015</v>
+        <v>36.0822</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9001</v>
+        <v>0.8909</v>
       </c>
       <c r="J218" t="n">
-        <v>18.9021</v>
+        <v>18.7089</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.26</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6489</v>
+        <v>0.6253</v>
       </c>
       <c r="J219" t="n">
-        <v>13.6269</v>
+        <v>13.1313</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>1.24</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6071</v>
+        <v>0.5816</v>
       </c>
       <c r="J220" t="n">
-        <v>12.7491</v>
+        <v>12.2136</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0747</v>
+        <v>0.0525</v>
       </c>
       <c r="J221" t="n">
-        <v>1.5687</v>
+        <v>1.1025</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7144</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>25.004</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.65</v>
+        <v>0.6143</v>
       </c>
       <c r="J223" t="n">
-        <v>22.75</v>
+        <v>21.5005</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.1</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3246</v>
+        <v>0.2873</v>
       </c>
       <c r="J224" t="n">
-        <v>11.361</v>
+        <v>10.0555</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1222</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>4.277</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5125</v>
+        <v>-0.4713</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.9375</v>
+        <v>-16.4955</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3479</v>
+        <v>0.2941</v>
       </c>
       <c r="J227" t="n">
-        <v>12.1765</v>
+        <v>10.2935</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.254</v>
+        <v>0.2072</v>
       </c>
       <c r="J228" t="n">
-        <v>8.890000000000001</v>
+        <v>7.252</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1714</v>
+        <v>0.1339</v>
       </c>
       <c r="J229" t="n">
-        <v>5.999</v>
+        <v>4.6865</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1463</v>
+        <v>-0.1267</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.1205</v>
+        <v>-4.4345</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3002</v>
+        <v>-0.2823</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.507</v>
+        <v>-9.8805</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4572</v>
+        <v>0.3993</v>
       </c>
       <c r="J232" t="n">
-        <v>13.716</v>
+        <v>11.979</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.04</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1285</v>
+        <v>0.0969</v>
       </c>
       <c r="J233" t="n">
-        <v>3.855</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.96</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0708</v>
+        <v>-0.0572</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.124</v>
+        <v>-1.716</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.156</v>
+        <v>-0.1363</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.68</v>
+        <v>-4.089</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.77</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2794</v>
+        <v>-0.2604</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.382</v>
+        <v>-7.812</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0155</v>
+        <v>1.0151</v>
       </c>
       <c r="J237" t="n">
-        <v>30.465</v>
+        <v>30.453</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9266</v>
+        <v>0.9115</v>
       </c>
       <c r="J238" t="n">
-        <v>27.798</v>
+        <v>27.345</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1797</v>
+        <v>0.1524</v>
       </c>
       <c r="J239" t="n">
-        <v>5.391</v>
+        <v>4.572</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2264</v>
+        <v>-0.1894</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.792</v>
+        <v>-5.682</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.89</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3957</v>
+        <v>-0.3534</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.871</v>
+        <v>-10.602</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.24</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5373</v>
+        <v>0.4827</v>
       </c>
       <c r="J242" t="n">
-        <v>15.5817</v>
+        <v>13.9983</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0188</v>
+        <v>0.0137</v>
       </c>
       <c r="J243" t="n">
-        <v>0.5452</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1031</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.9899</v>
+        <v>-2.5636</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.391</v>
+        <v>-0.3789</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.339</v>
+        <v>-10.9881</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4266</v>
+        <v>-0.4179</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.3714</v>
+        <v>-12.1191</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.64</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2832</v>
+        <v>1.302</v>
       </c>
       <c r="J247" t="n">
-        <v>37.2128</v>
+        <v>37.758</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.39</v>
       </c>
       <c r="I248" t="n">
-        <v>0.922</v>
+        <v>0.9082</v>
       </c>
       <c r="J248" t="n">
-        <v>26.738</v>
+        <v>26.3378</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.13</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3799</v>
+        <v>0.3468</v>
       </c>
       <c r="J249" t="n">
-        <v>11.0171</v>
+        <v>10.0572</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.03</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0772</v>
       </c>
       <c r="J250" t="n">
-        <v>2.8304</v>
+        <v>2.2388</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0402</v>
+        <v>-0.0348</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.1658</v>
+        <v>-1.0092</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>0.9</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.1209</v>
+        <v>-0.1058</v>
       </c>
       <c r="J252" t="n">
-        <v>-2.6598</v>
+        <v>-2.3276</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1884</v>
+        <v>-0.1727</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.1448</v>
+        <v>-3.7994</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.76</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2678</v>
+        <v>-0.252</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.8916</v>
+        <v>-5.544</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.73</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2947</v>
+        <v>-0.279</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.4834</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.51</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4911</v>
+        <v>-0.4887</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.8042</v>
+        <v>-10.7514</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.462</v>
+        <v>1.4912</v>
       </c>
       <c r="J257" t="n">
-        <v>32.164</v>
+        <v>32.8064</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9401</v>
+        <v>0.9328</v>
       </c>
       <c r="J258" t="n">
-        <v>20.6822</v>
+        <v>20.5216</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.38</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8855</v>
+        <v>0.8733</v>
       </c>
       <c r="J259" t="n">
-        <v>19.481</v>
+        <v>19.2126</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7541</v>
+        <v>0.7343</v>
       </c>
       <c r="J260" t="n">
-        <v>16.5902</v>
+        <v>16.1546</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6014</v>
+        <v>-0.5703</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.2308</v>
+        <v>-12.5466</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2962</v>
+        <v>0.2457</v>
       </c>
       <c r="J262" t="n">
-        <v>7.9974</v>
+        <v>6.6339</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0767</v>
+        <v>0.0545</v>
       </c>
       <c r="J263" t="n">
-        <v>2.0709</v>
+        <v>1.4715</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0025</v>
+        <v>0.0012</v>
       </c>
       <c r="J264" t="n">
-        <v>0.0675</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.9</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1447</v>
+        <v>-0.1254</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.9069</v>
+        <v>-3.3858</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.83</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.9346</v>
+        <v>-5.3811</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.6</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2468</v>
+        <v>1.2647</v>
       </c>
       <c r="J267" t="n">
-        <v>33.6636</v>
+        <v>34.1469</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6969</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J268" t="n">
-        <v>18.8163</v>
+        <v>17.9766</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I269" t="n">
-        <v>0.6761</v>
+        <v>0.644</v>
       </c>
       <c r="J269" t="n">
-        <v>18.2547</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0725</v>
+        <v>0.0562</v>
       </c>
       <c r="J270" t="n">
-        <v>1.9575</v>
+        <v>1.5174</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.71</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8193</v>
+        <v>-0.8</v>
       </c>
       <c r="J271" t="n">
-        <v>-22.1211</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0557</v>
+        <v>-0.0396</v>
       </c>
       <c r="J272" t="n">
-        <v>-1.1697</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1882</v>
+        <v>-0.1726</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.9522</v>
+        <v>-3.6246</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>0.6</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.404</v>
+        <v>-0.3936</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.484</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.57</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4306</v>
+        <v>-0.422</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.0426</v>
+        <v>-8.862</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.49</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.501</v>
+        <v>-0.4993</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.521</v>
+        <v>-10.4853</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.74</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3683</v>
+        <v>1.3918</v>
       </c>
       <c r="J277" t="n">
-        <v>28.7343</v>
+        <v>29.2278</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.62</v>
       </c>
       <c r="I278" t="n">
-        <v>1.2194</v>
+        <v>1.2373</v>
       </c>
       <c r="J278" t="n">
-        <v>25.6074</v>
+        <v>25.9833</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.61</v>
       </c>
       <c r="I279" t="n">
-        <v>1.2068</v>
+        <v>1.2244</v>
       </c>
       <c r="J279" t="n">
-        <v>25.3428</v>
+        <v>25.7124</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1.22</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5544</v>
+        <v>0.5276</v>
       </c>
       <c r="J280" t="n">
-        <v>11.6424</v>
+        <v>11.0796</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>1.05</v>
       </c>
       <c r="I281" t="n">
-        <v>0.13</v>
+        <v>0.1014</v>
       </c>
       <c r="J281" t="n">
-        <v>2.73</v>
+        <v>2.1294</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.5</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1158</v>
+        <v>1.1282</v>
       </c>
       <c r="J282" t="n">
-        <v>40.1688</v>
+        <v>40.6152</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5071</v>
+        <v>0.4699</v>
       </c>
       <c r="J283" t="n">
-        <v>18.2556</v>
+        <v>16.9164</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.07</v>
       </c>
       <c r="I284" t="n">
-        <v>0.237</v>
+        <v>0.2061</v>
       </c>
       <c r="J284" t="n">
-        <v>8.532</v>
+        <v>7.4196</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0247</v>
+        <v>-0.0193</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.8892</v>
+        <v>-0.6948</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.0247</v>
+        <v>-0.0193</v>
       </c>
       <c r="J286" t="n">
-        <v>-0.8892</v>
+        <v>-0.6948</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.56</v>
       </c>
       <c r="I287" t="n">
-        <v>0.9811</v>
+        <v>0.9483</v>
       </c>
       <c r="J287" t="n">
-        <v>35.3196</v>
+        <v>34.1388</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2127</v>
+        <v>0.1703</v>
       </c>
       <c r="J288" t="n">
-        <v>7.6572</v>
+        <v>6.1308</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.93</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1113</v>
+        <v>-0.0936</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.0068</v>
+        <v>-3.3696</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.329</v>
+        <v>-0.3128</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.844</v>
+        <v>-11.2608</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.7</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3475</v>
+        <v>-0.3327</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.51</v>
+        <v>-11.9772</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3505</v>
+        <v>0.2966</v>
       </c>
       <c r="J292" t="n">
-        <v>10.1645</v>
+        <v>8.6014</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2758</v>
+        <v>0.227</v>
       </c>
       <c r="J293" t="n">
-        <v>7.9982</v>
+        <v>6.583</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.151</v>
+        <v>0.1161</v>
       </c>
       <c r="J294" t="n">
-        <v>4.379</v>
+        <v>3.3669</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1452</v>
+        <v>-0.1259</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.2108</v>
+        <v>-3.6511</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3551</v>
+        <v>-0.3407</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.2979</v>
+        <v>-9.8803</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.51</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1348</v>
+        <v>1.1483</v>
       </c>
       <c r="J297" t="n">
-        <v>32.9092</v>
+        <v>33.3007</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5173</v>
       </c>
       <c r="J298" t="n">
-        <v>16.0921</v>
+        <v>15.0017</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4415</v>
+        <v>0.4033</v>
       </c>
       <c r="J299" t="n">
-        <v>12.8035</v>
+        <v>11.6957</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3674</v>
+        <v>-0.3252</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.6546</v>
+        <v>-9.4308</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3938</v>
+        <v>-0.3514</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.4202</v>
+        <v>-10.1906</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4262</v>
+        <v>1.4526</v>
       </c>
       <c r="J302" t="n">
-        <v>31.3764</v>
+        <v>31.9572</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.51</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0848</v>
+        <v>1.0982</v>
       </c>
       <c r="J303" t="n">
-        <v>23.8656</v>
+        <v>24.1604</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.42</v>
       </c>
       <c r="I304" t="n">
-        <v>0.951</v>
+        <v>0.9478</v>
       </c>
       <c r="J304" t="n">
-        <v>20.922</v>
+        <v>20.8516</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>1.24</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6045</v>
+        <v>0.5793</v>
       </c>
       <c r="J305" t="n">
-        <v>13.299</v>
+        <v>12.7446</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1056</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>2.3232</v>
+        <v>1.7644</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.3</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7151</v>
+        <v>0.6894</v>
       </c>
       <c r="J307" t="n">
-        <v>15.7322</v>
+        <v>15.1668</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2276</v>
+        <v>-0.2122</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.0072</v>
+        <v>-4.6684</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.419</v>
+        <v>-0.4091</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.218</v>
+        <v>-9.0002</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.5</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4982</v>
+        <v>-0.4965</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.9604</v>
+        <v>-10.923</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.48</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5161</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.3432</v>
+        <v>-11.3542</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.46</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8308</v>
+        <v>0.7798</v>
       </c>
       <c r="J312" t="n">
-        <v>24.924</v>
+        <v>23.394</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.28</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5583</v>
+        <v>0.4986</v>
       </c>
       <c r="J313" t="n">
-        <v>16.749</v>
+        <v>14.958</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>0.87</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1827</v>
+        <v>-0.1621</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.481</v>
+        <v>-4.863</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.245</v>
+        <v>-0.2249</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.35</v>
+        <v>-6.747</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3316</v>
+        <v>-0.3159</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.948</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.4</v>
       </c>
       <c r="I317" t="n">
-        <v>0.9816</v>
+        <v>0.9758</v>
       </c>
       <c r="J317" t="n">
-        <v>29.448</v>
+        <v>29.274</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.32</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8237</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>24.711</v>
+        <v>23.967</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.02</v>
       </c>
       <c r="I319" t="n">
-        <v>0.0886</v>
+        <v>0.0701</v>
       </c>
       <c r="J319" t="n">
-        <v>2.658</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2456</v>
+        <v>-0.2069</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.368</v>
+        <v>-6.207</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7565</v>
       </c>
       <c r="J321" t="n">
-        <v>-23.454</v>
+        <v>-22.695</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.92</v>
       </c>
       <c r="I322" t="n">
-        <v>1.583</v>
+        <v>1.6207</v>
       </c>
       <c r="J322" t="n">
-        <v>31.66</v>
+        <v>32.414</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.47</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0242</v>
+        <v>1.0336</v>
       </c>
       <c r="J323" t="n">
-        <v>20.484</v>
+        <v>20.672</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.33</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7786</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J324" t="n">
-        <v>15.572</v>
+        <v>15.292</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>1.33</v>
       </c>
       <c r="I325" t="n">
-        <v>0.7786</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J325" t="n">
-        <v>15.572</v>
+        <v>15.292</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>1.24</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5958</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>11.916</v>
+        <v>11.422</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.56</v>
       </c>
       <c r="I327" t="n">
-        <v>1.1293</v>
+        <v>1.1688</v>
       </c>
       <c r="J327" t="n">
-        <v>22.586</v>
+        <v>23.376</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.63</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.3794</v>
+        <v>-0.3674</v>
       </c>
       <c r="J328" t="n">
-        <v>-7.588</v>
+        <v>-7.348</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4591</v>
+        <v>-0.453</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.182</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.51</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4855</v>
+        <v>-0.4821</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.641999999999999</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.27</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6927</v>
+        <v>-0.7232</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.854</v>
+        <v>-14.464</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4585</v>
       </c>
       <c r="J332" t="n">
-        <v>15.0104</v>
+        <v>13.2965</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.23</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4847</v>
+        <v>0.4259</v>
       </c>
       <c r="J333" t="n">
-        <v>14.0563</v>
+        <v>12.3511</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0989</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J334" t="n">
-        <v>-2.8681</v>
+        <v>-2.3809</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.79</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2621</v>
+        <v>-0.2425</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.6009</v>
+        <v>-7.0325</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.78</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2719</v>
+        <v>-0.2527</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.8851</v>
+        <v>-7.3283</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.25</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6585</v>
+        <v>0.625</v>
       </c>
       <c r="J337" t="n">
-        <v>19.0965</v>
+        <v>18.125</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.23</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6159</v>
+        <v>0.5809</v>
       </c>
       <c r="J338" t="n">
-        <v>17.8611</v>
+        <v>16.8461</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>1.17</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4842</v>
+        <v>0.4471</v>
       </c>
       <c r="J339" t="n">
-        <v>14.0418</v>
+        <v>12.9659</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>1.12</v>
       </c>
       <c r="I340" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J340" t="n">
-        <v>10.672</v>
+        <v>9.633800000000001</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>1</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.0254</v>
+        <v>-0.02</v>
       </c>
       <c r="J341" t="n">
-        <v>-0.7366</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.61</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2153</v>
+        <v>1.2319</v>
       </c>
       <c r="J342" t="n">
-        <v>26.7366</v>
+        <v>27.1018</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.53</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1122</v>
+        <v>1.1266</v>
       </c>
       <c r="J343" t="n">
-        <v>24.4684</v>
+        <v>24.7852</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.42</v>
       </c>
       <c r="I344" t="n">
-        <v>0.952</v>
+        <v>0.9484</v>
       </c>
       <c r="J344" t="n">
-        <v>20.944</v>
+        <v>20.8648</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.3</v>
       </c>
       <c r="I345" t="n">
-        <v>0.7289</v>
+        <v>0.7096</v>
       </c>
       <c r="J345" t="n">
-        <v>16.0358</v>
+        <v>15.6112</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>1.08</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2263</v>
+        <v>0.1953</v>
       </c>
       <c r="J346" t="n">
-        <v>4.9786</v>
+        <v>4.2966</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>0.76</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.2515</v>
+        <v>-0.2377</v>
       </c>
       <c r="J347" t="n">
-        <v>-5.533</v>
+        <v>-5.2294</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3195</v>
+        <v>-0.3082</v>
       </c>
       <c r="J348" t="n">
-        <v>-7.029</v>
+        <v>-6.7804</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3378</v>
+        <v>-0.327</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.4316</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.58</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4153</v>
+        <v>-0.4066</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.1366</v>
+        <v>-8.9452</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4945</v>
+        <v>-0.492</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.879</v>
+        <v>-10.824</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5017</v>
+        <v>0.4605</v>
       </c>
       <c r="J352" t="n">
-        <v>15.051</v>
+        <v>13.815</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.13</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4057</v>
+        <v>0.3644</v>
       </c>
       <c r="J353" t="n">
-        <v>12.171</v>
+        <v>10.932</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.12</v>
       </c>
       <c r="I354" t="n">
-        <v>0.3808</v>
+        <v>0.3399</v>
       </c>
       <c r="J354" t="n">
-        <v>11.424</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.04</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1613</v>
+        <v>0.1332</v>
       </c>
       <c r="J355" t="n">
-        <v>4.839</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.529</v>
+        <v>-0.4879</v>
       </c>
       <c r="J356" t="n">
-        <v>-15.87</v>
+        <v>-14.637</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.48</v>
       </c>
       <c r="I357" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>25.449</v>
+        <v>23.907</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2428</v>
+        <v>0.1988</v>
       </c>
       <c r="J358" t="n">
-        <v>7.284</v>
+        <v>5.964</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.03</v>
       </c>
       <c r="I359" t="n">
-        <v>0.094</v>
+        <v>0.0709</v>
       </c>
       <c r="J359" t="n">
-        <v>2.82</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1168</v>
+        <v>-0.0983</v>
       </c>
       <c r="J360" t="n">
-        <v>-3.504</v>
+        <v>-2.949</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.78</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2777</v>
+        <v>-0.2591</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.331</v>
+        <v>-7.773</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.07</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2657</v>
+        <v>0.2291</v>
       </c>
       <c r="J362" t="n">
-        <v>5.8454</v>
+        <v>5.0402</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J363" t="n">
-        <v>-1.8282</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.7</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3216</v>
+        <v>-0.3064</v>
       </c>
       <c r="J364" t="n">
-        <v>-7.0752</v>
+        <v>-6.7408</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.58</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4293</v>
+        <v>-0.4203</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.444599999999999</v>
+        <v>-9.246600000000001</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.45</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.543</v>
+        <v>-0.5474</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.946</v>
+        <v>-12.0428</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.73</v>
       </c>
       <c r="I367" t="n">
-        <v>1.3733</v>
+        <v>1.3966</v>
       </c>
       <c r="J367" t="n">
-        <v>30.2126</v>
+        <v>30.7252</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.65</v>
       </c>
       <c r="I368" t="n">
-        <v>1.2724</v>
+        <v>1.2905</v>
       </c>
       <c r="J368" t="n">
-        <v>27.9928</v>
+        <v>28.391</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.41</v>
       </c>
       <c r="I369" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J369" t="n">
-        <v>20.658</v>
+        <v>20.504</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.02</v>
       </c>
       <c r="I370" t="n">
-        <v>0.0424</v>
+        <v>0.0248</v>
       </c>
       <c r="J370" t="n">
-        <v>0.9328</v>
+        <v>0.5456</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.95</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2623</v>
+        <v>-0.229</v>
       </c>
       <c r="J371" t="n">
-        <v>-5.7706</v>
+        <v>-5.038</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.08</v>
       </c>
       <c r="I372" t="n">
-        <v>0.2167</v>
+        <v>0.1735</v>
       </c>
       <c r="J372" t="n">
-        <v>6.0676</v>
+        <v>4.858</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.03</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1033</v>
+        <v>0.076</v>
       </c>
       <c r="J373" t="n">
-        <v>2.8924</v>
+        <v>2.128</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0765</v>
+        <v>0.0543</v>
       </c>
       <c r="J374" t="n">
-        <v>2.142</v>
+        <v>1.5204</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1449</v>
+        <v>-0.1256</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.0572</v>
+        <v>-3.5168</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.85</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1993</v>
+        <v>-0.1788</v>
       </c>
       <c r="J376" t="n">
-        <v>-5.5804</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.77</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4641</v>
+        <v>1.4973</v>
       </c>
       <c r="J377" t="n">
-        <v>40.9948</v>
+        <v>41.9244</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7137</v>
+        <v>0.6842</v>
       </c>
       <c r="J378" t="n">
-        <v>19.9836</v>
+        <v>19.1576</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.3115</v>
+        <v>0.2785</v>
       </c>
       <c r="J379" t="n">
-        <v>8.722</v>
+        <v>7.798</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.97</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.1701</v>
+        <v>-0.1387</v>
       </c>
       <c r="J380" t="n">
-        <v>-4.7628</v>
+        <v>-3.8836</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.84</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5301</v>
+        <v>-0.4914</v>
       </c>
       <c r="J381" t="n">
-        <v>-14.8428</v>
+        <v>-13.7592</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.82</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4599</v>
+        <v>1.4889</v>
       </c>
       <c r="J382" t="n">
-        <v>30.6579</v>
+        <v>31.2669</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.74</v>
       </c>
       <c r="I383" t="n">
-        <v>1.3633</v>
+        <v>1.387</v>
       </c>
       <c r="J383" t="n">
-        <v>28.6293</v>
+        <v>29.127</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0369</v>
+        <v>1.0488</v>
       </c>
       <c r="J384" t="n">
-        <v>21.7749</v>
+        <v>22.0248</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.29</v>
       </c>
       <c r="I385" t="n">
-        <v>0.6962</v>
+        <v>0.6773</v>
       </c>
       <c r="J385" t="n">
-        <v>14.6202</v>
+        <v>14.2233</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.07</v>
       </c>
       <c r="I386" t="n">
-        <v>0.1847</v>
+        <v>0.1528</v>
       </c>
       <c r="J386" t="n">
-        <v>3.8787</v>
+        <v>3.2088</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.07</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2434</v>
+        <v>0.2028</v>
       </c>
       <c r="J387" t="n">
-        <v>5.1114</v>
+        <v>4.2588</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.97</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.0369</v>
+        <v>-0.0276</v>
       </c>
       <c r="J388" t="n">
-        <v>-0.7749</v>
+        <v>-0.5796</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3183</v>
+        <v>-0.3019</v>
       </c>
       <c r="J389" t="n">
-        <v>-6.6843</v>
+        <v>-6.3399</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.7</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3276</v>
+        <v>-0.3115</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.8796</v>
+        <v>-6.5415</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.55</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.462</v>
+        <v>-0.4566</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.702</v>
+        <v>-9.5886</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>2.09</v>
       </c>
       <c r="I392" t="n">
-        <v>1.7754</v>
+        <v>1.8308</v>
       </c>
       <c r="J392" t="n">
-        <v>40.8342</v>
+        <v>42.1084</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.48</v>
       </c>
       <c r="I393" t="n">
-        <v>1.0368</v>
+        <v>1.0488</v>
       </c>
       <c r="J393" t="n">
-        <v>23.8464</v>
+        <v>24.1224</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.42</v>
       </c>
       <c r="I394" t="n">
-        <v>0.9436</v>
+        <v>0.9435</v>
       </c>
       <c r="J394" t="n">
-        <v>21.7028</v>
+        <v>21.7005</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>1.26</v>
       </c>
       <c r="I395" t="n">
-        <v>0.6341</v>
+        <v>0.6116</v>
       </c>
       <c r="J395" t="n">
-        <v>14.5843</v>
+        <v>14.0668</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>1.17</v>
       </c>
       <c r="I396" t="n">
-        <v>0.4374</v>
+        <v>0.4062</v>
       </c>
       <c r="J396" t="n">
-        <v>10.0602</v>
+        <v>9.342599999999999</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>0.75</v>
       </c>
       <c r="I397" t="n">
-        <v>-0.2514</v>
+        <v>-0.2373</v>
       </c>
       <c r="J397" t="n">
-        <v>-5.7822</v>
+        <v>-5.4579</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>0.64</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.3585</v>
+        <v>-0.3499</v>
       </c>
       <c r="J398" t="n">
-        <v>-8.2455</v>
+        <v>-8.047700000000001</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.53</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.4529</v>
+        <v>-0.4474</v>
       </c>
       <c r="J399" t="n">
-        <v>-10.4167</v>
+        <v>-10.2902</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.53</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4529</v>
+        <v>-0.4474</v>
       </c>
       <c r="J400" t="n">
-        <v>-10.4167</v>
+        <v>-10.2902</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.52</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4616</v>
+        <v>-0.4567</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.6168</v>
+        <v>-10.5041</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.58</v>
       </c>
       <c r="I402" t="n">
-        <v>1.2291</v>
+        <v>1.2469</v>
       </c>
       <c r="J402" t="n">
-        <v>33.1857</v>
+        <v>33.6663</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4174</v>
+        <v>0.38</v>
       </c>
       <c r="J403" t="n">
-        <v>11.2698</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3453</v>
+        <v>0.3094</v>
       </c>
       <c r="J404" t="n">
-        <v>9.3231</v>
+        <v>8.3538</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>1.05</v>
       </c>
       <c r="I405" t="n">
-        <v>0.1801</v>
+        <v>0.1527</v>
       </c>
       <c r="J405" t="n">
-        <v>4.8627</v>
+        <v>4.1229</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5914</v>
+        <v>-0.5542</v>
       </c>
       <c r="J406" t="n">
-        <v>-15.9678</v>
+        <v>-14.9634</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1911</v>
+        <v>0.1511</v>
       </c>
       <c r="J407" t="n">
-        <v>5.1597</v>
+        <v>4.0797</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.03</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1187</v>
+        <v>0.0887</v>
       </c>
       <c r="J408" t="n">
-        <v>3.2049</v>
+        <v>2.3949</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1392</v>
+        <v>-0.1218</v>
       </c>
       <c r="J409" t="n">
-        <v>-3.7584</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.83</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2126</v>
+        <v>-0.1929</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.7402</v>
+        <v>-5.2083</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.66</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3744</v>
+        <v>-0.361</v>
       </c>
       <c r="J411" t="n">
-        <v>-10.1088</v>
+        <v>-9.747</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.41</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0134</v>
+        <v>1.0151</v>
       </c>
       <c r="J412" t="n">
-        <v>26.3484</v>
+        <v>26.3926</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.35</v>
       </c>
       <c r="I413" t="n">
-        <v>0.9005</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J413" t="n">
-        <v>23.413</v>
+        <v>22.9736</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>0.99</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.0641</v>
+        <v>-0.0461</v>
       </c>
       <c r="J414" t="n">
-        <v>-1.6666</v>
+        <v>-1.1986</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>0.9</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3492</v>
+        <v>-0.3067</v>
       </c>
       <c r="J415" t="n">
-        <v>-9.0792</v>
+        <v>-7.9742</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.53</v>
       </c>
       <c r="I416" t="n">
-        <v>-1.164</v>
+        <v>-1.184</v>
       </c>
       <c r="J416" t="n">
-        <v>-30.264</v>
+        <v>-30.784</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.19</v>
       </c>
       <c r="I417" t="n">
-        <v>0.4109</v>
+        <v>0.3542</v>
       </c>
       <c r="J417" t="n">
-        <v>10.6834</v>
+        <v>9.209199999999999</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.14</v>
       </c>
       <c r="I418" t="n">
-        <v>0.323</v>
+        <v>0.2711</v>
       </c>
       <c r="J418" t="n">
-        <v>8.398</v>
+        <v>7.0486</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>1.03</v>
       </c>
       <c r="I419" t="n">
-        <v>0.0973</v>
+        <v>0.0725</v>
       </c>
       <c r="J419" t="n">
-        <v>2.5298</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>1.02</v>
       </c>
       <c r="I420" t="n">
-        <v>0.0713</v>
+        <v>0.0516</v>
       </c>
       <c r="J420" t="n">
-        <v>1.8538</v>
+        <v>1.3416</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.75</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3033</v>
+        <v>-0.2857</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.8858</v>
+        <v>-7.4282</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.59</v>
       </c>
       <c r="I422" t="n">
-        <v>1.2126</v>
+        <v>1.2279</v>
       </c>
       <c r="J422" t="n">
-        <v>29.1024</v>
+        <v>29.4696</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.41</v>
       </c>
       <c r="I423" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J423" t="n">
-        <v>22.8984</v>
+        <v>22.6824</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.25</v>
       </c>
       <c r="I424" t="n">
-        <v>0.6438</v>
+        <v>0.615</v>
       </c>
       <c r="J424" t="n">
-        <v>15.4512</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.15</v>
       </c>
       <c r="I425" t="n">
-        <v>0.4246</v>
+        <v>0.3919</v>
       </c>
       <c r="J425" t="n">
-        <v>10.1904</v>
+        <v>9.4056</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.9</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3903</v>
+        <v>-0.3508</v>
       </c>
       <c r="J426" t="n">
-        <v>-9.3672</v>
+        <v>-8.4192</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.09</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2795</v>
+        <v>0.2348</v>
       </c>
       <c r="J427" t="n">
-        <v>6.708</v>
+        <v>5.6352</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.04</v>
       </c>
       <c r="I428" t="n">
-        <v>0.1655</v>
+        <v>0.1317</v>
       </c>
       <c r="J428" t="n">
-        <v>3.972</v>
+        <v>3.1608</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2547</v>
+        <v>-0.2366</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.1128</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.74</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.2926</v>
+        <v>-0.275</v>
       </c>
       <c r="J430" t="n">
-        <v>-7.0224</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.45</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.5505</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J431" t="n">
-        <v>-13.212</v>
+        <v>-13.368</v>
       </c>
     </row>
   </sheetData>
